--- a/docs/requerimientos.xlsx
+++ b/docs/requerimientos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USUARIO\Desktop\roomtrip\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD161729-D921-48F5-96EC-A3781A35CDD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67C40F07-F2BB-4AD3-9B4C-0E54D1133DC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="390" yWindow="195" windowWidth="21600" windowHeight="15405" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
     <sheet name="Plan por laboratorio" sheetId="5" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Requerimientos!$A$5:$M$50</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Requerimientos!$A$5:$M$52</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'Plan por laboratorio'!$5:$5</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Por rol'!$5:$5</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">Requerimientos!$5:$5</definedName>
@@ -40,12 +40,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="840" uniqueCount="309">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="876" uniqueCount="316">
   <si>
     <t>RoomTrip · Cómo usar este libro</t>
   </si>
   <si>
-    <t>Matriz de requerimientos del proyecto · actualizado el 23/08/2026</t>
+    <t>Matriz de requerimientos del proyecto · versión interna del equipo</t>
   </si>
   <si>
     <t>Hojas del libro</t>
@@ -63,7 +63,7 @@
     <t>Resumen</t>
   </si>
   <si>
-    <t>Indicadores del proyecto: avance por rol, carga por laboratorio y por módulo. Todo calculado con fórmulas.</t>
+    <t>Indicadores del proyecto: avance por rol, carga por laboratorio y por módulo.</t>
   </si>
   <si>
     <t>No. Se actualiza solo.</t>
@@ -72,7 +72,7 @@
     <t>Requerimientos</t>
   </si>
   <si>
-    <t>Tabla maestra con los 45 requerimientos y todos sus atributos. Tiene filtros y listas desplegables.</t>
+    <t>Tabla maestra con todos los requerimientos. Tiene filtros y listas desplegables.</t>
   </si>
   <si>
     <t>Sí. Es la única hoja editable.</t>
@@ -81,7 +81,7 @@
     <t>Por rol</t>
   </si>
   <si>
-    <t>Los mismos requerimientos agrupados por rol, para repartir el trabajo entre el equipo.</t>
+    <t>Los mismos requerimientos agrupados por rol, para repartir el trabajo.</t>
   </si>
   <si>
     <t>No. Refleja la maestra.</t>
@@ -90,7 +90,7 @@
     <t>Plan por laboratorio</t>
   </si>
   <si>
-    <t>Qué se trabaja en cada entrega del curso. Un requerimiento aparece en varias.</t>
+    <t>Qué se trabaja en cada entrega. Un requerimiento aparece en varias.</t>
   </si>
   <si>
     <t>Guía</t>
@@ -111,7 +111,7 @@
     <t>•   Ejemplo: «reservar con tarjeta» se dibuja en el Lab 3 como pantalla navegable y recién en el Lab 6 guarda la reserva de verdad. Sus fases son L3 · L6 y su cierre es el Lab 6.</t>
   </si>
   <si>
-    <t>•   Por eso la suma de la columna «Se trabaja» del Resumen es mayor que 45. No es un error.</t>
+    <t>•   Por eso la suma de la columna «Se trabaja» del Resumen es mayor que el total. No es un error.</t>
   </si>
   <si>
     <t>•   Para saber qué se entrega en una fecha concreta, mira «Cierre», no «Fases».</t>
@@ -177,7 +177,7 @@
     <t>Criterio de aceptación</t>
   </si>
   <si>
-    <t>Cómo se comprueba que está cumplido. Es lo que lo hace evaluable.</t>
+    <t>Cómo se comprueba que está cumplido.</t>
   </si>
   <si>
     <t>Prioridad</t>
@@ -252,7 +252,7 @@
     <t>•   Los IDs no se reutilizan: si un requerimiento se elimina, su ID queda retirado.</t>
   </si>
   <si>
-    <t>•   Los cambios de este libro se versionan en el repositorio junto con docs/requerimientos.md.</t>
+    <t>•   Este libro es de uso interno. La versión que se entrega al profesor se genera con generar_entrega_xlsx.py.</t>
   </si>
   <si>
     <t>RoomTrip · Resumen de requerimientos</t>
@@ -336,7 +336,7 @@
     <t>Carga por laboratorio</t>
   </si>
   <si>
-    <t>«Se trabaja» cuenta los requerimientos que se tocan en ese laboratorio; «Cierra aquí», los que quedan terminados. Un requerimiento se trabaja en varios.</t>
+    <t>«Se trabaja» cuenta los requerimientos que se tocan en ese laboratorio; «Cierra aquí», los que quedan terminados. Uno se trabaja en varios.</t>
   </si>
   <si>
     <t>Laboratorio</t>
@@ -534,6 +534,21 @@
     <t>El hotel ve solo los chats de reservas activas y puede responder</t>
   </si>
   <si>
+    <t>RF-AH-10</t>
+  </si>
+  <si>
+    <t>Establecer el monto mínimo de reserva que da derecho al taxi gratuito al aeropuerto</t>
+  </si>
+  <si>
+    <t>El hotel guarda un monto mínimo y solo las reservas que lo alcanzan habilitan la opción de taxi al cliente</t>
+  </si>
+  <si>
+    <t>L3  ·  L6</t>
+  </si>
+  <si>
+    <t>Sin este monto no se puede evaluar la regla del taxi gratuito.</t>
+  </si>
+  <si>
     <t>RF-AH-07</t>
   </si>
   <si>
@@ -543,9 +558,6 @@
     <t>El cobro adicional exige los 3 campos y se suma al total de la reserva</t>
   </si>
   <si>
-    <t>L3  ·  L6</t>
-  </si>
-  <si>
     <t>RF-AH-08</t>
   </si>
   <si>
@@ -711,9 +723,6 @@
     <t>El cliente recibe una notificación push con el monto cobrado</t>
   </si>
   <si>
-    <t>L5  ·  L6</t>
-  </si>
-  <si>
     <t>Requiere Firebase Cloud Messaging.</t>
   </si>
   <si>
@@ -738,6 +747,18 @@
     <t>El historial lista las reservas del cliente autenticado con fechas hotel habitación estado y monto</t>
   </si>
   <si>
+    <t>RF-CL-12</t>
+  </si>
+  <si>
+    <t>Consultar los lugares históricos cercanos al hotel</t>
+  </si>
+  <si>
+    <t>El cliente ve la lista de lugares históricos cercanos registrados por el administrador del hotel</t>
+  </si>
+  <si>
+    <t>Falta la pantalla en Figma; el hotel ya los registra en RF-AH-01.</t>
+  </si>
+  <si>
     <t>RF-CL-08</t>
   </si>
   <si>
@@ -804,48 +825,48 @@
     <t>Al intentar reservar fechas que se solapan con una reserva existente de esa habitación el sistema rechaza la operación</t>
   </si>
   <si>
+    <t>Validar con una transacción; no basta con comprobarlo en el cliente.</t>
+  </si>
+  <si>
+    <t>RF-GN-02</t>
+  </si>
+  <si>
+    <t>Un mismo cliente no puede tener reservas con fechas de alojamiento superpuestas</t>
+  </si>
+  <si>
+    <t>Al intentar una segunda reserva que se solapa con otra propia el sistema la rechaza</t>
+  </si>
+  <si>
+    <t>RF-GN-03</t>
+  </si>
+  <si>
+    <t>Login único: tras autenticar se resuelve el rol y se navega al flujo correspondiente</t>
+  </si>
+  <si>
+    <t>Con credenciales válidas de cada uno de los 4 roles la app abre el grafo de navegación propio de ese rol</t>
+  </si>
+  <si>
+    <t>RF-GN-04</t>
+  </si>
+  <si>
+    <t>Los mensajes de chat persisten con fecha y hora</t>
+  </si>
+  <si>
+    <t>Al reabrir el chat los mensajes anteriores se muestran con su fecha y hora</t>
+  </si>
+  <si>
+    <t>RNF-01</t>
+  </si>
+  <si>
+    <t>Las contraseñas nunca se almacenan en texto plano</t>
+  </si>
+  <si>
+    <t>Ninguna colección contiene contraseñas legibles y la autenticación la gestiona Firebase Auth</t>
+  </si>
+  <si>
     <t>L6</t>
   </si>
   <si>
-    <t>Validar con una transacción; no basta con comprobarlo en el cliente.</t>
-  </si>
-  <si>
-    <t>RF-GN-02</t>
-  </si>
-  <si>
-    <t>Un mismo cliente no puede tener reservas con fechas de alojamiento superpuestas</t>
-  </si>
-  <si>
-    <t>Al intentar una segunda reserva que se solapa con otra propia el sistema la rechaza</t>
-  </si>
-  <si>
-    <t>RF-GN-03</t>
-  </si>
-  <si>
-    <t>Login único: tras autenticar se resuelve el rol y se navega al flujo correspondiente</t>
-  </si>
-  <si>
-    <t>Con credenciales válidas de cada uno de los 4 roles la app abre el grafo de navegación propio de ese rol</t>
-  </si>
-  <si>
-    <t>RF-GN-04</t>
-  </si>
-  <si>
-    <t>Los mensajes de chat persisten con fecha y hora</t>
-  </si>
-  <si>
-    <t>Al reabrir el chat los mensajes anteriores se muestran con su fecha y hora</t>
-  </si>
-  <si>
-    <t>RNF-01</t>
-  </si>
-  <si>
-    <t>Las contraseñas nunca se almacenan en texto plano</t>
-  </si>
-  <si>
-    <t>Ninguna colección contiene contraseñas legibles y la autenticación la gestiona Firebase Auth</t>
-  </si>
-  <si>
     <t>RNF-02</t>
   </si>
   <si>
@@ -930,13 +951,13 @@
     <t>Superadmin    ·    5 requerimientos</t>
   </si>
   <si>
-    <t>Administrador de hotel    ·    9 requerimientos</t>
+    <t>Administrador de hotel    ·    10 requerimientos</t>
   </si>
   <si>
     <t>Taxista    ·    7 requerimientos</t>
   </si>
   <si>
-    <t>Cliente    ·    11 requerimientos</t>
+    <t>Cliente    ·    12 requerimientos</t>
   </si>
   <si>
     <t>Transversal    ·    13 requerimientos</t>
@@ -948,19 +969,19 @@
     <t>Qué requerimientos se trabajan en cada entrega del curso</t>
   </si>
   <si>
-    <t>Un requerimiento aparece en varios laboratorios: los labs son capas de madurez, no un reparto del alcance. La columna «Cierre» indica dónde queda terminado.</t>
-  </si>
-  <si>
-    <t>Lab 3    ·    15/09/2026    ·    Implementación de mockups: navigation, menús y elementos UI    ·    30 requerimientos, 1 cierra aquí</t>
-  </si>
-  <si>
-    <t>Lab 4    ·    29/09/2026    ·    RecyclerView: listado de elementos con data estática    ·    13 requerimientos, 0 cierran aquí</t>
+    <t>Un requerimiento aparece en varios laboratorios: son capas de madurez, no un reparto del alcance. La columna «Cierre» indica dónde queda terminado.</t>
+  </si>
+  <si>
+    <t>Lab 3    ·    15/09/2026    ·    Implementación de mockups: navigation, menús y elementos UI    ·    36 requerimientos, 1 cierra aquí</t>
+  </si>
+  <si>
+    <t>Lab 4    ·    29/09/2026    ·    RecyclerView: listado de elementos con data estática    ·    15 requerimientos, 0 cierran aquí</t>
   </si>
   <si>
     <t>Lab 5    ·    20/10/2026    ·    Storage local y notificaciones    ·    6 requerimientos, 0 cierran aquí</t>
   </si>
   <si>
-    <t>Lab 6    ·    03/11/2026    ·    Firebase Authentication y Firebase Database    ·    36 requerimientos, 31 cierran aquí</t>
+    <t>Lab 6    ·    03/11/2026    ·    Firebase Authentication y Firebase Database    ·    38 requerimientos, 33 cierran aquí</t>
   </si>
   <si>
     <t>Lab 7    ·    14/12/2026    ·    Presentación prefinal (85%)    ·    11 requerimientos, 10 cierran aquí</t>
@@ -1592,13 +1613,13 @@
                   <c:v>5</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>9</c:v>
+                  <c:v>10</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>7</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>11</c:v>
+                  <c:v>12</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>13</c:v>
@@ -1608,7 +1629,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-3AA3-439E-A07C-02A3360A877E}"/>
+              <c16:uniqueId val="{00000000-B1AD-40AB-A069-E5D523AED9EF}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2489,40 +2510,40 @@
     </row>
     <row r="7" spans="1:9" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="6">
-        <f>COUNTA(Requerimientos!$A$6:$A$50)</f>
-        <v>45</v>
+        <f>COUNTA(Requerimientos!$A$6:$A$52)</f>
+        <v>47</v>
       </c>
       <c r="B7" s="6">
-        <f>COUNTIF(Requerimientos!$D$6:$D$50,"Funcional")</f>
-        <v>36</v>
+        <f>COUNTIF(Requerimientos!$D$6:$D$52,"Funcional")</f>
+        <v>38</v>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIF(Requerimientos!$D$6:$D$50,"No funcional")</f>
+        <f>COUNTIF(Requerimientos!$D$6:$D$52,"No funcional")</f>
         <v>9</v>
       </c>
       <c r="D7" s="6">
-        <f>COUNTIF(Requerimientos!$G$6:$G$50,"Alta")</f>
-        <v>37</v>
+        <f>COUNTIF(Requerimientos!$G$6:$G$52,"Alta")</f>
+        <v>38</v>
       </c>
       <c r="E7" s="6">
-        <f>COUNTIF(Requerimientos!$J$6:$J$50,"Hecho")</f>
+        <f>COUNTIF(Requerimientos!$J$6:$J$52,"Hecho")</f>
         <v>0</v>
       </c>
       <c r="F7" s="6">
-        <f>COUNTIF(Requerimientos!$J$6:$J$50,"En progreso")</f>
+        <f>COUNTIF(Requerimientos!$J$6:$J$52,"En progreso")</f>
         <v>0</v>
       </c>
       <c r="G7" s="6">
-        <f>COUNTIF(Requerimientos!$J$6:$J$50,"Pendiente")</f>
-        <v>45</v>
+        <f>COUNTIF(Requerimientos!$J$6:$J$52,"Pendiente")</f>
+        <v>47</v>
       </c>
       <c r="H7" s="7">
-        <f>IFERROR(COUNTIF(Requerimientos!$J$6:$J$50,"Hecho")/COUNTA(Requerimientos!$A$6:$A$50),0)</f>
+        <f>IFERROR(COUNTIF(Requerimientos!$J$6:$J$52,"Hecho")/COUNTA(Requerimientos!$A$6:$A$52),0)</f>
         <v>0</v>
       </c>
       <c r="I7" s="8">
-        <f>COUNTIF(Requerimientos!$K$6:$K$50,"No")</f>
-        <v>17</v>
+        <f>COUNTIF(Requerimientos!$K$6:$K$52,"No")</f>
+        <v>19</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -2572,27 +2593,27 @@
         <v>92</v>
       </c>
       <c r="B11" s="10">
-        <f>COUNTIF(Requerimientos!$C$6:$C$50,$A11)</f>
+        <f>COUNTIF(Requerimientos!$C$6:$C$52,$A11)</f>
         <v>5</v>
       </c>
       <c r="C11" s="10">
-        <f>COUNTIFS(Requerimientos!$C$6:$C$50,$A11,Requerimientos!$G$6:$G$50,"Alta")</f>
+        <f>COUNTIFS(Requerimientos!$C$6:$C$52,$A11,Requerimientos!$G$6:$G$52,"Alta")</f>
         <v>3</v>
       </c>
       <c r="D11" s="10">
-        <f>COUNTIFS(Requerimientos!$C$6:$C$50,$A11,Requerimientos!$G$6:$G$50,"Media")</f>
+        <f>COUNTIFS(Requerimientos!$C$6:$C$52,$A11,Requerimientos!$G$6:$G$52,"Media")</f>
         <v>2</v>
       </c>
       <c r="E11" s="10">
-        <f>COUNTIFS(Requerimientos!$C$6:$C$50,$A11,Requerimientos!$J$6:$J$50,"Pendiente")</f>
+        <f>COUNTIFS(Requerimientos!$C$6:$C$52,$A11,Requerimientos!$J$6:$J$52,"Pendiente")</f>
         <v>5</v>
       </c>
       <c r="F11" s="10">
-        <f>COUNTIFS(Requerimientos!$C$6:$C$50,$A11,Requerimientos!$J$6:$J$50,"En progreso")</f>
+        <f>COUNTIFS(Requerimientos!$C$6:$C$52,$A11,Requerimientos!$J$6:$J$52,"En progreso")</f>
         <v>0</v>
       </c>
       <c r="G11" s="10">
-        <f>COUNTIFS(Requerimientos!$C$6:$C$50,$A11,Requerimientos!$J$6:$J$50,"Hecho")</f>
+        <f>COUNTIFS(Requerimientos!$C$6:$C$52,$A11,Requerimientos!$J$6:$J$52,"Hecho")</f>
         <v>0</v>
       </c>
       <c r="H11" s="11">
@@ -2600,7 +2621,7 @@
         <v>0</v>
       </c>
       <c r="I11" s="10">
-        <f>COUNTIFS(Requerimientos!$C$6:$C$50,$A11,Requerimientos!$K$6:$K$50,"No")</f>
+        <f>COUNTIFS(Requerimientos!$C$6:$C$52,$A11,Requerimientos!$K$6:$K$52,"No")</f>
         <v>5</v>
       </c>
     </row>
@@ -2609,27 +2630,27 @@
         <v>93</v>
       </c>
       <c r="B12" s="13">
-        <f>COUNTIF(Requerimientos!$C$6:$C$50,$A12)</f>
-        <v>9</v>
+        <f>COUNTIF(Requerimientos!$C$6:$C$52,$A12)</f>
+        <v>10</v>
       </c>
       <c r="C12" s="13">
-        <f>COUNTIFS(Requerimientos!$C$6:$C$50,$A12,Requerimientos!$G$6:$G$50,"Alta")</f>
-        <v>6</v>
+        <f>COUNTIFS(Requerimientos!$C$6:$C$52,$A12,Requerimientos!$G$6:$G$52,"Alta")</f>
+        <v>7</v>
       </c>
       <c r="D12" s="13">
-        <f>COUNTIFS(Requerimientos!$C$6:$C$50,$A12,Requerimientos!$G$6:$G$50,"Media")</f>
+        <f>COUNTIFS(Requerimientos!$C$6:$C$52,$A12,Requerimientos!$G$6:$G$52,"Media")</f>
         <v>3</v>
       </c>
       <c r="E12" s="13">
-        <f>COUNTIFS(Requerimientos!$C$6:$C$50,$A12,Requerimientos!$J$6:$J$50,"Pendiente")</f>
-        <v>9</v>
+        <f>COUNTIFS(Requerimientos!$C$6:$C$52,$A12,Requerimientos!$J$6:$J$52,"Pendiente")</f>
+        <v>10</v>
       </c>
       <c r="F12" s="13">
-        <f>COUNTIFS(Requerimientos!$C$6:$C$50,$A12,Requerimientos!$J$6:$J$50,"En progreso")</f>
+        <f>COUNTIFS(Requerimientos!$C$6:$C$52,$A12,Requerimientos!$J$6:$J$52,"En progreso")</f>
         <v>0</v>
       </c>
       <c r="G12" s="13">
-        <f>COUNTIFS(Requerimientos!$C$6:$C$50,$A12,Requerimientos!$J$6:$J$50,"Hecho")</f>
+        <f>COUNTIFS(Requerimientos!$C$6:$C$52,$A12,Requerimientos!$J$6:$J$52,"Hecho")</f>
         <v>0</v>
       </c>
       <c r="H12" s="14">
@@ -2637,8 +2658,8 @@
         <v>0</v>
       </c>
       <c r="I12" s="13">
-        <f>COUNTIFS(Requerimientos!$C$6:$C$50,$A12,Requerimientos!$K$6:$K$50,"No")</f>
-        <v>1</v>
+        <f>COUNTIFS(Requerimientos!$C$6:$C$52,$A12,Requerimientos!$K$6:$K$52,"No")</f>
+        <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
@@ -2646,27 +2667,27 @@
         <v>94</v>
       </c>
       <c r="B13" s="10">
-        <f>COUNTIF(Requerimientos!$C$6:$C$50,$A13)</f>
+        <f>COUNTIF(Requerimientos!$C$6:$C$52,$A13)</f>
         <v>7</v>
       </c>
       <c r="C13" s="10">
-        <f>COUNTIFS(Requerimientos!$C$6:$C$50,$A13,Requerimientos!$G$6:$G$50,"Alta")</f>
+        <f>COUNTIFS(Requerimientos!$C$6:$C$52,$A13,Requerimientos!$G$6:$G$52,"Alta")</f>
         <v>7</v>
       </c>
       <c r="D13" s="10">
-        <f>COUNTIFS(Requerimientos!$C$6:$C$50,$A13,Requerimientos!$G$6:$G$50,"Media")</f>
+        <f>COUNTIFS(Requerimientos!$C$6:$C$52,$A13,Requerimientos!$G$6:$G$52,"Media")</f>
         <v>0</v>
       </c>
       <c r="E13" s="10">
-        <f>COUNTIFS(Requerimientos!$C$6:$C$50,$A13,Requerimientos!$J$6:$J$50,"Pendiente")</f>
+        <f>COUNTIFS(Requerimientos!$C$6:$C$52,$A13,Requerimientos!$J$6:$J$52,"Pendiente")</f>
         <v>7</v>
       </c>
       <c r="F13" s="10">
-        <f>COUNTIFS(Requerimientos!$C$6:$C$50,$A13,Requerimientos!$J$6:$J$50,"En progreso")</f>
+        <f>COUNTIFS(Requerimientos!$C$6:$C$52,$A13,Requerimientos!$J$6:$J$52,"En progreso")</f>
         <v>0</v>
       </c>
       <c r="G13" s="10">
-        <f>COUNTIFS(Requerimientos!$C$6:$C$50,$A13,Requerimientos!$J$6:$J$50,"Hecho")</f>
+        <f>COUNTIFS(Requerimientos!$C$6:$C$52,$A13,Requerimientos!$J$6:$J$52,"Hecho")</f>
         <v>0</v>
       </c>
       <c r="H13" s="11">
@@ -2674,7 +2695,7 @@
         <v>0</v>
       </c>
       <c r="I13" s="10">
-        <f>COUNTIFS(Requerimientos!$C$6:$C$50,$A13,Requerimientos!$K$6:$K$50,"No")</f>
+        <f>COUNTIFS(Requerimientos!$C$6:$C$52,$A13,Requerimientos!$K$6:$K$52,"No")</f>
         <v>7</v>
       </c>
     </row>
@@ -2683,27 +2704,27 @@
         <v>95</v>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIF(Requerimientos!$C$6:$C$50,$A14)</f>
-        <v>11</v>
+        <f>COUNTIF(Requerimientos!$C$6:$C$52,$A14)</f>
+        <v>12</v>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS(Requerimientos!$C$6:$C$50,$A14,Requerimientos!$G$6:$G$50,"Alta")</f>
+        <f>COUNTIFS(Requerimientos!$C$6:$C$52,$A14,Requerimientos!$G$6:$G$52,"Alta")</f>
         <v>9</v>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS(Requerimientos!$C$6:$C$50,$A14,Requerimientos!$G$6:$G$50,"Media")</f>
-        <v>2</v>
+        <f>COUNTIFS(Requerimientos!$C$6:$C$52,$A14,Requerimientos!$G$6:$G$52,"Media")</f>
+        <v>3</v>
       </c>
       <c r="E14" s="13">
-        <f>COUNTIFS(Requerimientos!$C$6:$C$50,$A14,Requerimientos!$J$6:$J$50,"Pendiente")</f>
-        <v>11</v>
+        <f>COUNTIFS(Requerimientos!$C$6:$C$52,$A14,Requerimientos!$J$6:$J$52,"Pendiente")</f>
+        <v>12</v>
       </c>
       <c r="F14" s="13">
-        <f>COUNTIFS(Requerimientos!$C$6:$C$50,$A14,Requerimientos!$J$6:$J$50,"En progreso")</f>
+        <f>COUNTIFS(Requerimientos!$C$6:$C$52,$A14,Requerimientos!$J$6:$J$52,"En progreso")</f>
         <v>0</v>
       </c>
       <c r="G14" s="13">
-        <f>COUNTIFS(Requerimientos!$C$6:$C$50,$A14,Requerimientos!$J$6:$J$50,"Hecho")</f>
+        <f>COUNTIFS(Requerimientos!$C$6:$C$52,$A14,Requerimientos!$J$6:$J$52,"Hecho")</f>
         <v>0</v>
       </c>
       <c r="H14" s="14">
@@ -2711,8 +2732,8 @@
         <v>0</v>
       </c>
       <c r="I14" s="13">
-        <f>COUNTIFS(Requerimientos!$C$6:$C$50,$A14,Requerimientos!$K$6:$K$50,"No")</f>
-        <v>4</v>
+        <f>COUNTIFS(Requerimientos!$C$6:$C$52,$A14,Requerimientos!$K$6:$K$52,"No")</f>
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
@@ -2720,27 +2741,27 @@
         <v>96</v>
       </c>
       <c r="B15" s="10">
-        <f>COUNTIF(Requerimientos!$C$6:$C$50,$A15)</f>
+        <f>COUNTIF(Requerimientos!$C$6:$C$52,$A15)</f>
         <v>13</v>
       </c>
       <c r="C15" s="10">
-        <f>COUNTIFS(Requerimientos!$C$6:$C$50,$A15,Requerimientos!$G$6:$G$50,"Alta")</f>
+        <f>COUNTIFS(Requerimientos!$C$6:$C$52,$A15,Requerimientos!$G$6:$G$52,"Alta")</f>
         <v>12</v>
       </c>
       <c r="D15" s="10">
-        <f>COUNTIFS(Requerimientos!$C$6:$C$50,$A15,Requerimientos!$G$6:$G$50,"Media")</f>
+        <f>COUNTIFS(Requerimientos!$C$6:$C$52,$A15,Requerimientos!$G$6:$G$52,"Media")</f>
         <v>1</v>
       </c>
       <c r="E15" s="10">
-        <f>COUNTIFS(Requerimientos!$C$6:$C$50,$A15,Requerimientos!$J$6:$J$50,"Pendiente")</f>
+        <f>COUNTIFS(Requerimientos!$C$6:$C$52,$A15,Requerimientos!$J$6:$J$52,"Pendiente")</f>
         <v>13</v>
       </c>
       <c r="F15" s="10">
-        <f>COUNTIFS(Requerimientos!$C$6:$C$50,$A15,Requerimientos!$J$6:$J$50,"En progreso")</f>
+        <f>COUNTIFS(Requerimientos!$C$6:$C$52,$A15,Requerimientos!$J$6:$J$52,"En progreso")</f>
         <v>0</v>
       </c>
       <c r="G15" s="10">
-        <f>COUNTIFS(Requerimientos!$C$6:$C$50,$A15,Requerimientos!$J$6:$J$50,"Hecho")</f>
+        <f>COUNTIFS(Requerimientos!$C$6:$C$52,$A15,Requerimientos!$J$6:$J$52,"Hecho")</f>
         <v>0</v>
       </c>
       <c r="H15" s="11">
@@ -2748,7 +2769,7 @@
         <v>0</v>
       </c>
       <c r="I15" s="10">
-        <f>COUNTIFS(Requerimientos!$C$6:$C$50,$A15,Requerimientos!$K$6:$K$50,"No")</f>
+        <f>COUNTIFS(Requerimientos!$C$6:$C$52,$A15,Requerimientos!$K$6:$K$52,"No")</f>
         <v>0</v>
       </c>
     </row>
@@ -2758,19 +2779,19 @@
       </c>
       <c r="B16" s="16">
         <f t="shared" ref="B16:G16" si="1">SUM(B11:B15)</f>
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C16" s="16">
         <f t="shared" si="1"/>
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D16" s="16">
         <f t="shared" si="1"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E16" s="16">
         <f t="shared" si="1"/>
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F16" s="16">
         <f t="shared" si="1"/>
@@ -2786,7 +2807,7 @@
       </c>
       <c r="I16" s="16">
         <f>SUM(I11:I15)</f>
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -2856,27 +2877,27 @@
         <v>23</v>
       </c>
       <c r="D21" s="10">
-        <f>COUNTIF(Requerimientos!$H$6:$H$50,"*L3*")</f>
-        <v>30</v>
+        <f>COUNTIF(Requerimientos!$H$6:$H$52,"*L3*")</f>
+        <v>36</v>
       </c>
       <c r="E21" s="10">
-        <f>COUNTIF(Requerimientos!$I$6:$I$50,$A21)</f>
+        <f>COUNTIF(Requerimientos!$I$6:$I$52,$A21)</f>
         <v>1</v>
       </c>
       <c r="F21" s="10">
-        <f>COUNTIFS(Requerimientos!$I$6:$I$50,$A21,Requerimientos!$G$6:$G$50,"Alta")</f>
+        <f>COUNTIFS(Requerimientos!$I$6:$I$52,$A21,Requerimientos!$G$6:$G$52,"Alta")</f>
         <v>1</v>
       </c>
       <c r="G21" s="10">
-        <f>COUNTIFS(Requerimientos!$I$6:$I$50,$A21,Requerimientos!$J$6:$J$50,"Pendiente")</f>
+        <f>COUNTIFS(Requerimientos!$I$6:$I$52,$A21,Requerimientos!$J$6:$J$52,"Pendiente")</f>
         <v>1</v>
       </c>
       <c r="H21" s="11">
-        <f>IFERROR(COUNTIFS(Requerimientos!$I$6:$I$50,$A21,Requerimientos!$J$6:$J$50,"Hecho")/$E21,0)</f>
+        <f>IFERROR(COUNTIFS(Requerimientos!$I$6:$I$52,$A21,Requerimientos!$J$6:$J$52,"Hecho")/$E21,0)</f>
         <v>0</v>
       </c>
       <c r="I21" s="10">
-        <f>COUNTIFS(Requerimientos!$I$6:$I$50,$A21,Requerimientos!$K$6:$K$50,"No")</f>
+        <f>COUNTIFS(Requerimientos!$I$6:$I$52,$A21,Requerimientos!$K$6:$K$52,"No")</f>
         <v>0</v>
       </c>
     </row>
@@ -2892,27 +2913,27 @@
         <v>37</v>
       </c>
       <c r="D22" s="13">
-        <f>COUNTIF(Requerimientos!$H$6:$H$50,"*L4*")</f>
-        <v>13</v>
+        <f>COUNTIF(Requerimientos!$H$6:$H$52,"*L4*")</f>
+        <v>15</v>
       </c>
       <c r="E22" s="13">
-        <f>COUNTIF(Requerimientos!$I$6:$I$50,$A22)</f>
+        <f>COUNTIF(Requerimientos!$I$6:$I$52,$A22)</f>
         <v>0</v>
       </c>
       <c r="F22" s="13">
-        <f>COUNTIFS(Requerimientos!$I$6:$I$50,$A22,Requerimientos!$G$6:$G$50,"Alta")</f>
+        <f>COUNTIFS(Requerimientos!$I$6:$I$52,$A22,Requerimientos!$G$6:$G$52,"Alta")</f>
         <v>0</v>
       </c>
       <c r="G22" s="13">
-        <f>COUNTIFS(Requerimientos!$I$6:$I$50,$A22,Requerimientos!$J$6:$J$50,"Pendiente")</f>
+        <f>COUNTIFS(Requerimientos!$I$6:$I$52,$A22,Requerimientos!$J$6:$J$52,"Pendiente")</f>
         <v>0</v>
       </c>
       <c r="H22" s="14">
-        <f>IFERROR(COUNTIFS(Requerimientos!$I$6:$I$50,$A22,Requerimientos!$J$6:$J$50,"Hecho")/$E22,0)</f>
+        <f>IFERROR(COUNTIFS(Requerimientos!$I$6:$I$52,$A22,Requerimientos!$J$6:$J$52,"Hecho")/$E22,0)</f>
         <v>0</v>
       </c>
       <c r="I22" s="13">
-        <f>COUNTIFS(Requerimientos!$I$6:$I$50,$A22,Requerimientos!$K$6:$K$50,"No")</f>
+        <f>COUNTIFS(Requerimientos!$I$6:$I$52,$A22,Requerimientos!$K$6:$K$52,"No")</f>
         <v>0</v>
       </c>
     </row>
@@ -2928,27 +2949,27 @@
         <v>58</v>
       </c>
       <c r="D23" s="10">
-        <f>COUNTIF(Requerimientos!$H$6:$H$50,"*L5*")</f>
+        <f>COUNTIF(Requerimientos!$H$6:$H$52,"*L5*")</f>
         <v>6</v>
       </c>
       <c r="E23" s="10">
-        <f>COUNTIF(Requerimientos!$I$6:$I$50,$A23)</f>
+        <f>COUNTIF(Requerimientos!$I$6:$I$52,$A23)</f>
         <v>0</v>
       </c>
       <c r="F23" s="10">
-        <f>COUNTIFS(Requerimientos!$I$6:$I$50,$A23,Requerimientos!$G$6:$G$50,"Alta")</f>
+        <f>COUNTIFS(Requerimientos!$I$6:$I$52,$A23,Requerimientos!$G$6:$G$52,"Alta")</f>
         <v>0</v>
       </c>
       <c r="G23" s="10">
-        <f>COUNTIFS(Requerimientos!$I$6:$I$50,$A23,Requerimientos!$J$6:$J$50,"Pendiente")</f>
+        <f>COUNTIFS(Requerimientos!$I$6:$I$52,$A23,Requerimientos!$J$6:$J$52,"Pendiente")</f>
         <v>0</v>
       </c>
       <c r="H23" s="11">
-        <f>IFERROR(COUNTIFS(Requerimientos!$I$6:$I$50,$A23,Requerimientos!$J$6:$J$50,"Hecho")/$E23,0)</f>
+        <f>IFERROR(COUNTIFS(Requerimientos!$I$6:$I$52,$A23,Requerimientos!$J$6:$J$52,"Hecho")/$E23,0)</f>
         <v>0</v>
       </c>
       <c r="I23" s="10">
-        <f>COUNTIFS(Requerimientos!$I$6:$I$50,$A23,Requerimientos!$K$6:$K$50,"No")</f>
+        <f>COUNTIFS(Requerimientos!$I$6:$I$52,$A23,Requerimientos!$K$6:$K$52,"No")</f>
         <v>0</v>
       </c>
     </row>
@@ -2964,28 +2985,28 @@
         <v>72</v>
       </c>
       <c r="D24" s="13">
-        <f>COUNTIF(Requerimientos!$H$6:$H$50,"*L6*")</f>
-        <v>36</v>
+        <f>COUNTIF(Requerimientos!$H$6:$H$52,"*L6*")</f>
+        <v>38</v>
       </c>
       <c r="E24" s="13">
-        <f>COUNTIF(Requerimientos!$I$6:$I$50,$A24)</f>
-        <v>31</v>
+        <f>COUNTIF(Requerimientos!$I$6:$I$52,$A24)</f>
+        <v>33</v>
       </c>
       <c r="F24" s="13">
-        <f>COUNTIFS(Requerimientos!$I$6:$I$50,$A24,Requerimientos!$G$6:$G$50,"Alta")</f>
-        <v>25</v>
+        <f>COUNTIFS(Requerimientos!$I$6:$I$52,$A24,Requerimientos!$G$6:$G$52,"Alta")</f>
+        <v>26</v>
       </c>
       <c r="G24" s="13">
-        <f>COUNTIFS(Requerimientos!$I$6:$I$50,$A24,Requerimientos!$J$6:$J$50,"Pendiente")</f>
-        <v>31</v>
+        <f>COUNTIFS(Requerimientos!$I$6:$I$52,$A24,Requerimientos!$J$6:$J$52,"Pendiente")</f>
+        <v>33</v>
       </c>
       <c r="H24" s="14">
-        <f>IFERROR(COUNTIFS(Requerimientos!$I$6:$I$50,$A24,Requerimientos!$J$6:$J$50,"Hecho")/$E24,0)</f>
+        <f>IFERROR(COUNTIFS(Requerimientos!$I$6:$I$52,$A24,Requerimientos!$J$6:$J$52,"Hecho")/$E24,0)</f>
         <v>0</v>
       </c>
       <c r="I24" s="13">
-        <f>COUNTIFS(Requerimientos!$I$6:$I$50,$A24,Requerimientos!$K$6:$K$50,"No")</f>
-        <v>8</v>
+        <f>COUNTIFS(Requerimientos!$I$6:$I$52,$A24,Requerimientos!$K$6:$K$52,"No")</f>
+        <v>10</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
@@ -3000,27 +3021,27 @@
         <v>113</v>
       </c>
       <c r="D25" s="10">
-        <f>COUNTIF(Requerimientos!$H$6:$H$50,"*L7*")</f>
+        <f>COUNTIF(Requerimientos!$H$6:$H$52,"*L7*")</f>
         <v>11</v>
       </c>
       <c r="E25" s="10">
-        <f>COUNTIF(Requerimientos!$I$6:$I$50,$A25)</f>
+        <f>COUNTIF(Requerimientos!$I$6:$I$52,$A25)</f>
         <v>10</v>
       </c>
       <c r="F25" s="10">
-        <f>COUNTIFS(Requerimientos!$I$6:$I$50,$A25,Requerimientos!$G$6:$G$50,"Alta")</f>
+        <f>COUNTIFS(Requerimientos!$I$6:$I$52,$A25,Requerimientos!$G$6:$G$52,"Alta")</f>
         <v>8</v>
       </c>
       <c r="G25" s="10">
-        <f>COUNTIFS(Requerimientos!$I$6:$I$50,$A25,Requerimientos!$J$6:$J$50,"Pendiente")</f>
+        <f>COUNTIFS(Requerimientos!$I$6:$I$52,$A25,Requerimientos!$J$6:$J$52,"Pendiente")</f>
         <v>10</v>
       </c>
       <c r="H25" s="11">
-        <f>IFERROR(COUNTIFS(Requerimientos!$I$6:$I$50,$A25,Requerimientos!$J$6:$J$50,"Hecho")/$E25,0)</f>
+        <f>IFERROR(COUNTIFS(Requerimientos!$I$6:$I$52,$A25,Requerimientos!$J$6:$J$52,"Hecho")/$E25,0)</f>
         <v>0</v>
       </c>
       <c r="I25" s="10">
-        <f>COUNTIFS(Requerimientos!$I$6:$I$50,$A25,Requerimientos!$K$6:$K$50,"No")</f>
+        <f>COUNTIFS(Requerimientos!$I$6:$I$52,$A25,Requerimientos!$K$6:$K$52,"No")</f>
         <v>7</v>
       </c>
     </row>
@@ -3035,27 +3056,27 @@
         <v>111</v>
       </c>
       <c r="D26" s="13">
-        <f>COUNTIF(Requerimientos!$H$6:$H$50,"*Web*")</f>
+        <f>COUNTIF(Requerimientos!$H$6:$H$52,"*Web*")</f>
         <v>3</v>
       </c>
       <c r="E26" s="13">
-        <f>COUNTIF(Requerimientos!$I$6:$I$50,$A26)</f>
+        <f>COUNTIF(Requerimientos!$I$6:$I$52,$A26)</f>
         <v>3</v>
       </c>
       <c r="F26" s="13">
-        <f>COUNTIFS(Requerimientos!$I$6:$I$50,$A26,Requerimientos!$G$6:$G$50,"Alta")</f>
+        <f>COUNTIFS(Requerimientos!$I$6:$I$52,$A26,Requerimientos!$G$6:$G$52,"Alta")</f>
         <v>3</v>
       </c>
       <c r="G26" s="13">
-        <f>COUNTIFS(Requerimientos!$I$6:$I$50,$A26,Requerimientos!$J$6:$J$50,"Pendiente")</f>
+        <f>COUNTIFS(Requerimientos!$I$6:$I$52,$A26,Requerimientos!$J$6:$J$52,"Pendiente")</f>
         <v>3</v>
       </c>
       <c r="H26" s="14">
-        <f>IFERROR(COUNTIFS(Requerimientos!$I$6:$I$50,$A26,Requerimientos!$J$6:$J$50,"Hecho")/$E26,0)</f>
+        <f>IFERROR(COUNTIFS(Requerimientos!$I$6:$I$52,$A26,Requerimientos!$J$6:$J$52,"Hecho")/$E26,0)</f>
         <v>0</v>
       </c>
       <c r="I26" s="13">
-        <f>COUNTIFS(Requerimientos!$I$6:$I$50,$A26,Requerimientos!$K$6:$K$50,"No")</f>
+        <f>COUNTIFS(Requerimientos!$I$6:$I$52,$A26,Requerimientos!$K$6:$K$52,"No")</f>
         <v>2</v>
       </c>
     </row>
@@ -3100,19 +3121,19 @@
         <v>113</v>
       </c>
       <c r="B30" s="13">
-        <f>COUNTIF(Requerimientos!$B$6:$B$50,$A30)</f>
+        <f>COUNTIF(Requerimientos!$B$6:$B$52,$A30)</f>
         <v>4</v>
       </c>
       <c r="C30" s="13">
-        <f>COUNTIFS(Requerimientos!$B$6:$B$50,$A30,Requerimientos!$G$6:$G$50,"Alta")</f>
+        <f>COUNTIFS(Requerimientos!$B$6:$B$52,$A30,Requerimientos!$G$6:$G$52,"Alta")</f>
         <v>4</v>
       </c>
       <c r="D30" s="13">
-        <f>COUNTIFS(Requerimientos!$B$6:$B$50,$A30,Requerimientos!$J$6:$J$50,"Pendiente")</f>
+        <f>COUNTIFS(Requerimientos!$B$6:$B$52,$A30,Requerimientos!$J$6:$J$52,"Pendiente")</f>
         <v>4</v>
       </c>
       <c r="E30" s="13">
-        <f>COUNTIFS(Requerimientos!$B$6:$B$50,$A30,Requerimientos!$J$6:$J$50,"Hecho")</f>
+        <f>COUNTIFS(Requerimientos!$B$6:$B$52,$A30,Requerimientos!$J$6:$J$52,"Hecho")</f>
         <v>0</v>
       </c>
       <c r="F30" s="14">
@@ -3125,19 +3146,19 @@
         <v>114</v>
       </c>
       <c r="B31" s="10">
-        <f>COUNTIF(Requerimientos!$B$6:$B$50,$A31)</f>
+        <f>COUNTIF(Requerimientos!$B$6:$B$52,$A31)</f>
         <v>3</v>
       </c>
       <c r="C31" s="10">
-        <f>COUNTIFS(Requerimientos!$B$6:$B$50,$A31,Requerimientos!$G$6:$G$50,"Alta")</f>
+        <f>COUNTIFS(Requerimientos!$B$6:$B$52,$A31,Requerimientos!$G$6:$G$52,"Alta")</f>
         <v>3</v>
       </c>
       <c r="D31" s="10">
-        <f>COUNTIFS(Requerimientos!$B$6:$B$50,$A31,Requerimientos!$J$6:$J$50,"Pendiente")</f>
+        <f>COUNTIFS(Requerimientos!$B$6:$B$52,$A31,Requerimientos!$J$6:$J$52,"Pendiente")</f>
         <v>3</v>
       </c>
       <c r="E31" s="10">
-        <f>COUNTIFS(Requerimientos!$B$6:$B$50,$A31,Requerimientos!$J$6:$J$50,"Hecho")</f>
+        <f>COUNTIFS(Requerimientos!$B$6:$B$52,$A31,Requerimientos!$J$6:$J$52,"Hecho")</f>
         <v>0</v>
       </c>
       <c r="F31" s="11">
@@ -3150,19 +3171,19 @@
         <v>115</v>
       </c>
       <c r="B32" s="13">
-        <f>COUNTIF(Requerimientos!$B$6:$B$50,$A32)</f>
+        <f>COUNTIF(Requerimientos!$B$6:$B$52,$A32)</f>
+        <v>6</v>
+      </c>
+      <c r="C32" s="13">
+        <f>COUNTIFS(Requerimientos!$B$6:$B$52,$A32,Requerimientos!$G$6:$G$52,"Alta")</f>
         <v>5</v>
       </c>
-      <c r="C32" s="13">
-        <f>COUNTIFS(Requerimientos!$B$6:$B$50,$A32,Requerimientos!$G$6:$G$50,"Alta")</f>
-        <v>5</v>
-      </c>
       <c r="D32" s="13">
-        <f>COUNTIFS(Requerimientos!$B$6:$B$50,$A32,Requerimientos!$J$6:$J$50,"Pendiente")</f>
-        <v>5</v>
+        <f>COUNTIFS(Requerimientos!$B$6:$B$52,$A32,Requerimientos!$J$6:$J$52,"Pendiente")</f>
+        <v>6</v>
       </c>
       <c r="E32" s="13">
-        <f>COUNTIFS(Requerimientos!$B$6:$B$50,$A32,Requerimientos!$J$6:$J$50,"Hecho")</f>
+        <f>COUNTIFS(Requerimientos!$B$6:$B$52,$A32,Requerimientos!$J$6:$J$52,"Hecho")</f>
         <v>0</v>
       </c>
       <c r="F32" s="14">
@@ -3175,19 +3196,19 @@
         <v>116</v>
       </c>
       <c r="B33" s="10">
-        <f>COUNTIF(Requerimientos!$B$6:$B$50,$A33)</f>
+        <f>COUNTIF(Requerimientos!$B$6:$B$52,$A33)</f>
         <v>4</v>
       </c>
       <c r="C33" s="10">
-        <f>COUNTIFS(Requerimientos!$B$6:$B$50,$A33,Requerimientos!$G$6:$G$50,"Alta")</f>
+        <f>COUNTIFS(Requerimientos!$B$6:$B$52,$A33,Requerimientos!$G$6:$G$52,"Alta")</f>
         <v>3</v>
       </c>
       <c r="D33" s="10">
-        <f>COUNTIFS(Requerimientos!$B$6:$B$50,$A33,Requerimientos!$J$6:$J$50,"Pendiente")</f>
+        <f>COUNTIFS(Requerimientos!$B$6:$B$52,$A33,Requerimientos!$J$6:$J$52,"Pendiente")</f>
         <v>4</v>
       </c>
       <c r="E33" s="10">
-        <f>COUNTIFS(Requerimientos!$B$6:$B$50,$A33,Requerimientos!$J$6:$J$50,"Hecho")</f>
+        <f>COUNTIFS(Requerimientos!$B$6:$B$52,$A33,Requerimientos!$J$6:$J$52,"Hecho")</f>
         <v>0</v>
       </c>
       <c r="F33" s="11">
@@ -3200,19 +3221,19 @@
         <v>117</v>
       </c>
       <c r="B34" s="13">
-        <f>COUNTIF(Requerimientos!$B$6:$B$50,$A34)</f>
+        <f>COUNTIF(Requerimientos!$B$6:$B$52,$A34)</f>
         <v>3</v>
       </c>
       <c r="C34" s="13">
-        <f>COUNTIFS(Requerimientos!$B$6:$B$50,$A34,Requerimientos!$G$6:$G$50,"Alta")</f>
+        <f>COUNTIFS(Requerimientos!$B$6:$B$52,$A34,Requerimientos!$G$6:$G$52,"Alta")</f>
         <v>2</v>
       </c>
       <c r="D34" s="13">
-        <f>COUNTIFS(Requerimientos!$B$6:$B$50,$A34,Requerimientos!$J$6:$J$50,"Pendiente")</f>
+        <f>COUNTIFS(Requerimientos!$B$6:$B$52,$A34,Requerimientos!$J$6:$J$52,"Pendiente")</f>
         <v>3</v>
       </c>
       <c r="E34" s="13">
-        <f>COUNTIFS(Requerimientos!$B$6:$B$50,$A34,Requerimientos!$J$6:$J$50,"Hecho")</f>
+        <f>COUNTIFS(Requerimientos!$B$6:$B$52,$A34,Requerimientos!$J$6:$J$52,"Hecho")</f>
         <v>0</v>
       </c>
       <c r="F34" s="14">
@@ -3225,19 +3246,19 @@
         <v>118</v>
       </c>
       <c r="B35" s="10">
-        <f>COUNTIF(Requerimientos!$B$6:$B$50,$A35)</f>
+        <f>COUNTIF(Requerimientos!$B$6:$B$52,$A35)</f>
         <v>1</v>
       </c>
       <c r="C35" s="10">
-        <f>COUNTIFS(Requerimientos!$B$6:$B$50,$A35,Requerimientos!$G$6:$G$50,"Alta")</f>
+        <f>COUNTIFS(Requerimientos!$B$6:$B$52,$A35,Requerimientos!$G$6:$G$52,"Alta")</f>
         <v>1</v>
       </c>
       <c r="D35" s="10">
-        <f>COUNTIFS(Requerimientos!$B$6:$B$50,$A35,Requerimientos!$J$6:$J$50,"Pendiente")</f>
+        <f>COUNTIFS(Requerimientos!$B$6:$B$52,$A35,Requerimientos!$J$6:$J$52,"Pendiente")</f>
         <v>1</v>
       </c>
       <c r="E35" s="10">
-        <f>COUNTIFS(Requerimientos!$B$6:$B$50,$A35,Requerimientos!$J$6:$J$50,"Hecho")</f>
+        <f>COUNTIFS(Requerimientos!$B$6:$B$52,$A35,Requerimientos!$J$6:$J$52,"Hecho")</f>
         <v>0</v>
       </c>
       <c r="F35" s="11">
@@ -3250,19 +3271,19 @@
         <v>119</v>
       </c>
       <c r="B36" s="13">
-        <f>COUNTIF(Requerimientos!$B$6:$B$50,$A36)</f>
+        <f>COUNTIF(Requerimientos!$B$6:$B$52,$A36)</f>
         <v>3</v>
       </c>
       <c r="C36" s="13">
-        <f>COUNTIFS(Requerimientos!$B$6:$B$50,$A36,Requerimientos!$G$6:$G$50,"Alta")</f>
+        <f>COUNTIFS(Requerimientos!$B$6:$B$52,$A36,Requerimientos!$G$6:$G$52,"Alta")</f>
         <v>3</v>
       </c>
       <c r="D36" s="13">
-        <f>COUNTIFS(Requerimientos!$B$6:$B$50,$A36,Requerimientos!$J$6:$J$50,"Pendiente")</f>
+        <f>COUNTIFS(Requerimientos!$B$6:$B$52,$A36,Requerimientos!$J$6:$J$52,"Pendiente")</f>
         <v>3</v>
       </c>
       <c r="E36" s="13">
-        <f>COUNTIFS(Requerimientos!$B$6:$B$50,$A36,Requerimientos!$J$6:$J$50,"Hecho")</f>
+        <f>COUNTIFS(Requerimientos!$B$6:$B$52,$A36,Requerimientos!$J$6:$J$52,"Hecho")</f>
         <v>0</v>
       </c>
       <c r="F36" s="14">
@@ -3275,19 +3296,19 @@
         <v>120</v>
       </c>
       <c r="B37" s="10">
-        <f>COUNTIF(Requerimientos!$B$6:$B$50,$A37)</f>
-        <v>10</v>
+        <f>COUNTIF(Requerimientos!$B$6:$B$52,$A37)</f>
+        <v>11</v>
       </c>
       <c r="C37" s="10">
-        <f>COUNTIFS(Requerimientos!$B$6:$B$50,$A37,Requerimientos!$G$6:$G$50,"Alta")</f>
-        <v>8</v>
+        <f>COUNTIFS(Requerimientos!$B$6:$B$52,$A37,Requerimientos!$G$6:$G$52,"Alta")</f>
+        <v>9</v>
       </c>
       <c r="D37" s="10">
-        <f>COUNTIFS(Requerimientos!$B$6:$B$50,$A37,Requerimientos!$J$6:$J$50,"Pendiente")</f>
-        <v>10</v>
+        <f>COUNTIFS(Requerimientos!$B$6:$B$52,$A37,Requerimientos!$J$6:$J$52,"Pendiente")</f>
+        <v>11</v>
       </c>
       <c r="E37" s="10">
-        <f>COUNTIFS(Requerimientos!$B$6:$B$50,$A37,Requerimientos!$J$6:$J$50,"Hecho")</f>
+        <f>COUNTIFS(Requerimientos!$B$6:$B$52,$A37,Requerimientos!$J$6:$J$52,"Hecho")</f>
         <v>0</v>
       </c>
       <c r="F37" s="11">
@@ -3300,19 +3321,19 @@
         <v>121</v>
       </c>
       <c r="B38" s="13">
-        <f>COUNTIF(Requerimientos!$B$6:$B$50,$A38)</f>
+        <f>COUNTIF(Requerimientos!$B$6:$B$52,$A38)</f>
         <v>3</v>
       </c>
       <c r="C38" s="13">
-        <f>COUNTIFS(Requerimientos!$B$6:$B$50,$A38,Requerimientos!$G$6:$G$50,"Alta")</f>
+        <f>COUNTIFS(Requerimientos!$B$6:$B$52,$A38,Requerimientos!$G$6:$G$52,"Alta")</f>
         <v>0</v>
       </c>
       <c r="D38" s="13">
-        <f>COUNTIFS(Requerimientos!$B$6:$B$50,$A38,Requerimientos!$J$6:$J$50,"Pendiente")</f>
+        <f>COUNTIFS(Requerimientos!$B$6:$B$52,$A38,Requerimientos!$J$6:$J$52,"Pendiente")</f>
         <v>3</v>
       </c>
       <c r="E38" s="13">
-        <f>COUNTIFS(Requerimientos!$B$6:$B$50,$A38,Requerimientos!$J$6:$J$50,"Hecho")</f>
+        <f>COUNTIFS(Requerimientos!$B$6:$B$52,$A38,Requerimientos!$J$6:$J$52,"Hecho")</f>
         <v>0</v>
       </c>
       <c r="F38" s="14">
@@ -3325,19 +3346,19 @@
         <v>122</v>
       </c>
       <c r="B39" s="10">
-        <f>COUNTIF(Requerimientos!$B$6:$B$50,$A39)</f>
+        <f>COUNTIF(Requerimientos!$B$6:$B$52,$A39)</f>
         <v>9</v>
       </c>
       <c r="C39" s="10">
-        <f>COUNTIFS(Requerimientos!$B$6:$B$50,$A39,Requerimientos!$G$6:$G$50,"Alta")</f>
+        <f>COUNTIFS(Requerimientos!$B$6:$B$52,$A39,Requerimientos!$G$6:$G$52,"Alta")</f>
         <v>8</v>
       </c>
       <c r="D39" s="10">
-        <f>COUNTIFS(Requerimientos!$B$6:$B$50,$A39,Requerimientos!$J$6:$J$50,"Pendiente")</f>
+        <f>COUNTIFS(Requerimientos!$B$6:$B$52,$A39,Requerimientos!$J$6:$J$52,"Pendiente")</f>
         <v>9</v>
       </c>
       <c r="E39" s="10">
-        <f>COUNTIFS(Requerimientos!$B$6:$B$50,$A39,Requerimientos!$J$6:$J$50,"Hecho")</f>
+        <f>COUNTIFS(Requerimientos!$B$6:$B$52,$A39,Requerimientos!$J$6:$J$52,"Hecho")</f>
         <v>0</v>
       </c>
       <c r="F39" s="11">
@@ -3384,7 +3405,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M50"/>
+  <dimension ref="A1:M52"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
@@ -3871,7 +3892,7 @@
         <v>164</v>
       </c>
       <c r="B16" s="23" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="C16" s="24" t="s">
         <v>93</v>
@@ -3886,7 +3907,7 @@
         <v>166</v>
       </c>
       <c r="G16" s="24" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H16" s="25" t="s">
         <v>167</v>
@@ -3898,17 +3919,19 @@
         <v>88</v>
       </c>
       <c r="K16" s="24" t="s">
-        <v>149</v>
+        <v>131</v>
       </c>
       <c r="L16" s="23"/>
-      <c r="M16" s="23"/>
+      <c r="M16" s="23" t="s">
+        <v>168</v>
+      </c>
     </row>
     <row r="17" spans="1:13" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="22" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B17" s="23" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="C17" s="24" t="s">
         <v>93</v>
@@ -3917,16 +3940,16 @@
         <v>127</v>
       </c>
       <c r="E17" s="23" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F17" s="23" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G17" s="24" t="s">
         <v>87</v>
       </c>
       <c r="H17" s="25" t="s">
-        <v>130</v>
+        <v>167</v>
       </c>
       <c r="I17" s="24" t="s">
         <v>107</v>
@@ -3935,19 +3958,17 @@
         <v>88</v>
       </c>
       <c r="K17" s="24" t="s">
-        <v>171</v>
+        <v>149</v>
       </c>
       <c r="L17" s="23"/>
-      <c r="M17" s="23" t="s">
-        <v>172</v>
-      </c>
+      <c r="M17" s="23"/>
     </row>
     <row r="18" spans="1:13" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="22" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B18" s="23" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="C18" s="24" t="s">
         <v>93</v>
@@ -3956,37 +3977,37 @@
         <v>127</v>
       </c>
       <c r="E18" s="23" t="s">
+        <v>173</v>
+      </c>
+      <c r="F18" s="23" t="s">
         <v>174</v>
       </c>
-      <c r="F18" s="23" t="s">
-        <v>175</v>
-      </c>
       <c r="G18" s="24" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H18" s="25" t="s">
-        <v>176</v>
+        <v>130</v>
       </c>
       <c r="I18" s="24" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="J18" s="24" t="s">
         <v>88</v>
       </c>
       <c r="K18" s="24" t="s">
-        <v>131</v>
+        <v>175</v>
       </c>
       <c r="L18" s="23"/>
       <c r="M18" s="23" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="19" spans="1:13" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="22" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B19" s="23" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="C19" s="24" t="s">
         <v>93</v>
@@ -3995,16 +4016,16 @@
         <v>127</v>
       </c>
       <c r="E19" s="23" t="s">
+        <v>178</v>
+      </c>
+      <c r="F19" s="23" t="s">
         <v>179</v>
       </c>
-      <c r="F19" s="23" t="s">
+      <c r="G19" s="24" t="s">
+        <v>86</v>
+      </c>
+      <c r="H19" s="25" t="s">
         <v>180</v>
-      </c>
-      <c r="G19" s="24" t="s">
-        <v>87</v>
-      </c>
-      <c r="H19" s="25" t="s">
-        <v>176</v>
       </c>
       <c r="I19" s="24" t="s">
         <v>108</v>
@@ -4013,54 +4034,56 @@
         <v>88</v>
       </c>
       <c r="K19" s="24" t="s">
-        <v>149</v>
+        <v>131</v>
       </c>
       <c r="L19" s="23"/>
-      <c r="M19" s="23"/>
+      <c r="M19" s="23" t="s">
+        <v>181</v>
+      </c>
     </row>
     <row r="20" spans="1:13" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="22" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B20" s="23" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="C20" s="24" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D20" s="24" t="s">
         <v>127</v>
       </c>
       <c r="E20" s="23" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F20" s="23" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="G20" s="24" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H20" s="25" t="s">
-        <v>160</v>
+        <v>180</v>
       </c>
       <c r="I20" s="24" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="J20" s="24" t="s">
         <v>88</v>
       </c>
       <c r="K20" s="24" t="s">
-        <v>131</v>
+        <v>149</v>
       </c>
       <c r="L20" s="23"/>
       <c r="M20" s="23"/>
     </row>
     <row r="21" spans="1:13" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="22" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B21" s="23" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="C21" s="24" t="s">
         <v>94</v>
@@ -4069,16 +4092,16 @@
         <v>127</v>
       </c>
       <c r="E21" s="23" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F21" s="23" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="G21" s="24" t="s">
         <v>86</v>
       </c>
       <c r="H21" s="25" t="s">
-        <v>148</v>
+        <v>160</v>
       </c>
       <c r="I21" s="24" t="s">
         <v>107</v>
@@ -4094,7 +4117,7 @@
     </row>
     <row r="22" spans="1:13" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="22" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B22" s="23" t="s">
         <v>120</v>
@@ -4106,16 +4129,16 @@
         <v>127</v>
       </c>
       <c r="E22" s="23" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F22" s="23" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="G22" s="24" t="s">
         <v>86</v>
       </c>
       <c r="H22" s="25" t="s">
-        <v>167</v>
+        <v>148</v>
       </c>
       <c r="I22" s="24" t="s">
         <v>107</v>
@@ -4127,9 +4150,7 @@
         <v>131</v>
       </c>
       <c r="L22" s="23"/>
-      <c r="M22" s="23" t="s">
-        <v>190</v>
-      </c>
+      <c r="M22" s="23"/>
     </row>
     <row r="23" spans="1:13" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="22" t="s">
@@ -4166,11 +4187,13 @@
         <v>131</v>
       </c>
       <c r="L23" s="23"/>
-      <c r="M23" s="23"/>
+      <c r="M23" s="23" t="s">
+        <v>194</v>
+      </c>
     </row>
     <row r="24" spans="1:13" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="22" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B24" s="23" t="s">
         <v>120</v>
@@ -4182,19 +4205,19 @@
         <v>127</v>
       </c>
       <c r="E24" s="23" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F24" s="23" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="G24" s="24" t="s">
         <v>86</v>
       </c>
       <c r="H24" s="25" t="s">
-        <v>197</v>
+        <v>167</v>
       </c>
       <c r="I24" s="24" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="J24" s="24" t="s">
         <v>88</v>
@@ -4203,13 +4226,11 @@
         <v>131</v>
       </c>
       <c r="L24" s="23"/>
-      <c r="M24" s="23" t="s">
-        <v>198</v>
-      </c>
+      <c r="M24" s="23"/>
     </row>
     <row r="25" spans="1:13" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="22" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B25" s="23" t="s">
         <v>120</v>
@@ -4221,16 +4242,16 @@
         <v>127</v>
       </c>
       <c r="E25" s="23" t="s">
+        <v>199</v>
+      </c>
+      <c r="F25" s="23" t="s">
         <v>200</v>
-      </c>
-      <c r="F25" s="23" t="s">
-        <v>201</v>
       </c>
       <c r="G25" s="24" t="s">
         <v>86</v>
       </c>
       <c r="H25" s="25" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="I25" s="24" t="s">
         <v>108</v>
@@ -4243,15 +4264,15 @@
       </c>
       <c r="L25" s="23"/>
       <c r="M25" s="23" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="26" spans="1:13" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="22" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B26" s="23" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="C26" s="24" t="s">
         <v>94</v>
@@ -4260,19 +4281,19 @@
         <v>127</v>
       </c>
       <c r="E26" s="23" t="s">
+        <v>204</v>
+      </c>
+      <c r="F26" s="23" t="s">
         <v>205</v>
-      </c>
-      <c r="F26" s="23" t="s">
-        <v>206</v>
       </c>
       <c r="G26" s="24" t="s">
         <v>86</v>
       </c>
       <c r="H26" s="25" t="s">
-        <v>144</v>
+        <v>206</v>
       </c>
       <c r="I26" s="24" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="J26" s="24" t="s">
         <v>88</v>
@@ -4281,53 +4302,53 @@
         <v>131</v>
       </c>
       <c r="L26" s="23"/>
-      <c r="M26" s="23"/>
+      <c r="M26" s="23" t="s">
+        <v>207</v>
+      </c>
     </row>
     <row r="27" spans="1:13" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="22" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B27" s="23" t="s">
         <v>113</v>
       </c>
       <c r="C27" s="24" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D27" s="24" t="s">
         <v>127</v>
       </c>
       <c r="E27" s="23" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F27" s="23" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="G27" s="24" t="s">
         <v>86</v>
       </c>
       <c r="H27" s="25" t="s">
-        <v>160</v>
+        <v>144</v>
       </c>
       <c r="I27" s="24" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="J27" s="24" t="s">
         <v>88</v>
       </c>
       <c r="K27" s="24" t="s">
-        <v>171</v>
+        <v>131</v>
       </c>
       <c r="L27" s="23"/>
-      <c r="M27" s="23" t="s">
-        <v>210</v>
-      </c>
+      <c r="M27" s="23"/>
     </row>
     <row r="28" spans="1:13" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="22" t="s">
         <v>211</v>
       </c>
       <c r="B28" s="23" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C28" s="24" t="s">
         <v>95</v>
@@ -4345,7 +4366,7 @@
         <v>86</v>
       </c>
       <c r="H28" s="25" t="s">
-        <v>130</v>
+        <v>160</v>
       </c>
       <c r="I28" s="24" t="s">
         <v>107</v>
@@ -4354,17 +4375,19 @@
         <v>88</v>
       </c>
       <c r="K28" s="24" t="s">
-        <v>149</v>
+        <v>175</v>
       </c>
       <c r="L28" s="23"/>
-      <c r="M28" s="23"/>
+      <c r="M28" s="23" t="s">
+        <v>214</v>
+      </c>
     </row>
     <row r="29" spans="1:13" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="22" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B29" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C29" s="24" t="s">
         <v>95</v>
@@ -4373,16 +4396,16 @@
         <v>127</v>
       </c>
       <c r="E29" s="23" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F29" s="23" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="G29" s="24" t="s">
         <v>86</v>
       </c>
       <c r="H29" s="25" t="s">
-        <v>167</v>
+        <v>130</v>
       </c>
       <c r="I29" s="24" t="s">
         <v>107</v>
@@ -4398,10 +4421,10 @@
     </row>
     <row r="30" spans="1:13" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="22" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B30" s="23" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C30" s="24" t="s">
         <v>95</v>
@@ -4410,10 +4433,10 @@
         <v>127</v>
       </c>
       <c r="E30" s="23" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F30" s="23" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G30" s="24" t="s">
         <v>86</v>
@@ -4435,10 +4458,10 @@
     </row>
     <row r="31" spans="1:13" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="22" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B31" s="23" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C31" s="24" t="s">
         <v>95</v>
@@ -4447,16 +4470,16 @@
         <v>127</v>
       </c>
       <c r="E31" s="23" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F31" s="23" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="G31" s="24" t="s">
         <v>86</v>
       </c>
       <c r="H31" s="25" t="s">
-        <v>223</v>
+        <v>167</v>
       </c>
       <c r="I31" s="24" t="s">
         <v>107</v>
@@ -4465,19 +4488,17 @@
         <v>88</v>
       </c>
       <c r="K31" s="24" t="s">
-        <v>171</v>
+        <v>149</v>
       </c>
       <c r="L31" s="23"/>
-      <c r="M31" s="23" t="s">
-        <v>224</v>
-      </c>
+      <c r="M31" s="23"/>
     </row>
     <row r="32" spans="1:13" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="22" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B32" s="23" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C32" s="24" t="s">
         <v>95</v>
@@ -4486,16 +4507,16 @@
         <v>127</v>
       </c>
       <c r="E32" s="23" t="s">
+        <v>225</v>
+      </c>
+      <c r="F32" s="23" t="s">
         <v>226</v>
-      </c>
-      <c r="F32" s="23" t="s">
-        <v>227</v>
       </c>
       <c r="G32" s="24" t="s">
         <v>86</v>
       </c>
       <c r="H32" s="25" t="s">
-        <v>130</v>
+        <v>160</v>
       </c>
       <c r="I32" s="24" t="s">
         <v>107</v>
@@ -4504,19 +4525,19 @@
         <v>88</v>
       </c>
       <c r="K32" s="24" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="L32" s="23"/>
       <c r="M32" s="23" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="33" spans="1:13" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="22" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B33" s="23" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="C33" s="24" t="s">
         <v>95</v>
@@ -4525,13 +4546,13 @@
         <v>127</v>
       </c>
       <c r="E33" s="23" t="s">
+        <v>229</v>
+      </c>
+      <c r="F33" s="23" t="s">
         <v>230</v>
       </c>
-      <c r="F33" s="23" t="s">
-        <v>231</v>
-      </c>
       <c r="G33" s="24" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H33" s="25" t="s">
         <v>130</v>
@@ -4543,17 +4564,19 @@
         <v>88</v>
       </c>
       <c r="K33" s="24" t="s">
-        <v>149</v>
+        <v>175</v>
       </c>
       <c r="L33" s="23"/>
-      <c r="M33" s="23"/>
+      <c r="M33" s="23" t="s">
+        <v>231</v>
+      </c>
     </row>
     <row r="34" spans="1:13" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="22" t="s">
         <v>232</v>
       </c>
       <c r="B34" s="23" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="C34" s="24" t="s">
         <v>95</v>
@@ -4568,19 +4591,19 @@
         <v>234</v>
       </c>
       <c r="G34" s="24" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H34" s="25" t="s">
-        <v>176</v>
+        <v>130</v>
       </c>
       <c r="I34" s="24" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="J34" s="24" t="s">
         <v>88</v>
       </c>
       <c r="K34" s="24" t="s">
-        <v>131</v>
+        <v>149</v>
       </c>
       <c r="L34" s="23"/>
       <c r="M34" s="23"/>
@@ -4590,7 +4613,7 @@
         <v>235</v>
       </c>
       <c r="B35" s="23" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="C35" s="24" t="s">
         <v>95</v>
@@ -4605,13 +4628,13 @@
         <v>237</v>
       </c>
       <c r="G35" s="24" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H35" s="25" t="s">
-        <v>202</v>
+        <v>130</v>
       </c>
       <c r="I35" s="24" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="J35" s="24" t="s">
         <v>88</v>
@@ -4647,7 +4670,7 @@
         <v>86</v>
       </c>
       <c r="H36" s="25" t="s">
-        <v>202</v>
+        <v>180</v>
       </c>
       <c r="I36" s="24" t="s">
         <v>108</v>
@@ -4681,10 +4704,10 @@
         <v>244</v>
       </c>
       <c r="G37" s="24" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H37" s="25" t="s">
-        <v>176</v>
+        <v>206</v>
       </c>
       <c r="I37" s="24" t="s">
         <v>108</v>
@@ -4696,20 +4719,22 @@
         <v>131</v>
       </c>
       <c r="L37" s="23"/>
-      <c r="M37" s="23"/>
+      <c r="M37" s="23" t="s">
+        <v>245</v>
+      </c>
     </row>
     <row r="38" spans="1:13" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="22" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B38" s="23" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C38" s="24" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D38" s="24" t="s">
-        <v>246</v>
+        <v>127</v>
       </c>
       <c r="E38" s="23" t="s">
         <v>247</v>
@@ -4721,104 +4746,100 @@
         <v>86</v>
       </c>
       <c r="H38" s="25" t="s">
-        <v>249</v>
+        <v>206</v>
       </c>
       <c r="I38" s="24" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="J38" s="24" t="s">
         <v>88</v>
       </c>
       <c r="K38" s="24" t="s">
-        <v>250</v>
+        <v>131</v>
       </c>
       <c r="L38" s="23"/>
       <c r="M38" s="23"/>
     </row>
     <row r="39" spans="1:13" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="22" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="B39" s="23" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="C39" s="24" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D39" s="24" t="s">
         <v>127</v>
       </c>
       <c r="E39" s="23" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="F39" s="23" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="G39" s="24" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H39" s="25" t="s">
-        <v>254</v>
+        <v>180</v>
       </c>
       <c r="I39" s="24" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="J39" s="24" t="s">
         <v>88</v>
       </c>
       <c r="K39" s="24" t="s">
-        <v>149</v>
+        <v>131</v>
       </c>
       <c r="L39" s="23"/>
-      <c r="M39" s="23" t="s">
-        <v>255</v>
-      </c>
+      <c r="M39" s="23"/>
     </row>
     <row r="40" spans="1:13" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="22" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="B40" s="23" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="C40" s="24" t="s">
         <v>96</v>
       </c>
       <c r="D40" s="24" t="s">
-        <v>127</v>
+        <v>253</v>
       </c>
       <c r="E40" s="23" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="F40" s="23" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="G40" s="24" t="s">
         <v>86</v>
       </c>
       <c r="H40" s="25" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="I40" s="24" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="J40" s="24" t="s">
         <v>88</v>
       </c>
       <c r="K40" s="24" t="s">
-        <v>149</v>
+        <v>257</v>
       </c>
       <c r="L40" s="23"/>
-      <c r="M40" s="23" t="s">
-        <v>255</v>
-      </c>
+      <c r="M40" s="23"/>
     </row>
     <row r="41" spans="1:13" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="22" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B41" s="23" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="C41" s="24" t="s">
         <v>96</v>
@@ -4827,10 +4848,10 @@
         <v>127</v>
       </c>
       <c r="E41" s="23" t="s">
+        <v>259</v>
+      </c>
+      <c r="F41" s="23" t="s">
         <v>260</v>
-      </c>
-      <c r="F41" s="23" t="s">
-        <v>261</v>
       </c>
       <c r="G41" s="24" t="s">
         <v>86</v>
@@ -4848,14 +4869,16 @@
         <v>149</v>
       </c>
       <c r="L41" s="23"/>
-      <c r="M41" s="23"/>
+      <c r="M41" s="23" t="s">
+        <v>261</v>
+      </c>
     </row>
     <row r="42" spans="1:13" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="22" t="s">
         <v>262</v>
       </c>
       <c r="B42" s="23" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="C42" s="24" t="s">
         <v>96</v>
@@ -4873,7 +4896,7 @@
         <v>86</v>
       </c>
       <c r="H42" s="25" t="s">
-        <v>254</v>
+        <v>167</v>
       </c>
       <c r="I42" s="24" t="s">
         <v>107</v>
@@ -4885,20 +4908,22 @@
         <v>149</v>
       </c>
       <c r="L42" s="23"/>
-      <c r="M42" s="23"/>
+      <c r="M42" s="23" t="s">
+        <v>261</v>
+      </c>
     </row>
     <row r="43" spans="1:13" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="22" t="s">
         <v>265</v>
       </c>
       <c r="B43" s="23" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="C43" s="24" t="s">
         <v>96</v>
       </c>
       <c r="D43" s="24" t="s">
-        <v>246</v>
+        <v>127</v>
       </c>
       <c r="E43" s="23" t="s">
         <v>266</v>
@@ -4910,7 +4935,7 @@
         <v>86</v>
       </c>
       <c r="H43" s="25" t="s">
-        <v>254</v>
+        <v>167</v>
       </c>
       <c r="I43" s="24" t="s">
         <v>107</v>
@@ -4919,7 +4944,7 @@
         <v>88</v>
       </c>
       <c r="K43" s="24" t="s">
-        <v>250</v>
+        <v>149</v>
       </c>
       <c r="L43" s="23"/>
       <c r="M43" s="23"/>
@@ -4929,13 +4954,13 @@
         <v>268</v>
       </c>
       <c r="B44" s="23" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C44" s="24" t="s">
         <v>96</v>
       </c>
       <c r="D44" s="24" t="s">
-        <v>246</v>
+        <v>127</v>
       </c>
       <c r="E44" s="23" t="s">
         <v>269</v>
@@ -4947,7 +4972,7 @@
         <v>86</v>
       </c>
       <c r="H44" s="25" t="s">
-        <v>254</v>
+        <v>130</v>
       </c>
       <c r="I44" s="24" t="s">
         <v>107</v>
@@ -4956,7 +4981,7 @@
         <v>88</v>
       </c>
       <c r="K44" s="24" t="s">
-        <v>250</v>
+        <v>149</v>
       </c>
       <c r="L44" s="23"/>
       <c r="M44" s="23"/>
@@ -4972,7 +4997,7 @@
         <v>96</v>
       </c>
       <c r="D45" s="24" t="s">
-        <v>246</v>
+        <v>253</v>
       </c>
       <c r="E45" s="23" t="s">
         <v>272</v>
@@ -4984,7 +5009,7 @@
         <v>86</v>
       </c>
       <c r="H45" s="25" t="s">
-        <v>254</v>
+        <v>274</v>
       </c>
       <c r="I45" s="24" t="s">
         <v>107</v>
@@ -4993,14 +5018,14 @@
         <v>88</v>
       </c>
       <c r="K45" s="24" t="s">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="L45" s="23"/>
       <c r="M45" s="23"/>
     </row>
     <row r="46" spans="1:13" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="22" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B46" s="23" t="s">
         <v>122</v>
@@ -5009,19 +5034,19 @@
         <v>96</v>
       </c>
       <c r="D46" s="24" t="s">
-        <v>246</v>
+        <v>253</v>
       </c>
       <c r="E46" s="23" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F46" s="23" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="G46" s="24" t="s">
         <v>86</v>
       </c>
       <c r="H46" s="25" t="s">
-        <v>254</v>
+        <v>274</v>
       </c>
       <c r="I46" s="24" t="s">
         <v>107</v>
@@ -5030,14 +5055,14 @@
         <v>88</v>
       </c>
       <c r="K46" s="24" t="s">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="L46" s="23"/>
       <c r="M46" s="23"/>
     </row>
     <row r="47" spans="1:13" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="22" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B47" s="23" t="s">
         <v>122</v>
@@ -5046,19 +5071,19 @@
         <v>96</v>
       </c>
       <c r="D47" s="24" t="s">
-        <v>246</v>
+        <v>253</v>
       </c>
       <c r="E47" s="23" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F47" s="23" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="G47" s="24" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H47" s="25" t="s">
-        <v>254</v>
+        <v>274</v>
       </c>
       <c r="I47" s="24" t="s">
         <v>107</v>
@@ -5067,14 +5092,14 @@
         <v>88</v>
       </c>
       <c r="K47" s="24" t="s">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="L47" s="23"/>
       <c r="M47" s="23"/>
     </row>
     <row r="48" spans="1:13" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="22" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B48" s="23" t="s">
         <v>122</v>
@@ -5083,28 +5108,28 @@
         <v>96</v>
       </c>
       <c r="D48" s="24" t="s">
-        <v>246</v>
+        <v>253</v>
       </c>
       <c r="E48" s="23" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F48" s="23" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="G48" s="24" t="s">
         <v>86</v>
       </c>
       <c r="H48" s="25" t="s">
-        <v>283</v>
+        <v>274</v>
       </c>
       <c r="I48" s="24" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="J48" s="24" t="s">
         <v>88</v>
       </c>
       <c r="K48" s="24" t="s">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="L48" s="23"/>
       <c r="M48" s="23"/>
@@ -5120,7 +5145,7 @@
         <v>96</v>
       </c>
       <c r="D49" s="24" t="s">
-        <v>246</v>
+        <v>253</v>
       </c>
       <c r="E49" s="23" t="s">
         <v>285</v>
@@ -5129,28 +5154,26 @@
         <v>286</v>
       </c>
       <c r="G49" s="24" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H49" s="25" t="s">
-        <v>283</v>
+        <v>274</v>
       </c>
       <c r="I49" s="24" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="J49" s="24" t="s">
         <v>88</v>
       </c>
       <c r="K49" s="24" t="s">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="L49" s="23"/>
-      <c r="M49" s="23" t="s">
-        <v>287</v>
-      </c>
+      <c r="M49" s="23"/>
     </row>
     <row r="50" spans="1:13" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="22" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B50" s="23" t="s">
         <v>122</v>
@@ -5159,40 +5182,116 @@
         <v>96</v>
       </c>
       <c r="D50" s="24" t="s">
-        <v>246</v>
+        <v>253</v>
       </c>
       <c r="E50" s="23" t="s">
+        <v>288</v>
+      </c>
+      <c r="F50" s="23" t="s">
         <v>289</v>
-      </c>
-      <c r="F50" s="23" t="s">
-        <v>290</v>
       </c>
       <c r="G50" s="24" t="s">
         <v>86</v>
       </c>
       <c r="H50" s="25" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="I50" s="24" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="J50" s="24" t="s">
         <v>88</v>
       </c>
       <c r="K50" s="24" t="s">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="L50" s="23"/>
       <c r="M50" s="23"/>
     </row>
+    <row r="51" spans="1:13" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="22" t="s">
+        <v>291</v>
+      </c>
+      <c r="B51" s="23" t="s">
+        <v>122</v>
+      </c>
+      <c r="C51" s="24" t="s">
+        <v>96</v>
+      </c>
+      <c r="D51" s="24" t="s">
+        <v>253</v>
+      </c>
+      <c r="E51" s="23" t="s">
+        <v>292</v>
+      </c>
+      <c r="F51" s="23" t="s">
+        <v>293</v>
+      </c>
+      <c r="G51" s="24" t="s">
+        <v>86</v>
+      </c>
+      <c r="H51" s="25" t="s">
+        <v>290</v>
+      </c>
+      <c r="I51" s="24" t="s">
+        <v>108</v>
+      </c>
+      <c r="J51" s="24" t="s">
+        <v>88</v>
+      </c>
+      <c r="K51" s="24" t="s">
+        <v>257</v>
+      </c>
+      <c r="L51" s="23"/>
+      <c r="M51" s="23" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="52" spans="1:13" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="22" t="s">
+        <v>295</v>
+      </c>
+      <c r="B52" s="23" t="s">
+        <v>122</v>
+      </c>
+      <c r="C52" s="24" t="s">
+        <v>96</v>
+      </c>
+      <c r="D52" s="24" t="s">
+        <v>253</v>
+      </c>
+      <c r="E52" s="23" t="s">
+        <v>296</v>
+      </c>
+      <c r="F52" s="23" t="s">
+        <v>297</v>
+      </c>
+      <c r="G52" s="24" t="s">
+        <v>86</v>
+      </c>
+      <c r="H52" s="25" t="s">
+        <v>298</v>
+      </c>
+      <c r="I52" s="24" t="s">
+        <v>109</v>
+      </c>
+      <c r="J52" s="24" t="s">
+        <v>88</v>
+      </c>
+      <c r="K52" s="24" t="s">
+        <v>257</v>
+      </c>
+      <c r="L52" s="23"/>
+      <c r="M52" s="23"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A5:M50" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
+  <autoFilter ref="A5:M52" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
   <mergeCells count="3">
     <mergeCell ref="A3:M3"/>
     <mergeCell ref="A2:M2"/>
     <mergeCell ref="A1:M1"/>
   </mergeCells>
-  <conditionalFormatting sqref="J6:J50">
+  <conditionalFormatting sqref="J6:J52">
     <cfRule type="cellIs" dxfId="23" priority="1" operator="equal">
       <formula>"Hecho"</formula>
     </cfRule>
@@ -5206,7 +5305,7 @@
       <formula>"Pendiente"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K6:K50">
+  <conditionalFormatting sqref="K6:K52">
     <cfRule type="cellIs" dxfId="19" priority="5" operator="equal">
       <formula>"Sí"</formula>
     </cfRule>
@@ -5217,7 +5316,7 @@
       <formula>"No"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G6:G50">
+  <conditionalFormatting sqref="G6:G52">
     <cfRule type="cellIs" dxfId="16" priority="8" operator="equal">
       <formula>"Alta"</formula>
     </cfRule>
@@ -5226,13 +5325,13 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation type="list" sqref="J6:J50" xr:uid="{00000000-0002-0000-0200-000000000000}">
+    <dataValidation type="list" sqref="J6:J52" xr:uid="{00000000-0002-0000-0200-000000000000}">
       <formula1>"Pendiente,En progreso,Hecho,Bloqueado"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="G6:G50" xr:uid="{00000000-0002-0000-0200-000001000000}">
+    <dataValidation type="list" sqref="G6:G52" xr:uid="{00000000-0002-0000-0200-000001000000}">
       <formula1>"Alta,Media,Baja"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="K6:K50" xr:uid="{00000000-0002-0000-0200-000002000000}">
+    <dataValidation type="list" sqref="K6:K52" xr:uid="{00000000-0002-0000-0200-000002000000}">
       <formula1>"Sí,Parcial,No,NA"</formula1>
     </dataValidation>
   </dataValidations>
@@ -5246,7 +5345,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H59"/>
+  <dimension ref="A1:H61"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" outlineLevelRow="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
@@ -5261,7 +5360,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="27" t="s">
-        <v>292</v>
+        <v>299</v>
       </c>
       <c r="B1" s="28"/>
       <c r="C1" s="28"/>
@@ -5273,7 +5372,7 @@
     </row>
     <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="33" t="s">
-        <v>293</v>
+        <v>300</v>
       </c>
       <c r="B2" s="34"/>
       <c r="C2" s="34"/>
@@ -5285,7 +5384,7 @@
     </row>
     <row r="3" spans="1:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="36" t="s">
-        <v>294</v>
+        <v>301</v>
       </c>
       <c r="B3" s="32"/>
       <c r="C3" s="32"/>
@@ -5323,7 +5422,7 @@
     </row>
     <row r="6" spans="1:8" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="29" t="s">
-        <v>295</v>
+        <v>302</v>
       </c>
       <c r="B6" s="30"/>
       <c r="C6" s="30"/>
@@ -5500,7 +5599,7 @@
     </row>
     <row r="13" spans="1:8" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="29" t="s">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="B13" s="30"/>
       <c r="C13" s="30"/>
@@ -5681,15 +5780,15 @@
       </c>
       <c r="B19" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A19,Requerimientos!$A:$A,0)),"")</f>
-        <v>Añadir cobros adicionales por daños con monto motivo y observación</v>
+        <v>Establecer el monto mínimo de reserva que da derecho al taxi gratuito al aeropuerto</v>
       </c>
       <c r="C19" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A19,Requerimientos!$A:$A,0)),"")</f>
-        <v>M5 Pagos y cobros</v>
+        <v>M8 Taxi</v>
       </c>
       <c r="D19" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A19,Requerimientos!$A:$A,0)),"")</f>
-        <v>Media</v>
+        <v>Alta</v>
       </c>
       <c r="E19" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$I:$I,MATCH($A19,Requerimientos!$A:$A,0)),"")</f>
@@ -5701,7 +5800,7 @@
       </c>
       <c r="G19" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$K:$K,MATCH($A19,Requerimientos!$A:$A,0)),"")</f>
-        <v>Sí</v>
+        <v>No</v>
       </c>
       <c r="H19" s="24">
         <f>IFERROR(INDEX(Requerimientos!$L:$L,MATCH($A19,Requerimientos!$A:$A,0)),"")</f>
@@ -5710,15 +5809,15 @@
     </row>
     <row r="20" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A20" s="26" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B20" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A20,Requerimientos!$A:$A,0)),"")</f>
-        <v>Reporte de ingresos por servicios adicionales ordenado de menor a mayor</v>
+        <v>Añadir cobros adicionales por daños con monto motivo y observación</v>
       </c>
       <c r="C20" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A20,Requerimientos!$A:$A,0)),"")</f>
-        <v>M9 Reportes y logs</v>
+        <v>M5 Pagos y cobros</v>
       </c>
       <c r="D20" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A20,Requerimientos!$A:$A,0)),"")</f>
@@ -5734,7 +5833,7 @@
       </c>
       <c r="G20" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$K:$K,MATCH($A20,Requerimientos!$A:$A,0)),"")</f>
-        <v>Parcial</v>
+        <v>Sí</v>
       </c>
       <c r="H20" s="24">
         <f>IFERROR(INDEX(Requerimientos!$L:$L,MATCH($A20,Requerimientos!$A:$A,0)),"")</f>
@@ -5743,23 +5842,23 @@
     </row>
     <row r="21" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A21" s="26" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B21" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A21,Requerimientos!$A:$A,0)),"")</f>
-        <v>Registrar la ubicación del hotel y los lugares históricos cercanos</v>
+        <v>Reporte de ingresos por servicios adicionales ordenado de menor a mayor</v>
       </c>
       <c r="C21" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A21,Requerimientos!$A:$A,0)),"")</f>
-        <v>M3 Catálogo</v>
+        <v>M9 Reportes y logs</v>
       </c>
       <c r="D21" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A21,Requerimientos!$A:$A,0)),"")</f>
-        <v>Alta</v>
+        <v>Media</v>
       </c>
       <c r="E21" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$I:$I,MATCH($A21,Requerimientos!$A:$A,0)),"")</f>
-        <v>Lab 7</v>
+        <v>Lab 6</v>
       </c>
       <c r="F21" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$J:$J,MATCH($A21,Requerimientos!$A:$A,0)),"")</f>
@@ -5767,7 +5866,7 @@
       </c>
       <c r="G21" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$K:$K,MATCH($A21,Requerimientos!$A:$A,0)),"")</f>
-        <v>No</v>
+        <v>Parcial</v>
       </c>
       <c r="H21" s="24">
         <f>IFERROR(INDEX(Requerimientos!$L:$L,MATCH($A21,Requerimientos!$A:$A,0)),"")</f>
@@ -5776,19 +5875,19 @@
     </row>
     <row r="22" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A22" s="26" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B22" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A22,Requerimientos!$A:$A,0)),"")</f>
-        <v>Ver el estado del taxista asignado en camino a recoger y llegó al destino</v>
+        <v>Registrar la ubicación del hotel y los lugares históricos cercanos</v>
       </c>
       <c r="C22" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A22,Requerimientos!$A:$A,0)),"")</f>
-        <v>M8 Taxi</v>
+        <v>M3 Catálogo</v>
       </c>
       <c r="D22" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A22,Requerimientos!$A:$A,0)),"")</f>
-        <v>Media</v>
+        <v>Alta</v>
       </c>
       <c r="E22" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$I:$I,MATCH($A22,Requerimientos!$A:$A,0)),"")</f>
@@ -5800,69 +5899,69 @@
       </c>
       <c r="G22" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$K:$K,MATCH($A22,Requerimientos!$A:$A,0)),"")</f>
-        <v>Sí</v>
+        <v>No</v>
       </c>
       <c r="H22" s="24">
         <f>IFERROR(INDEX(Requerimientos!$L:$L,MATCH($A22,Requerimientos!$A:$A,0)),"")</f>
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:8" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="29" t="s">
-        <v>297</v>
-      </c>
-      <c r="B24" s="30"/>
-      <c r="C24" s="30"/>
-      <c r="D24" s="30"/>
-      <c r="E24" s="30"/>
-      <c r="F24" s="30"/>
-      <c r="G24" s="30"/>
-      <c r="H24" s="30"/>
-    </row>
-    <row r="25" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="26" t="s">
-        <v>181</v>
-      </c>
-      <c r="B25" s="3" t="str">
-        <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A25,Requerimientos!$A:$A,0)),"")</f>
-        <v>Acceder a la app móvil una vez habilitado</v>
-      </c>
-      <c r="C25" s="24" t="str">
-        <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A25,Requerimientos!$A:$A,0)),"")</f>
-        <v>M1 Autenticación</v>
-      </c>
-      <c r="D25" s="24" t="str">
-        <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A25,Requerimientos!$A:$A,0)),"")</f>
-        <v>Alta</v>
-      </c>
-      <c r="E25" s="24" t="str">
-        <f>IFERROR(INDEX(Requerimientos!$I:$I,MATCH($A25,Requerimientos!$A:$A,0)),"")</f>
-        <v>Lab 6</v>
-      </c>
-      <c r="F25" s="24" t="str">
-        <f>IFERROR(INDEX(Requerimientos!$J:$J,MATCH($A25,Requerimientos!$A:$A,0)),"")</f>
-        <v>Pendiente</v>
-      </c>
-      <c r="G25" s="24" t="str">
-        <f>IFERROR(INDEX(Requerimientos!$K:$K,MATCH($A25,Requerimientos!$A:$A,0)),"")</f>
-        <v>No</v>
-      </c>
-      <c r="H25" s="24">
-        <f>IFERROR(INDEX(Requerimientos!$L:$L,MATCH($A25,Requerimientos!$A:$A,0)),"")</f>
+    <row r="23" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="26" t="s">
+        <v>182</v>
+      </c>
+      <c r="B23" s="3" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A23,Requerimientos!$A:$A,0)),"")</f>
+        <v>Ver el estado del taxista asignado en camino a recoger y llegó al destino</v>
+      </c>
+      <c r="C23" s="24" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A23,Requerimientos!$A:$A,0)),"")</f>
+        <v>M8 Taxi</v>
+      </c>
+      <c r="D23" s="24" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A23,Requerimientos!$A:$A,0)),"")</f>
+        <v>Media</v>
+      </c>
+      <c r="E23" s="24" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$I:$I,MATCH($A23,Requerimientos!$A:$A,0)),"")</f>
+        <v>Lab 7</v>
+      </c>
+      <c r="F23" s="24" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$J:$J,MATCH($A23,Requerimientos!$A:$A,0)),"")</f>
+        <v>Pendiente</v>
+      </c>
+      <c r="G23" s="24" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$K:$K,MATCH($A23,Requerimientos!$A:$A,0)),"")</f>
+        <v>Sí</v>
+      </c>
+      <c r="H23" s="24">
+        <f>IFERROR(INDEX(Requerimientos!$L:$L,MATCH($A23,Requerimientos!$A:$A,0)),"")</f>
         <v>0</v>
       </c>
+    </row>
+    <row r="25" spans="1:8" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="29" t="s">
+        <v>304</v>
+      </c>
+      <c r="B25" s="30"/>
+      <c r="C25" s="30"/>
+      <c r="D25" s="30"/>
+      <c r="E25" s="30"/>
+      <c r="F25" s="30"/>
+      <c r="G25" s="30"/>
+      <c r="H25" s="30"/>
     </row>
     <row r="26" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A26" s="26" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B26" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A26,Requerimientos!$A:$A,0)),"")</f>
-        <v>Ver hoteles y pedidos disponibles</v>
+        <v>Acceder a la app móvil una vez habilitado</v>
       </c>
       <c r="C26" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A26,Requerimientos!$A:$A,0)),"")</f>
-        <v>M8 Taxi</v>
+        <v>M1 Autenticación</v>
       </c>
       <c r="D26" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A26,Requerimientos!$A:$A,0)),"")</f>
@@ -5887,11 +5986,11 @@
     </row>
     <row r="27" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A27" s="26" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B27" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A27,Requerimientos!$A:$A,0)),"")</f>
-        <v>Aceptar un pedido que deja de estar disponible para los demás</v>
+        <v>Ver hoteles y pedidos disponibles</v>
       </c>
       <c r="C27" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A27,Requerimientos!$A:$A,0)),"")</f>
@@ -5924,7 +6023,7 @@
       </c>
       <c r="B28" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A28,Requerimientos!$A:$A,0)),"")</f>
-        <v>Actualizar los estados del servicio</v>
+        <v>Aceptar un pedido que deja de estar disponible para los demás</v>
       </c>
       <c r="C28" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A28,Requerimientos!$A:$A,0)),"")</f>
@@ -5953,11 +6052,11 @@
     </row>
     <row r="29" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A29" s="26" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B29" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A29,Requerimientos!$A:$A,0)),"")</f>
-        <v>Registrar automáticamente su ubicación durante el servicio activo</v>
+        <v>Actualizar los estados del servicio</v>
       </c>
       <c r="C29" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A29,Requerimientos!$A:$A,0)),"")</f>
@@ -5969,7 +6068,7 @@
       </c>
       <c r="E29" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$I:$I,MATCH($A29,Requerimientos!$A:$A,0)),"")</f>
-        <v>Lab 7</v>
+        <v>Lab 6</v>
       </c>
       <c r="F29" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$J:$J,MATCH($A29,Requerimientos!$A:$A,0)),"")</f>
@@ -5986,11 +6085,11 @@
     </row>
     <row r="30" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A30" s="26" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B30" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A30,Requerimientos!$A:$A,0)),"")</f>
-        <v>Registrar FINALIZADO únicamente escaneando el QR del cliente</v>
+        <v>Registrar automáticamente su ubicación durante el servicio activo</v>
       </c>
       <c r="C30" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A30,Requerimientos!$A:$A,0)),"")</f>
@@ -6019,15 +6118,15 @@
     </row>
     <row r="31" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A31" s="26" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B31" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A31,Requerimientos!$A:$A,0)),"")</f>
-        <v>Autoregistrarse en la app web con todos sus datos y fotos</v>
+        <v>Registrar FINALIZADO únicamente escaneando el QR del cliente</v>
       </c>
       <c r="C31" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A31,Requerimientos!$A:$A,0)),"")</f>
-        <v>M1 Autenticación</v>
+        <v>M8 Taxi</v>
       </c>
       <c r="D31" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A31,Requerimientos!$A:$A,0)),"")</f>
@@ -6035,7 +6134,7 @@
       </c>
       <c r="E31" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$I:$I,MATCH($A31,Requerimientos!$A:$A,0)),"")</f>
-        <v>App web</v>
+        <v>Lab 7</v>
       </c>
       <c r="F31" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$J:$J,MATCH($A31,Requerimientos!$A:$A,0)),"")</f>
@@ -6050,50 +6149,50 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:8" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="29" t="s">
-        <v>298</v>
-      </c>
-      <c r="B33" s="30"/>
-      <c r="C33" s="30"/>
-      <c r="D33" s="30"/>
-      <c r="E33" s="30"/>
-      <c r="F33" s="30"/>
-      <c r="G33" s="30"/>
-      <c r="H33" s="30"/>
-    </row>
-    <row r="34" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="26" t="s">
-        <v>207</v>
-      </c>
-      <c r="B34" s="3" t="str">
-        <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A34,Requerimientos!$A:$A,0)),"")</f>
-        <v>Autoregistrarse y quedar habilitado automáticamente</v>
-      </c>
-      <c r="C34" s="24" t="str">
-        <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A34,Requerimientos!$A:$A,0)),"")</f>
+    <row r="32" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="26" t="s">
+        <v>208</v>
+      </c>
+      <c r="B32" s="3" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A32,Requerimientos!$A:$A,0)),"")</f>
+        <v>Autoregistrarse en la app web con todos sus datos y fotos</v>
+      </c>
+      <c r="C32" s="24" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A32,Requerimientos!$A:$A,0)),"")</f>
         <v>M1 Autenticación</v>
       </c>
-      <c r="D34" s="24" t="str">
-        <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A34,Requerimientos!$A:$A,0)),"")</f>
-        <v>Alta</v>
-      </c>
-      <c r="E34" s="24" t="str">
-        <f>IFERROR(INDEX(Requerimientos!$I:$I,MATCH($A34,Requerimientos!$A:$A,0)),"")</f>
-        <v>Lab 6</v>
-      </c>
-      <c r="F34" s="24" t="str">
-        <f>IFERROR(INDEX(Requerimientos!$J:$J,MATCH($A34,Requerimientos!$A:$A,0)),"")</f>
-        <v>Pendiente</v>
-      </c>
-      <c r="G34" s="24" t="str">
-        <f>IFERROR(INDEX(Requerimientos!$K:$K,MATCH($A34,Requerimientos!$A:$A,0)),"")</f>
-        <v>Parcial</v>
-      </c>
-      <c r="H34" s="24">
-        <f>IFERROR(INDEX(Requerimientos!$L:$L,MATCH($A34,Requerimientos!$A:$A,0)),"")</f>
+      <c r="D32" s="24" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A32,Requerimientos!$A:$A,0)),"")</f>
+        <v>Alta</v>
+      </c>
+      <c r="E32" s="24" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$I:$I,MATCH($A32,Requerimientos!$A:$A,0)),"")</f>
+        <v>App web</v>
+      </c>
+      <c r="F32" s="24" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$J:$J,MATCH($A32,Requerimientos!$A:$A,0)),"")</f>
+        <v>Pendiente</v>
+      </c>
+      <c r="G32" s="24" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$K:$K,MATCH($A32,Requerimientos!$A:$A,0)),"")</f>
+        <v>No</v>
+      </c>
+      <c r="H32" s="24">
+        <f>IFERROR(INDEX(Requerimientos!$L:$L,MATCH($A32,Requerimientos!$A:$A,0)),"")</f>
         <v>0</v>
       </c>
+    </row>
+    <row r="34" spans="1:8" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="29" t="s">
+        <v>305</v>
+      </c>
+      <c r="B34" s="30"/>
+      <c r="C34" s="30"/>
+      <c r="D34" s="30"/>
+      <c r="E34" s="30"/>
+      <c r="F34" s="30"/>
+      <c r="G34" s="30"/>
+      <c r="H34" s="30"/>
     </row>
     <row r="35" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A35" s="26" t="s">
@@ -6101,11 +6200,11 @@
       </c>
       <c r="B35" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A35,Requerimientos!$A:$A,0)),"")</f>
-        <v>Consultar hoteles habitaciones servicios disponibilidad y valoraciones</v>
+        <v>Autoregistrarse y quedar habilitado automáticamente</v>
       </c>
       <c r="C35" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A35,Requerimientos!$A:$A,0)),"")</f>
-        <v>M3 Catálogo</v>
+        <v>M1 Autenticación</v>
       </c>
       <c r="D35" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A35,Requerimientos!$A:$A,0)),"")</f>
@@ -6121,7 +6220,7 @@
       </c>
       <c r="G35" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$K:$K,MATCH($A35,Requerimientos!$A:$A,0)),"")</f>
-        <v>Sí</v>
+        <v>Parcial</v>
       </c>
       <c r="H35" s="24">
         <f>IFERROR(INDEX(Requerimientos!$L:$L,MATCH($A35,Requerimientos!$A:$A,0)),"")</f>
@@ -6130,15 +6229,15 @@
     </row>
     <row r="36" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A36" s="26" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B36" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A36,Requerimientos!$A:$A,0)),"")</f>
-        <v>Reservar con tarjeta de crédito o débito simulada</v>
+        <v>Consultar hoteles habitaciones servicios disponibilidad y valoraciones</v>
       </c>
       <c r="C36" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A36,Requerimientos!$A:$A,0)),"")</f>
-        <v>M4 Reservas</v>
+        <v>M3 Catálogo</v>
       </c>
       <c r="D36" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A36,Requerimientos!$A:$A,0)),"")</f>
@@ -6163,15 +6262,15 @@
     </row>
     <row r="37" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A37" s="26" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B37" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A37,Requerimientos!$A:$A,0)),"")</f>
-        <v>Hacer checkout y registrar valoración y observaciones obligatorias</v>
+        <v>Reservar con tarjeta de crédito o débito simulada</v>
       </c>
       <c r="C37" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A37,Requerimientos!$A:$A,0)),"")</f>
-        <v>M6 Checkout y valoraciones</v>
+        <v>M4 Reservas</v>
       </c>
       <c r="D37" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A37,Requerimientos!$A:$A,0)),"")</f>
@@ -6196,15 +6295,15 @@
     </row>
     <row r="38" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A38" s="26" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B38" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A38,Requerimientos!$A:$A,0)),"")</f>
-        <v>Recibir notificación cuando se le hace el cobro</v>
+        <v>Hacer checkout y registrar valoración y observaciones obligatorias</v>
       </c>
       <c r="C38" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A38,Requerimientos!$A:$A,0)),"")</f>
-        <v>M5 Pagos y cobros</v>
+        <v>M6 Checkout y valoraciones</v>
       </c>
       <c r="D38" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A38,Requerimientos!$A:$A,0)),"")</f>
@@ -6220,7 +6319,7 @@
       </c>
       <c r="G38" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$K:$K,MATCH($A38,Requerimientos!$A:$A,0)),"")</f>
-        <v>Parcial</v>
+        <v>Sí</v>
       </c>
       <c r="H38" s="24">
         <f>IFERROR(INDEX(Requerimientos!$L:$L,MATCH($A38,Requerimientos!$A:$A,0)),"")</f>
@@ -6229,15 +6328,15 @@
     </row>
     <row r="39" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A39" s="26" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B39" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A39,Requerimientos!$A:$A,0)),"")</f>
-        <v>Chat privado con el hotel entre la confirmación de la reserva y el fin del checkout</v>
+        <v>Recibir notificación cuando se le hace el cobro</v>
       </c>
       <c r="C39" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A39,Requerimientos!$A:$A,0)),"")</f>
-        <v>M7 Chat</v>
+        <v>M5 Pagos y cobros</v>
       </c>
       <c r="D39" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A39,Requerimientos!$A:$A,0)),"")</f>
@@ -6262,19 +6361,19 @@
     </row>
     <row r="40" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A40" s="26" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B40" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A40,Requerimientos!$A:$A,0)),"")</f>
-        <v>Ver el historial de sus reservas</v>
+        <v>Chat privado con el hotel entre la confirmación de la reserva y el fin del checkout</v>
       </c>
       <c r="C40" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A40,Requerimientos!$A:$A,0)),"")</f>
-        <v>M4 Reservas</v>
+        <v>M7 Chat</v>
       </c>
       <c r="D40" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A40,Requerimientos!$A:$A,0)),"")</f>
-        <v>Media</v>
+        <v>Alta</v>
       </c>
       <c r="E40" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$I:$I,MATCH($A40,Requerimientos!$A:$A,0)),"")</f>
@@ -6286,7 +6385,7 @@
       </c>
       <c r="G40" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$K:$K,MATCH($A40,Requerimientos!$A:$A,0)),"")</f>
-        <v>Sí</v>
+        <v>Parcial</v>
       </c>
       <c r="H40" s="24">
         <f>IFERROR(INDEX(Requerimientos!$L:$L,MATCH($A40,Requerimientos!$A:$A,0)),"")</f>
@@ -6299,19 +6398,19 @@
       </c>
       <c r="B41" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A41,Requerimientos!$A:$A,0)),"")</f>
-        <v>Solicitar el taxi gratuito al aeropuerto si la reserva alcanza el monto mínimo</v>
+        <v>Ver el historial de sus reservas</v>
       </c>
       <c r="C41" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A41,Requerimientos!$A:$A,0)),"")</f>
-        <v>M8 Taxi</v>
+        <v>M4 Reservas</v>
       </c>
       <c r="D41" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A41,Requerimientos!$A:$A,0)),"")</f>
-        <v>Alta</v>
+        <v>Media</v>
       </c>
       <c r="E41" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$I:$I,MATCH($A41,Requerimientos!$A:$A,0)),"")</f>
-        <v>Lab 7</v>
+        <v>Lab 6</v>
       </c>
       <c r="F41" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$J:$J,MATCH($A41,Requerimientos!$A:$A,0)),"")</f>
@@ -6319,7 +6418,7 @@
       </c>
       <c r="G41" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$K:$K,MATCH($A41,Requerimientos!$A:$A,0)),"")</f>
-        <v>No</v>
+        <v>Sí</v>
       </c>
       <c r="H41" s="24">
         <f>IFERROR(INDEX(Requerimientos!$L:$L,MATCH($A41,Requerimientos!$A:$A,0)),"")</f>
@@ -6332,19 +6431,19 @@
       </c>
       <c r="B42" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A42,Requerimientos!$A:$A,0)),"")</f>
-        <v>Ver datos vehículo valoración y ubicación del taxista en un mapa</v>
+        <v>Consultar los lugares históricos cercanos al hotel</v>
       </c>
       <c r="C42" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A42,Requerimientos!$A:$A,0)),"")</f>
-        <v>M8 Taxi</v>
+        <v>M3 Catálogo</v>
       </c>
       <c r="D42" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A42,Requerimientos!$A:$A,0)),"")</f>
-        <v>Alta</v>
+        <v>Media</v>
       </c>
       <c r="E42" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$I:$I,MATCH($A42,Requerimientos!$A:$A,0)),"")</f>
-        <v>Lab 7</v>
+        <v>Lab 6</v>
       </c>
       <c r="F42" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$J:$J,MATCH($A42,Requerimientos!$A:$A,0)),"")</f>
@@ -6365,7 +6464,7 @@
       </c>
       <c r="B43" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A43,Requerimientos!$A:$A,0)),"")</f>
-        <v>Recibir el QR del hotel y mostrarlo al llegar</v>
+        <v>Solicitar el taxi gratuito al aeropuerto si la reserva alcanza el monto mínimo</v>
       </c>
       <c r="C43" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A43,Requerimientos!$A:$A,0)),"")</f>
@@ -6398,7 +6497,7 @@
       </c>
       <c r="B44" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A44,Requerimientos!$A:$A,0)),"")</f>
-        <v>Calificar al taxista al finalizar el servicio</v>
+        <v>Ver datos vehículo valoración y ubicación del taxista en un mapa</v>
       </c>
       <c r="C44" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A44,Requerimientos!$A:$A,0)),"")</f>
@@ -6406,7 +6505,7 @@
       </c>
       <c r="D44" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A44,Requerimientos!$A:$A,0)),"")</f>
-        <v>Media</v>
+        <v>Alta</v>
       </c>
       <c r="E44" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$I:$I,MATCH($A44,Requerimientos!$A:$A,0)),"")</f>
@@ -6425,95 +6524,95 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:8" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="29" t="s">
-        <v>299</v>
-      </c>
-      <c r="B46" s="30"/>
-      <c r="C46" s="30"/>
-      <c r="D46" s="30"/>
-      <c r="E46" s="30"/>
-      <c r="F46" s="30"/>
-      <c r="G46" s="30"/>
-      <c r="H46" s="30"/>
-    </row>
-    <row r="47" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="26" t="s">
-        <v>245</v>
-      </c>
-      <c r="B47" s="3" t="str">
-        <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A47,Requerimientos!$A:$A,0)),"")</f>
-        <v>La app móvil es Android nativa en Java con versión mínima Android 14 API 34</v>
-      </c>
-      <c r="C47" s="24" t="str">
-        <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A47,Requerimientos!$A:$A,0)),"")</f>
-        <v>M10 Calidad</v>
-      </c>
-      <c r="D47" s="24" t="str">
-        <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A47,Requerimientos!$A:$A,0)),"")</f>
-        <v>Alta</v>
-      </c>
-      <c r="E47" s="24" t="str">
-        <f>IFERROR(INDEX(Requerimientos!$I:$I,MATCH($A47,Requerimientos!$A:$A,0)),"")</f>
-        <v>Lab 3</v>
-      </c>
-      <c r="F47" s="24" t="str">
-        <f>IFERROR(INDEX(Requerimientos!$J:$J,MATCH($A47,Requerimientos!$A:$A,0)),"")</f>
-        <v>Pendiente</v>
-      </c>
-      <c r="G47" s="24" t="str">
-        <f>IFERROR(INDEX(Requerimientos!$K:$K,MATCH($A47,Requerimientos!$A:$A,0)),"")</f>
-        <v>NA</v>
-      </c>
-      <c r="H47" s="24">
-        <f>IFERROR(INDEX(Requerimientos!$L:$L,MATCH($A47,Requerimientos!$A:$A,0)),"")</f>
+    <row r="45" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="26" t="s">
+        <v>246</v>
+      </c>
+      <c r="B45" s="3" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A45,Requerimientos!$A:$A,0)),"")</f>
+        <v>Recibir el QR del hotel y mostrarlo al llegar</v>
+      </c>
+      <c r="C45" s="24" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A45,Requerimientos!$A:$A,0)),"")</f>
+        <v>M8 Taxi</v>
+      </c>
+      <c r="D45" s="24" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A45,Requerimientos!$A:$A,0)),"")</f>
+        <v>Alta</v>
+      </c>
+      <c r="E45" s="24" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$I:$I,MATCH($A45,Requerimientos!$A:$A,0)),"")</f>
+        <v>Lab 7</v>
+      </c>
+      <c r="F45" s="24" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$J:$J,MATCH($A45,Requerimientos!$A:$A,0)),"")</f>
+        <v>Pendiente</v>
+      </c>
+      <c r="G45" s="24" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$K:$K,MATCH($A45,Requerimientos!$A:$A,0)),"")</f>
+        <v>No</v>
+      </c>
+      <c r="H45" s="24">
+        <f>IFERROR(INDEX(Requerimientos!$L:$L,MATCH($A45,Requerimientos!$A:$A,0)),"")</f>
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="26" t="s">
-        <v>251</v>
-      </c>
-      <c r="B48" s="3" t="str">
-        <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A48,Requerimientos!$A:$A,0)),"")</f>
-        <v>Una habitación no puede tener reservas de distintos clientes con períodos superpuestos</v>
-      </c>
-      <c r="C48" s="24" t="str">
-        <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A48,Requerimientos!$A:$A,0)),"")</f>
-        <v>M4 Reservas</v>
-      </c>
-      <c r="D48" s="24" t="str">
-        <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A48,Requerimientos!$A:$A,0)),"")</f>
-        <v>Alta</v>
-      </c>
-      <c r="E48" s="24" t="str">
-        <f>IFERROR(INDEX(Requerimientos!$I:$I,MATCH($A48,Requerimientos!$A:$A,0)),"")</f>
-        <v>Lab 6</v>
-      </c>
-      <c r="F48" s="24" t="str">
-        <f>IFERROR(INDEX(Requerimientos!$J:$J,MATCH($A48,Requerimientos!$A:$A,0)),"")</f>
-        <v>Pendiente</v>
-      </c>
-      <c r="G48" s="24" t="str">
-        <f>IFERROR(INDEX(Requerimientos!$K:$K,MATCH($A48,Requerimientos!$A:$A,0)),"")</f>
-        <v>Sí</v>
-      </c>
-      <c r="H48" s="24">
-        <f>IFERROR(INDEX(Requerimientos!$L:$L,MATCH($A48,Requerimientos!$A:$A,0)),"")</f>
+    <row r="46" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="26" t="s">
+        <v>249</v>
+      </c>
+      <c r="B46" s="3" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A46,Requerimientos!$A:$A,0)),"")</f>
+        <v>Calificar al taxista al finalizar el servicio</v>
+      </c>
+      <c r="C46" s="24" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A46,Requerimientos!$A:$A,0)),"")</f>
+        <v>M8 Taxi</v>
+      </c>
+      <c r="D46" s="24" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A46,Requerimientos!$A:$A,0)),"")</f>
+        <v>Media</v>
+      </c>
+      <c r="E46" s="24" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$I:$I,MATCH($A46,Requerimientos!$A:$A,0)),"")</f>
+        <v>Lab 7</v>
+      </c>
+      <c r="F46" s="24" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$J:$J,MATCH($A46,Requerimientos!$A:$A,0)),"")</f>
+        <v>Pendiente</v>
+      </c>
+      <c r="G46" s="24" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$K:$K,MATCH($A46,Requerimientos!$A:$A,0)),"")</f>
+        <v>No</v>
+      </c>
+      <c r="H46" s="24">
+        <f>IFERROR(INDEX(Requerimientos!$L:$L,MATCH($A46,Requerimientos!$A:$A,0)),"")</f>
         <v>0</v>
       </c>
+    </row>
+    <row r="48" spans="1:8" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="29" t="s">
+        <v>306</v>
+      </c>
+      <c r="B48" s="30"/>
+      <c r="C48" s="30"/>
+      <c r="D48" s="30"/>
+      <c r="E48" s="30"/>
+      <c r="F48" s="30"/>
+      <c r="G48" s="30"/>
+      <c r="H48" s="30"/>
     </row>
     <row r="49" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A49" s="26" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="B49" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A49,Requerimientos!$A:$A,0)),"")</f>
-        <v>Un mismo cliente no puede tener reservas con fechas de alojamiento superpuestas</v>
+        <v>La app móvil es Android nativa en Java con versión mínima Android 14 API 34</v>
       </c>
       <c r="C49" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A49,Requerimientos!$A:$A,0)),"")</f>
-        <v>M4 Reservas</v>
+        <v>M10 Calidad</v>
       </c>
       <c r="D49" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A49,Requerimientos!$A:$A,0)),"")</f>
@@ -6521,7 +6620,7 @@
       </c>
       <c r="E49" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$I:$I,MATCH($A49,Requerimientos!$A:$A,0)),"")</f>
-        <v>Lab 6</v>
+        <v>Lab 3</v>
       </c>
       <c r="F49" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$J:$J,MATCH($A49,Requerimientos!$A:$A,0)),"")</f>
@@ -6529,7 +6628,7 @@
       </c>
       <c r="G49" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$K:$K,MATCH($A49,Requerimientos!$A:$A,0)),"")</f>
-        <v>Sí</v>
+        <v>NA</v>
       </c>
       <c r="H49" s="24">
         <f>IFERROR(INDEX(Requerimientos!$L:$L,MATCH($A49,Requerimientos!$A:$A,0)),"")</f>
@@ -6538,15 +6637,15 @@
     </row>
     <row r="50" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A50" s="26" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B50" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A50,Requerimientos!$A:$A,0)),"")</f>
-        <v>Login único: tras autenticar se resuelve el rol y se navega al flujo correspondiente</v>
+        <v>Una habitación no puede tener reservas de distintos clientes con períodos superpuestos</v>
       </c>
       <c r="C50" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A50,Requerimientos!$A:$A,0)),"")</f>
-        <v>M1 Autenticación</v>
+        <v>M4 Reservas</v>
       </c>
       <c r="D50" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A50,Requerimientos!$A:$A,0)),"")</f>
@@ -6575,11 +6674,11 @@
       </c>
       <c r="B51" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A51,Requerimientos!$A:$A,0)),"")</f>
-        <v>Los mensajes de chat persisten con fecha y hora</v>
+        <v>Un mismo cliente no puede tener reservas con fechas de alojamiento superpuestas</v>
       </c>
       <c r="C51" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A51,Requerimientos!$A:$A,0)),"")</f>
-        <v>M7 Chat</v>
+        <v>M4 Reservas</v>
       </c>
       <c r="D51" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A51,Requerimientos!$A:$A,0)),"")</f>
@@ -6608,11 +6707,11 @@
       </c>
       <c r="B52" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A52,Requerimientos!$A:$A,0)),"")</f>
-        <v>Las contraseñas nunca se almacenan en texto plano</v>
+        <v>Login único: tras autenticar se resuelve el rol y se navega al flujo correspondiente</v>
       </c>
       <c r="C52" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A52,Requerimientos!$A:$A,0)),"")</f>
-        <v>M10 Calidad</v>
+        <v>M1 Autenticación</v>
       </c>
       <c r="D52" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A52,Requerimientos!$A:$A,0)),"")</f>
@@ -6628,7 +6727,7 @@
       </c>
       <c r="G52" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$K:$K,MATCH($A52,Requerimientos!$A:$A,0)),"")</f>
-        <v>NA</v>
+        <v>Sí</v>
       </c>
       <c r="H52" s="24">
         <f>IFERROR(INDEX(Requerimientos!$L:$L,MATCH($A52,Requerimientos!$A:$A,0)),"")</f>
@@ -6641,11 +6740,11 @@
       </c>
       <c r="B53" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A53,Requerimientos!$A:$A,0)),"")</f>
-        <v>Las operaciones están restringidas según el rol autenticado</v>
+        <v>Los mensajes de chat persisten con fecha y hora</v>
       </c>
       <c r="C53" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A53,Requerimientos!$A:$A,0)),"")</f>
-        <v>M10 Calidad</v>
+        <v>M7 Chat</v>
       </c>
       <c r="D53" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A53,Requerimientos!$A:$A,0)),"")</f>
@@ -6661,7 +6760,7 @@
       </c>
       <c r="G53" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$K:$K,MATCH($A53,Requerimientos!$A:$A,0)),"")</f>
-        <v>NA</v>
+        <v>Sí</v>
       </c>
       <c r="H53" s="24">
         <f>IFERROR(INDEX(Requerimientos!$L:$L,MATCH($A53,Requerimientos!$A:$A,0)),"")</f>
@@ -6674,7 +6773,7 @@
       </c>
       <c r="B54" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A54,Requerimientos!$A:$A,0)),"")</f>
-        <v>Un cliente solo accede a sus propios datos</v>
+        <v>Las contraseñas nunca se almacenan en texto plano</v>
       </c>
       <c r="C54" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A54,Requerimientos!$A:$A,0)),"")</f>
@@ -6703,11 +6802,11 @@
     </row>
     <row r="55" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A55" s="26" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B55" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A55,Requerimientos!$A:$A,0)),"")</f>
-        <v>La persistencia de la app principal es una base de datos NoSQL</v>
+        <v>Las operaciones están restringidas según el rol autenticado</v>
       </c>
       <c r="C55" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A55,Requerimientos!$A:$A,0)),"")</f>
@@ -6736,11 +6835,11 @@
     </row>
     <row r="56" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A56" s="26" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B56" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A56,Requerimientos!$A:$A,0)),"")</f>
-        <v>El sistema registra los eventos relevantes en logs consultables por el Superadmin</v>
+        <v>Un cliente solo accede a sus propios datos</v>
       </c>
       <c r="C56" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A56,Requerimientos!$A:$A,0)),"")</f>
@@ -6748,7 +6847,7 @@
       </c>
       <c r="D56" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A56,Requerimientos!$A:$A,0)),"")</f>
-        <v>Media</v>
+        <v>Alta</v>
       </c>
       <c r="E56" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$I:$I,MATCH($A56,Requerimientos!$A:$A,0)),"")</f>
@@ -6769,11 +6868,11 @@
     </row>
     <row r="57" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A57" s="26" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B57" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A57,Requerimientos!$A:$A,0)),"")</f>
-        <v>La ubicación del taxista se actualiza periódicamente durante un servicio activo</v>
+        <v>La persistencia de la app principal es una base de datos NoSQL</v>
       </c>
       <c r="C57" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A57,Requerimientos!$A:$A,0)),"")</f>
@@ -6785,7 +6884,7 @@
       </c>
       <c r="E57" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$I:$I,MATCH($A57,Requerimientos!$A:$A,0)),"")</f>
-        <v>Lab 7</v>
+        <v>Lab 6</v>
       </c>
       <c r="F57" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$J:$J,MATCH($A57,Requerimientos!$A:$A,0)),"")</f>
@@ -6806,7 +6905,7 @@
       </c>
       <c r="B58" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A58,Requerimientos!$A:$A,0)),"")</f>
-        <v>Si la API de taxistas está caída la app lo informa sin afectar el resto del sistema</v>
+        <v>El sistema registra los eventos relevantes en logs consultables por el Superadmin</v>
       </c>
       <c r="C58" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A58,Requerimientos!$A:$A,0)),"")</f>
@@ -6814,11 +6913,11 @@
       </c>
       <c r="D58" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A58,Requerimientos!$A:$A,0)),"")</f>
-        <v>Alta</v>
+        <v>Media</v>
       </c>
       <c r="E58" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$I:$I,MATCH($A58,Requerimientos!$A:$A,0)),"")</f>
-        <v>Lab 7</v>
+        <v>Lab 6</v>
       </c>
       <c r="F58" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$J:$J,MATCH($A58,Requerimientos!$A:$A,0)),"")</f>
@@ -6835,11 +6934,11 @@
     </row>
     <row r="59" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A59" s="26" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B59" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A59,Requerimientos!$A:$A,0)),"")</f>
-        <v>La app móvil no accede directamente a la base de datos del sistema de taxistas</v>
+        <v>La ubicación del taxista se actualiza periódicamente durante un servicio activo</v>
       </c>
       <c r="C59" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A59,Requerimientos!$A:$A,0)),"")</f>
@@ -6851,7 +6950,7 @@
       </c>
       <c r="E59" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$I:$I,MATCH($A59,Requerimientos!$A:$A,0)),"")</f>
-        <v>App web</v>
+        <v>Lab 7</v>
       </c>
       <c r="F59" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$J:$J,MATCH($A59,Requerimientos!$A:$A,0)),"")</f>
@@ -6866,18 +6965,84 @@
         <v>0</v>
       </c>
     </row>
+    <row r="60" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="26" t="s">
+        <v>291</v>
+      </c>
+      <c r="B60" s="3" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A60,Requerimientos!$A:$A,0)),"")</f>
+        <v>Si la API de taxistas está caída la app lo informa sin afectar el resto del sistema</v>
+      </c>
+      <c r="C60" s="24" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A60,Requerimientos!$A:$A,0)),"")</f>
+        <v>M10 Calidad</v>
+      </c>
+      <c r="D60" s="24" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A60,Requerimientos!$A:$A,0)),"")</f>
+        <v>Alta</v>
+      </c>
+      <c r="E60" s="24" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$I:$I,MATCH($A60,Requerimientos!$A:$A,0)),"")</f>
+        <v>Lab 7</v>
+      </c>
+      <c r="F60" s="24" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$J:$J,MATCH($A60,Requerimientos!$A:$A,0)),"")</f>
+        <v>Pendiente</v>
+      </c>
+      <c r="G60" s="24" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$K:$K,MATCH($A60,Requerimientos!$A:$A,0)),"")</f>
+        <v>NA</v>
+      </c>
+      <c r="H60" s="24">
+        <f>IFERROR(INDEX(Requerimientos!$L:$L,MATCH($A60,Requerimientos!$A:$A,0)),"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="26" t="s">
+        <v>295</v>
+      </c>
+      <c r="B61" s="3" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A61,Requerimientos!$A:$A,0)),"")</f>
+        <v>La app móvil no accede directamente a la base de datos del sistema de taxistas</v>
+      </c>
+      <c r="C61" s="24" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A61,Requerimientos!$A:$A,0)),"")</f>
+        <v>M10 Calidad</v>
+      </c>
+      <c r="D61" s="24" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A61,Requerimientos!$A:$A,0)),"")</f>
+        <v>Alta</v>
+      </c>
+      <c r="E61" s="24" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$I:$I,MATCH($A61,Requerimientos!$A:$A,0)),"")</f>
+        <v>App web</v>
+      </c>
+      <c r="F61" s="24" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$J:$J,MATCH($A61,Requerimientos!$A:$A,0)),"")</f>
+        <v>Pendiente</v>
+      </c>
+      <c r="G61" s="24" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$K:$K,MATCH($A61,Requerimientos!$A:$A,0)),"")</f>
+        <v>NA</v>
+      </c>
+      <c r="H61" s="24">
+        <f>IFERROR(INDEX(Requerimientos!$L:$L,MATCH($A61,Requerimientos!$A:$A,0)),"")</f>
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A46:H46"/>
     <mergeCell ref="A6:H6"/>
+    <mergeCell ref="A34:H34"/>
+    <mergeCell ref="A48:H48"/>
     <mergeCell ref="A3:H3"/>
-    <mergeCell ref="A24:H24"/>
+    <mergeCell ref="A25:H25"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A13:H13"/>
-    <mergeCell ref="A33:H33"/>
   </mergeCells>
-  <conditionalFormatting sqref="F6:F59">
+  <conditionalFormatting sqref="F6:F61">
     <cfRule type="cellIs" dxfId="14" priority="1" operator="equal">
       <formula>"Hecho"</formula>
     </cfRule>
@@ -6891,7 +7056,7 @@
       <formula>"Pendiente"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G6:G59">
+  <conditionalFormatting sqref="G6:G61">
     <cfRule type="cellIs" dxfId="10" priority="5" operator="equal">
       <formula>"Sí"</formula>
     </cfRule>
@@ -6902,7 +7067,7 @@
       <formula>"No"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D6:D59">
+  <conditionalFormatting sqref="D6:D61">
     <cfRule type="cellIs" dxfId="7" priority="8" operator="equal">
       <formula>"Alta"</formula>
     </cfRule>
@@ -6920,7 +7085,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H115"/>
+  <dimension ref="A1:H125"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" outlineLevelRow="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
@@ -6935,7 +7100,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="27" t="s">
-        <v>300</v>
+        <v>307</v>
       </c>
       <c r="B1" s="28"/>
       <c r="C1" s="28"/>
@@ -6947,7 +7112,7 @@
     </row>
     <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="33" t="s">
-        <v>301</v>
+        <v>308</v>
       </c>
       <c r="B2" s="34"/>
       <c r="C2" s="34"/>
@@ -6959,7 +7124,7 @@
     </row>
     <row r="3" spans="1:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="36" t="s">
-        <v>302</v>
+        <v>309</v>
       </c>
       <c r="B3" s="32"/>
       <c r="C3" s="32"/>
@@ -6997,7 +7162,7 @@
     </row>
     <row r="6" spans="1:8" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="29" t="s">
-        <v>303</v>
+        <v>310</v>
       </c>
       <c r="B6" s="30"/>
       <c r="C6" s="30"/>
@@ -7310,7 +7475,7 @@
       </c>
       <c r="B16" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A16,Requerimientos!$A:$A,0)),"")</f>
-        <v>Añadir cobros adicionales por daños con monto motivo y observación</v>
+        <v>Establecer el monto mínimo de reserva que da derecho al taxi gratuito al aeropuerto</v>
       </c>
       <c r="C16" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$C:$C,MATCH($A16,Requerimientos!$A:$A,0)),"")</f>
@@ -7318,11 +7483,11 @@
       </c>
       <c r="D16" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A16,Requerimientos!$A:$A,0)),"")</f>
-        <v>M5 Pagos y cobros</v>
+        <v>M8 Taxi</v>
       </c>
       <c r="E16" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A16,Requerimientos!$A:$A,0)),"")</f>
-        <v>Media</v>
+        <v>Alta</v>
       </c>
       <c r="F16" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$H:$H,MATCH($A16,Requerimientos!$A:$A,0)),"")</f>
@@ -7339,11 +7504,11 @@
     </row>
     <row r="17" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A17" s="26" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B17" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A17,Requerimientos!$A:$A,0)),"")</f>
-        <v>Reporte de ingresos por servicios adicionales ordenado de menor a mayor</v>
+        <v>Añadir cobros adicionales por daños con monto motivo y observación</v>
       </c>
       <c r="C17" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$C:$C,MATCH($A17,Requerimientos!$A:$A,0)),"")</f>
@@ -7351,7 +7516,7 @@
       </c>
       <c r="D17" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A17,Requerimientos!$A:$A,0)),"")</f>
-        <v>M9 Reportes y logs</v>
+        <v>M5 Pagos y cobros</v>
       </c>
       <c r="E17" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A17,Requerimientos!$A:$A,0)),"")</f>
@@ -7359,7 +7524,7 @@
       </c>
       <c r="F17" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$H:$H,MATCH($A17,Requerimientos!$A:$A,0)),"")</f>
-        <v>L3  ·  L4  ·  L6</v>
+        <v>L3  ·  L6</v>
       </c>
       <c r="G17" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$I:$I,MATCH($A17,Requerimientos!$A:$A,0)),"")</f>
@@ -7372,11 +7537,11 @@
     </row>
     <row r="18" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A18" s="26" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B18" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A18,Requerimientos!$A:$A,0)),"")</f>
-        <v>Registrar la ubicación del hotel y los lugares históricos cercanos</v>
+        <v>Reporte de ingresos por servicios adicionales ordenado de menor a mayor</v>
       </c>
       <c r="C18" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$C:$C,MATCH($A18,Requerimientos!$A:$A,0)),"")</f>
@@ -7384,19 +7549,19 @@
       </c>
       <c r="D18" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A18,Requerimientos!$A:$A,0)),"")</f>
-        <v>M3 Catálogo</v>
+        <v>M9 Reportes y logs</v>
       </c>
       <c r="E18" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A18,Requerimientos!$A:$A,0)),"")</f>
-        <v>Alta</v>
+        <v>Media</v>
       </c>
       <c r="F18" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$H:$H,MATCH($A18,Requerimientos!$A:$A,0)),"")</f>
-        <v>L3  ·  L6  ·  L7</v>
+        <v>L3  ·  L4  ·  L6</v>
       </c>
       <c r="G18" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$I:$I,MATCH($A18,Requerimientos!$A:$A,0)),"")</f>
-        <v>Lab 7</v>
+        <v>Lab 6</v>
       </c>
       <c r="H18" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$J:$J,MATCH($A18,Requerimientos!$A:$A,0)),"")</f>
@@ -7405,11 +7570,11 @@
     </row>
     <row r="19" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A19" s="26" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B19" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A19,Requerimientos!$A:$A,0)),"")</f>
-        <v>Ver el estado del taxista asignado en camino a recoger y llegó al destino</v>
+        <v>Registrar la ubicación del hotel y los lugares históricos cercanos</v>
       </c>
       <c r="C19" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$C:$C,MATCH($A19,Requerimientos!$A:$A,0)),"")</f>
@@ -7417,11 +7582,11 @@
       </c>
       <c r="D19" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A19,Requerimientos!$A:$A,0)),"")</f>
-        <v>M8 Taxi</v>
+        <v>M3 Catálogo</v>
       </c>
       <c r="E19" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A19,Requerimientos!$A:$A,0)),"")</f>
-        <v>Media</v>
+        <v>Alta</v>
       </c>
       <c r="F19" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$H:$H,MATCH($A19,Requerimientos!$A:$A,0)),"")</f>
@@ -7438,31 +7603,31 @@
     </row>
     <row r="20" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A20" s="26" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B20" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A20,Requerimientos!$A:$A,0)),"")</f>
-        <v>Acceder a la app móvil una vez habilitado</v>
+        <v>Ver el estado del taxista asignado en camino a recoger y llegó al destino</v>
       </c>
       <c r="C20" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$C:$C,MATCH($A20,Requerimientos!$A:$A,0)),"")</f>
-        <v>Taxista</v>
+        <v>Administrador de hotel</v>
       </c>
       <c r="D20" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A20,Requerimientos!$A:$A,0)),"")</f>
-        <v>M1 Autenticación</v>
+        <v>M8 Taxi</v>
       </c>
       <c r="E20" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A20,Requerimientos!$A:$A,0)),"")</f>
-        <v>Alta</v>
+        <v>Media</v>
       </c>
       <c r="F20" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$H:$H,MATCH($A20,Requerimientos!$A:$A,0)),"")</f>
-        <v>L3  ·  L5  ·  L6</v>
+        <v>L3  ·  L6  ·  L7</v>
       </c>
       <c r="G20" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$I:$I,MATCH($A20,Requerimientos!$A:$A,0)),"")</f>
-        <v>Lab 6</v>
+        <v>Lab 7</v>
       </c>
       <c r="H20" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$J:$J,MATCH($A20,Requerimientos!$A:$A,0)),"")</f>
@@ -7471,11 +7636,11 @@
     </row>
     <row r="21" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A21" s="26" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B21" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A21,Requerimientos!$A:$A,0)),"")</f>
-        <v>Ver hoteles y pedidos disponibles</v>
+        <v>Acceder a la app móvil una vez habilitado</v>
       </c>
       <c r="C21" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$C:$C,MATCH($A21,Requerimientos!$A:$A,0)),"")</f>
@@ -7483,7 +7648,7 @@
       </c>
       <c r="D21" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A21,Requerimientos!$A:$A,0)),"")</f>
-        <v>M8 Taxi</v>
+        <v>M1 Autenticación</v>
       </c>
       <c r="E21" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A21,Requerimientos!$A:$A,0)),"")</f>
@@ -7491,7 +7656,7 @@
       </c>
       <c r="F21" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$H:$H,MATCH($A21,Requerimientos!$A:$A,0)),"")</f>
-        <v>L3  ·  L4  ·  L5  ·  L6</v>
+        <v>L3  ·  L5  ·  L6</v>
       </c>
       <c r="G21" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$I:$I,MATCH($A21,Requerimientos!$A:$A,0)),"")</f>
@@ -7504,11 +7669,11 @@
     </row>
     <row r="22" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A22" s="26" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B22" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A22,Requerimientos!$A:$A,0)),"")</f>
-        <v>Aceptar un pedido que deja de estar disponible para los demás</v>
+        <v>Ver hoteles y pedidos disponibles</v>
       </c>
       <c r="C22" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$C:$C,MATCH($A22,Requerimientos!$A:$A,0)),"")</f>
@@ -7524,7 +7689,7 @@
       </c>
       <c r="F22" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$H:$H,MATCH($A22,Requerimientos!$A:$A,0)),"")</f>
-        <v>L3  ·  L6</v>
+        <v>L3  ·  L4  ·  L5  ·  L6</v>
       </c>
       <c r="G22" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$I:$I,MATCH($A22,Requerimientos!$A:$A,0)),"")</f>
@@ -7541,7 +7706,7 @@
       </c>
       <c r="B23" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A23,Requerimientos!$A:$A,0)),"")</f>
-        <v>Actualizar los estados del servicio</v>
+        <v>Aceptar un pedido que deja de estar disponible para los demás</v>
       </c>
       <c r="C23" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$C:$C,MATCH($A23,Requerimientos!$A:$A,0)),"")</f>
@@ -7570,11 +7735,11 @@
     </row>
     <row r="24" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A24" s="26" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="B24" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A24,Requerimientos!$A:$A,0)),"")</f>
-        <v>Registrar FINALIZADO únicamente escaneando el QR del cliente</v>
+        <v>Actualizar los estados del servicio</v>
       </c>
       <c r="C24" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$C:$C,MATCH($A24,Requerimientos!$A:$A,0)),"")</f>
@@ -7590,11 +7755,11 @@
       </c>
       <c r="F24" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$H:$H,MATCH($A24,Requerimientos!$A:$A,0)),"")</f>
-        <v>L3  ·  L7</v>
+        <v>L3  ·  L6</v>
       </c>
       <c r="G24" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$I:$I,MATCH($A24,Requerimientos!$A:$A,0)),"")</f>
-        <v>Lab 7</v>
+        <v>Lab 6</v>
       </c>
       <c r="H24" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$J:$J,MATCH($A24,Requerimientos!$A:$A,0)),"")</f>
@@ -7603,19 +7768,19 @@
     </row>
     <row r="25" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A25" s="26" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="B25" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A25,Requerimientos!$A:$A,0)),"")</f>
-        <v>Autoregistrarse y quedar habilitado automáticamente</v>
+        <v>Registrar FINALIZADO únicamente escaneando el QR del cliente</v>
       </c>
       <c r="C25" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$C:$C,MATCH($A25,Requerimientos!$A:$A,0)),"")</f>
-        <v>Cliente</v>
+        <v>Taxista</v>
       </c>
       <c r="D25" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A25,Requerimientos!$A:$A,0)),"")</f>
-        <v>M1 Autenticación</v>
+        <v>M8 Taxi</v>
       </c>
       <c r="E25" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A25,Requerimientos!$A:$A,0)),"")</f>
@@ -7623,11 +7788,11 @@
       </c>
       <c r="F25" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$H:$H,MATCH($A25,Requerimientos!$A:$A,0)),"")</f>
-        <v>L3  ·  L5  ·  L6</v>
+        <v>L3  ·  L7</v>
       </c>
       <c r="G25" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$I:$I,MATCH($A25,Requerimientos!$A:$A,0)),"")</f>
-        <v>Lab 6</v>
+        <v>Lab 7</v>
       </c>
       <c r="H25" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$J:$J,MATCH($A25,Requerimientos!$A:$A,0)),"")</f>
@@ -7640,7 +7805,7 @@
       </c>
       <c r="B26" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A26,Requerimientos!$A:$A,0)),"")</f>
-        <v>Consultar hoteles habitaciones servicios disponibilidad y valoraciones</v>
+        <v>Autoregistrarse y quedar habilitado automáticamente</v>
       </c>
       <c r="C26" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$C:$C,MATCH($A26,Requerimientos!$A:$A,0)),"")</f>
@@ -7648,7 +7813,7 @@
       </c>
       <c r="D26" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A26,Requerimientos!$A:$A,0)),"")</f>
-        <v>M3 Catálogo</v>
+        <v>M1 Autenticación</v>
       </c>
       <c r="E26" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A26,Requerimientos!$A:$A,0)),"")</f>
@@ -7656,7 +7821,7 @@
       </c>
       <c r="F26" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$H:$H,MATCH($A26,Requerimientos!$A:$A,0)),"")</f>
-        <v>L3  ·  L4  ·  L6</v>
+        <v>L3  ·  L5  ·  L6</v>
       </c>
       <c r="G26" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$I:$I,MATCH($A26,Requerimientos!$A:$A,0)),"")</f>
@@ -7669,11 +7834,11 @@
     </row>
     <row r="27" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A27" s="26" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B27" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A27,Requerimientos!$A:$A,0)),"")</f>
-        <v>Reservar con tarjeta de crédito o débito simulada</v>
+        <v>Consultar hoteles habitaciones servicios disponibilidad y valoraciones</v>
       </c>
       <c r="C27" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$C:$C,MATCH($A27,Requerimientos!$A:$A,0)),"")</f>
@@ -7681,7 +7846,7 @@
       </c>
       <c r="D27" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A27,Requerimientos!$A:$A,0)),"")</f>
-        <v>M4 Reservas</v>
+        <v>M3 Catálogo</v>
       </c>
       <c r="E27" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A27,Requerimientos!$A:$A,0)),"")</f>
@@ -7689,7 +7854,7 @@
       </c>
       <c r="F27" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$H:$H,MATCH($A27,Requerimientos!$A:$A,0)),"")</f>
-        <v>L3  ·  L6</v>
+        <v>L3  ·  L4  ·  L6</v>
       </c>
       <c r="G27" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$I:$I,MATCH($A27,Requerimientos!$A:$A,0)),"")</f>
@@ -7702,11 +7867,11 @@
     </row>
     <row r="28" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A28" s="26" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B28" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A28,Requerimientos!$A:$A,0)),"")</f>
-        <v>Hacer checkout y registrar valoración y observaciones obligatorias</v>
+        <v>Reservar con tarjeta de crédito o débito simulada</v>
       </c>
       <c r="C28" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$C:$C,MATCH($A28,Requerimientos!$A:$A,0)),"")</f>
@@ -7714,7 +7879,7 @@
       </c>
       <c r="D28" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A28,Requerimientos!$A:$A,0)),"")</f>
-        <v>M6 Checkout y valoraciones</v>
+        <v>M4 Reservas</v>
       </c>
       <c r="E28" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A28,Requerimientos!$A:$A,0)),"")</f>
@@ -7735,11 +7900,11 @@
     </row>
     <row r="29" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A29" s="26" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="B29" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A29,Requerimientos!$A:$A,0)),"")</f>
-        <v>Chat privado con el hotel entre la confirmación de la reserva y el fin del checkout</v>
+        <v>Hacer checkout y registrar valoración y observaciones obligatorias</v>
       </c>
       <c r="C29" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$C:$C,MATCH($A29,Requerimientos!$A:$A,0)),"")</f>
@@ -7747,7 +7912,7 @@
       </c>
       <c r="D29" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A29,Requerimientos!$A:$A,0)),"")</f>
-        <v>M7 Chat</v>
+        <v>M6 Checkout y valoraciones</v>
       </c>
       <c r="E29" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A29,Requerimientos!$A:$A,0)),"")</f>
@@ -7755,7 +7920,7 @@
       </c>
       <c r="F29" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$H:$H,MATCH($A29,Requerimientos!$A:$A,0)),"")</f>
-        <v>L3  ·  L4  ·  L6</v>
+        <v>L3  ·  L6</v>
       </c>
       <c r="G29" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$I:$I,MATCH($A29,Requerimientos!$A:$A,0)),"")</f>
@@ -7768,11 +7933,11 @@
     </row>
     <row r="30" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A30" s="26" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="B30" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A30,Requerimientos!$A:$A,0)),"")</f>
-        <v>Ver el historial de sus reservas</v>
+        <v>Recibir notificación cuando se le hace el cobro</v>
       </c>
       <c r="C30" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$C:$C,MATCH($A30,Requerimientos!$A:$A,0)),"")</f>
@@ -7780,15 +7945,15 @@
       </c>
       <c r="D30" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A30,Requerimientos!$A:$A,0)),"")</f>
-        <v>M4 Reservas</v>
+        <v>M5 Pagos y cobros</v>
       </c>
       <c r="E30" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A30,Requerimientos!$A:$A,0)),"")</f>
-        <v>Media</v>
+        <v>Alta</v>
       </c>
       <c r="F30" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$H:$H,MATCH($A30,Requerimientos!$A:$A,0)),"")</f>
-        <v>L3  ·  L4  ·  L6</v>
+        <v>L3  ·  L5  ·  L6</v>
       </c>
       <c r="G30" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$I:$I,MATCH($A30,Requerimientos!$A:$A,0)),"")</f>
@@ -7801,11 +7966,11 @@
     </row>
     <row r="31" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A31" s="26" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="B31" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A31,Requerimientos!$A:$A,0)),"")</f>
-        <v>Solicitar el taxi gratuito al aeropuerto si la reserva alcanza el monto mínimo</v>
+        <v>Chat privado con el hotel entre la confirmación de la reserva y el fin del checkout</v>
       </c>
       <c r="C31" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$C:$C,MATCH($A31,Requerimientos!$A:$A,0)),"")</f>
@@ -7813,7 +7978,7 @@
       </c>
       <c r="D31" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A31,Requerimientos!$A:$A,0)),"")</f>
-        <v>M8 Taxi</v>
+        <v>M7 Chat</v>
       </c>
       <c r="E31" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A31,Requerimientos!$A:$A,0)),"")</f>
@@ -7821,11 +7986,11 @@
       </c>
       <c r="F31" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$H:$H,MATCH($A31,Requerimientos!$A:$A,0)),"")</f>
-        <v>L3  ·  L6  ·  L7</v>
+        <v>L3  ·  L4  ·  L6</v>
       </c>
       <c r="G31" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$I:$I,MATCH($A31,Requerimientos!$A:$A,0)),"")</f>
-        <v>Lab 7</v>
+        <v>Lab 6</v>
       </c>
       <c r="H31" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$J:$J,MATCH($A31,Requerimientos!$A:$A,0)),"")</f>
@@ -7834,11 +7999,11 @@
     </row>
     <row r="32" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A32" s="26" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="B32" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A32,Requerimientos!$A:$A,0)),"")</f>
-        <v>Ver datos vehículo valoración y ubicación del taxista en un mapa</v>
+        <v>Ver el historial de sus reservas</v>
       </c>
       <c r="C32" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$C:$C,MATCH($A32,Requerimientos!$A:$A,0)),"")</f>
@@ -7846,19 +8011,19 @@
       </c>
       <c r="D32" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A32,Requerimientos!$A:$A,0)),"")</f>
-        <v>M8 Taxi</v>
+        <v>M4 Reservas</v>
       </c>
       <c r="E32" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A32,Requerimientos!$A:$A,0)),"")</f>
-        <v>Alta</v>
+        <v>Media</v>
       </c>
       <c r="F32" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$H:$H,MATCH($A32,Requerimientos!$A:$A,0)),"")</f>
-        <v>L3  ·  L7</v>
+        <v>L3  ·  L4  ·  L6</v>
       </c>
       <c r="G32" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$I:$I,MATCH($A32,Requerimientos!$A:$A,0)),"")</f>
-        <v>Lab 7</v>
+        <v>Lab 6</v>
       </c>
       <c r="H32" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$J:$J,MATCH($A32,Requerimientos!$A:$A,0)),"")</f>
@@ -7867,11 +8032,11 @@
     </row>
     <row r="33" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A33" s="26" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="B33" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A33,Requerimientos!$A:$A,0)),"")</f>
-        <v>Recibir el QR del hotel y mostrarlo al llegar</v>
+        <v>Consultar los lugares históricos cercanos al hotel</v>
       </c>
       <c r="C33" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$C:$C,MATCH($A33,Requerimientos!$A:$A,0)),"")</f>
@@ -7879,19 +8044,19 @@
       </c>
       <c r="D33" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A33,Requerimientos!$A:$A,0)),"")</f>
-        <v>M8 Taxi</v>
+        <v>M3 Catálogo</v>
       </c>
       <c r="E33" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A33,Requerimientos!$A:$A,0)),"")</f>
-        <v>Alta</v>
+        <v>Media</v>
       </c>
       <c r="F33" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$H:$H,MATCH($A33,Requerimientos!$A:$A,0)),"")</f>
-        <v>L3  ·  L7</v>
+        <v>L3  ·  L4  ·  L6</v>
       </c>
       <c r="G33" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$I:$I,MATCH($A33,Requerimientos!$A:$A,0)),"")</f>
-        <v>Lab 7</v>
+        <v>Lab 6</v>
       </c>
       <c r="H33" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$J:$J,MATCH($A33,Requerimientos!$A:$A,0)),"")</f>
@@ -7900,11 +8065,11 @@
     </row>
     <row r="34" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A34" s="26" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="B34" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A34,Requerimientos!$A:$A,0)),"")</f>
-        <v>Calificar al taxista al finalizar el servicio</v>
+        <v>Solicitar el taxi gratuito al aeropuerto si la reserva alcanza el monto mínimo</v>
       </c>
       <c r="C34" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$C:$C,MATCH($A34,Requerimientos!$A:$A,0)),"")</f>
@@ -7916,7 +8081,7 @@
       </c>
       <c r="E34" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A34,Requerimientos!$A:$A,0)),"")</f>
-        <v>Media</v>
+        <v>Alta</v>
       </c>
       <c r="F34" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$H:$H,MATCH($A34,Requerimientos!$A:$A,0)),"")</f>
@@ -7933,19 +8098,19 @@
     </row>
     <row r="35" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A35" s="26" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="B35" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A35,Requerimientos!$A:$A,0)),"")</f>
-        <v>La app móvil es Android nativa en Java con versión mínima Android 14 API 34</v>
+        <v>Ver datos vehículo valoración y ubicación del taxista en un mapa</v>
       </c>
       <c r="C35" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$C:$C,MATCH($A35,Requerimientos!$A:$A,0)),"")</f>
-        <v>Transversal</v>
+        <v>Cliente</v>
       </c>
       <c r="D35" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A35,Requerimientos!$A:$A,0)),"")</f>
-        <v>M10 Calidad</v>
+        <v>M8 Taxi</v>
       </c>
       <c r="E35" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A35,Requerimientos!$A:$A,0)),"")</f>
@@ -7953,11 +8118,11 @@
       </c>
       <c r="F35" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$H:$H,MATCH($A35,Requerimientos!$A:$A,0)),"")</f>
-        <v>L3</v>
+        <v>L3  ·  L7</v>
       </c>
       <c r="G35" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$I:$I,MATCH($A35,Requerimientos!$A:$A,0)),"")</f>
-        <v>Lab 3</v>
+        <v>Lab 7</v>
       </c>
       <c r="H35" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$J:$J,MATCH($A35,Requerimientos!$A:$A,0)),"")</f>
@@ -7966,19 +8131,19 @@
     </row>
     <row r="36" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A36" s="26" t="s">
-        <v>259</v>
+        <v>246</v>
       </c>
       <c r="B36" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A36,Requerimientos!$A:$A,0)),"")</f>
-        <v>Login único: tras autenticar se resuelve el rol y se navega al flujo correspondiente</v>
+        <v>Recibir el QR del hotel y mostrarlo al llegar</v>
       </c>
       <c r="C36" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$C:$C,MATCH($A36,Requerimientos!$A:$A,0)),"")</f>
-        <v>Transversal</v>
+        <v>Cliente</v>
       </c>
       <c r="D36" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A36,Requerimientos!$A:$A,0)),"")</f>
-        <v>M1 Autenticación</v>
+        <v>M8 Taxi</v>
       </c>
       <c r="E36" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A36,Requerimientos!$A:$A,0)),"")</f>
@@ -7986,44 +8151,98 @@
       </c>
       <c r="F36" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$H:$H,MATCH($A36,Requerimientos!$A:$A,0)),"")</f>
-        <v>L3  ·  L6</v>
+        <v>L3  ·  L7</v>
       </c>
       <c r="G36" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$I:$I,MATCH($A36,Requerimientos!$A:$A,0)),"")</f>
-        <v>Lab 6</v>
+        <v>Lab 7</v>
       </c>
       <c r="H36" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$J:$J,MATCH($A36,Requerimientos!$A:$A,0)),"")</f>
         <v>Pendiente</v>
       </c>
     </row>
-    <row r="38" spans="1:8" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="29" t="s">
-        <v>304</v>
-      </c>
-      <c r="B38" s="30"/>
-      <c r="C38" s="30"/>
-      <c r="D38" s="30"/>
-      <c r="E38" s="30"/>
-      <c r="F38" s="30"/>
-      <c r="G38" s="30"/>
-      <c r="H38" s="30"/>
+    <row r="37" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="26" t="s">
+        <v>249</v>
+      </c>
+      <c r="B37" s="3" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A37,Requerimientos!$A:$A,0)),"")</f>
+        <v>Calificar al taxista al finalizar el servicio</v>
+      </c>
+      <c r="C37" s="24" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$C:$C,MATCH($A37,Requerimientos!$A:$A,0)),"")</f>
+        <v>Cliente</v>
+      </c>
+      <c r="D37" s="24" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A37,Requerimientos!$A:$A,0)),"")</f>
+        <v>M8 Taxi</v>
+      </c>
+      <c r="E37" s="24" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A37,Requerimientos!$A:$A,0)),"")</f>
+        <v>Media</v>
+      </c>
+      <c r="F37" s="24" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$H:$H,MATCH($A37,Requerimientos!$A:$A,0)),"")</f>
+        <v>L3  ·  L6  ·  L7</v>
+      </c>
+      <c r="G37" s="24" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$I:$I,MATCH($A37,Requerimientos!$A:$A,0)),"")</f>
+        <v>Lab 7</v>
+      </c>
+      <c r="H37" s="24" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$J:$J,MATCH($A37,Requerimientos!$A:$A,0)),"")</f>
+        <v>Pendiente</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="26" t="s">
+        <v>252</v>
+      </c>
+      <c r="B38" s="3" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A38,Requerimientos!$A:$A,0)),"")</f>
+        <v>La app móvil es Android nativa en Java con versión mínima Android 14 API 34</v>
+      </c>
+      <c r="C38" s="24" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$C:$C,MATCH($A38,Requerimientos!$A:$A,0)),"")</f>
+        <v>Transversal</v>
+      </c>
+      <c r="D38" s="24" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A38,Requerimientos!$A:$A,0)),"")</f>
+        <v>M10 Calidad</v>
+      </c>
+      <c r="E38" s="24" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A38,Requerimientos!$A:$A,0)),"")</f>
+        <v>Alta</v>
+      </c>
+      <c r="F38" s="24" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$H:$H,MATCH($A38,Requerimientos!$A:$A,0)),"")</f>
+        <v>L3</v>
+      </c>
+      <c r="G38" s="24" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$I:$I,MATCH($A38,Requerimientos!$A:$A,0)),"")</f>
+        <v>Lab 3</v>
+      </c>
+      <c r="H38" s="24" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$J:$J,MATCH($A38,Requerimientos!$A:$A,0)),"")</f>
+        <v>Pendiente</v>
+      </c>
     </row>
     <row r="39" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A39" s="26" t="s">
-        <v>126</v>
+        <v>258</v>
       </c>
       <c r="B39" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A39,Requerimientos!$A:$A,0)),"")</f>
-        <v>Activar y desactivar administradores de hotel taxistas y clientes</v>
+        <v>Una habitación no puede tener reservas de distintos clientes con períodos superpuestos</v>
       </c>
       <c r="C39" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$C:$C,MATCH($A39,Requerimientos!$A:$A,0)),"")</f>
-        <v>Superadmin</v>
+        <v>Transversal</v>
       </c>
       <c r="D39" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A39,Requerimientos!$A:$A,0)),"")</f>
-        <v>M2 Gestión de usuarios</v>
+        <v>M4 Reservas</v>
       </c>
       <c r="E39" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A39,Requerimientos!$A:$A,0)),"")</f>
@@ -8031,7 +8250,7 @@
       </c>
       <c r="F39" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$H:$H,MATCH($A39,Requerimientos!$A:$A,0)),"")</f>
-        <v>L3  ·  L4  ·  L6</v>
+        <v>L3  ·  L6</v>
       </c>
       <c r="G39" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$I:$I,MATCH($A39,Requerimientos!$A:$A,0)),"")</f>
@@ -8044,19 +8263,19 @@
     </row>
     <row r="40" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A40" s="26" t="s">
-        <v>132</v>
+        <v>262</v>
       </c>
       <c r="B40" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A40,Requerimientos!$A:$A,0)),"")</f>
-        <v>Registrar hoteles y asignar un administrador a cada uno</v>
+        <v>Un mismo cliente no puede tener reservas con fechas de alojamiento superpuestas</v>
       </c>
       <c r="C40" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$C:$C,MATCH($A40,Requerimientos!$A:$A,0)),"")</f>
-        <v>Superadmin</v>
+        <v>Transversal</v>
       </c>
       <c r="D40" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A40,Requerimientos!$A:$A,0)),"")</f>
-        <v>M2 Gestión de usuarios</v>
+        <v>M4 Reservas</v>
       </c>
       <c r="E40" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A40,Requerimientos!$A:$A,0)),"")</f>
@@ -8064,7 +8283,7 @@
       </c>
       <c r="F40" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$H:$H,MATCH($A40,Requerimientos!$A:$A,0)),"")</f>
-        <v>L3  ·  L4  ·  L6</v>
+        <v>L3  ·  L6</v>
       </c>
       <c r="G40" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$I:$I,MATCH($A40,Requerimientos!$A:$A,0)),"")</f>
@@ -8077,27 +8296,27 @@
     </row>
     <row r="41" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A41" s="26" t="s">
-        <v>135</v>
+        <v>265</v>
       </c>
       <c r="B41" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A41,Requerimientos!$A:$A,0)),"")</f>
-        <v>Generar el reporte de reservas por hotel</v>
+        <v>Login único: tras autenticar se resuelve el rol y se navega al flujo correspondiente</v>
       </c>
       <c r="C41" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$C:$C,MATCH($A41,Requerimientos!$A:$A,0)),"")</f>
-        <v>Superadmin</v>
+        <v>Transversal</v>
       </c>
       <c r="D41" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A41,Requerimientos!$A:$A,0)),"")</f>
-        <v>M9 Reportes y logs</v>
+        <v>M1 Autenticación</v>
       </c>
       <c r="E41" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A41,Requerimientos!$A:$A,0)),"")</f>
-        <v>Media</v>
+        <v>Alta</v>
       </c>
       <c r="F41" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$H:$H,MATCH($A41,Requerimientos!$A:$A,0)),"")</f>
-        <v>L3  ·  L4  ·  L6</v>
+        <v>L3  ·  L6</v>
       </c>
       <c r="G41" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$I:$I,MATCH($A41,Requerimientos!$A:$A,0)),"")</f>
@@ -8110,23 +8329,23 @@
     </row>
     <row r="42" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A42" s="26" t="s">
-        <v>138</v>
+        <v>268</v>
       </c>
       <c r="B42" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A42,Requerimientos!$A:$A,0)),"")</f>
-        <v>Consultar el visor de logs de eventos del sistema</v>
+        <v>Los mensajes de chat persisten con fecha y hora</v>
       </c>
       <c r="C42" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$C:$C,MATCH($A42,Requerimientos!$A:$A,0)),"")</f>
-        <v>Superadmin</v>
+        <v>Transversal</v>
       </c>
       <c r="D42" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A42,Requerimientos!$A:$A,0)),"")</f>
-        <v>M9 Reportes y logs</v>
+        <v>M7 Chat</v>
       </c>
       <c r="E42" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A42,Requerimientos!$A:$A,0)),"")</f>
-        <v>Media</v>
+        <v>Alta</v>
       </c>
       <c r="F42" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$H:$H,MATCH($A42,Requerimientos!$A:$A,0)),"")</f>
@@ -8141,87 +8360,33 @@
         <v>Pendiente</v>
       </c>
     </row>
-    <row r="43" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="26" t="s">
-        <v>145</v>
-      </c>
-      <c r="B43" s="3" t="str">
-        <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A43,Requerimientos!$A:$A,0)),"")</f>
-        <v>Subir fotos del hotel con un mínimo de 4</v>
-      </c>
-      <c r="C43" s="24" t="str">
-        <f>IFERROR(INDEX(Requerimientos!$C:$C,MATCH($A43,Requerimientos!$A:$A,0)),"")</f>
-        <v>Administrador de hotel</v>
-      </c>
-      <c r="D43" s="24" t="str">
-        <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A43,Requerimientos!$A:$A,0)),"")</f>
-        <v>M3 Catálogo</v>
-      </c>
-      <c r="E43" s="24" t="str">
-        <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A43,Requerimientos!$A:$A,0)),"")</f>
-        <v>Alta</v>
-      </c>
-      <c r="F43" s="24" t="str">
-        <f>IFERROR(INDEX(Requerimientos!$H:$H,MATCH($A43,Requerimientos!$A:$A,0)),"")</f>
-        <v>L3  ·  L4  ·  L5  ·  L6</v>
-      </c>
-      <c r="G43" s="24" t="str">
-        <f>IFERROR(INDEX(Requerimientos!$I:$I,MATCH($A43,Requerimientos!$A:$A,0)),"")</f>
-        <v>Lab 6</v>
-      </c>
-      <c r="H43" s="24" t="str">
-        <f>IFERROR(INDEX(Requerimientos!$J:$J,MATCH($A43,Requerimientos!$A:$A,0)),"")</f>
-        <v>Pendiente</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="26" t="s">
-        <v>151</v>
-      </c>
-      <c r="B44" s="3" t="str">
-        <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A44,Requerimientos!$A:$A,0)),"")</f>
-        <v>Registrar habitaciones con tipo capacidad de adultos y niños y tamaño en m2</v>
-      </c>
-      <c r="C44" s="24" t="str">
-        <f>IFERROR(INDEX(Requerimientos!$C:$C,MATCH($A44,Requerimientos!$A:$A,0)),"")</f>
-        <v>Administrador de hotel</v>
-      </c>
-      <c r="D44" s="24" t="str">
-        <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A44,Requerimientos!$A:$A,0)),"")</f>
-        <v>M3 Catálogo</v>
-      </c>
-      <c r="E44" s="24" t="str">
-        <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A44,Requerimientos!$A:$A,0)),"")</f>
-        <v>Alta</v>
-      </c>
-      <c r="F44" s="24" t="str">
-        <f>IFERROR(INDEX(Requerimientos!$H:$H,MATCH($A44,Requerimientos!$A:$A,0)),"")</f>
-        <v>L3  ·  L4  ·  L6</v>
-      </c>
-      <c r="G44" s="24" t="str">
-        <f>IFERROR(INDEX(Requerimientos!$I:$I,MATCH($A44,Requerimientos!$A:$A,0)),"")</f>
-        <v>Lab 6</v>
-      </c>
-      <c r="H44" s="24" t="str">
-        <f>IFERROR(INDEX(Requerimientos!$J:$J,MATCH($A44,Requerimientos!$A:$A,0)),"")</f>
-        <v>Pendiente</v>
-      </c>
+    <row r="44" spans="1:8" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="29" t="s">
+        <v>311</v>
+      </c>
+      <c r="B44" s="30"/>
+      <c r="C44" s="30"/>
+      <c r="D44" s="30"/>
+      <c r="E44" s="30"/>
+      <c r="F44" s="30"/>
+      <c r="G44" s="30"/>
+      <c r="H44" s="30"/>
     </row>
     <row r="45" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A45" s="26" t="s">
-        <v>154</v>
+        <v>126</v>
       </c>
       <c r="B45" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A45,Requerimientos!$A:$A,0)),"")</f>
-        <v>Registrar servicios con nombre descripción precio imágenes y si tienen costo</v>
+        <v>Activar y desactivar administradores de hotel taxistas y clientes</v>
       </c>
       <c r="C45" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$C:$C,MATCH($A45,Requerimientos!$A:$A,0)),"")</f>
-        <v>Administrador de hotel</v>
+        <v>Superadmin</v>
       </c>
       <c r="D45" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A45,Requerimientos!$A:$A,0)),"")</f>
-        <v>M3 Catálogo</v>
+        <v>M2 Gestión de usuarios</v>
       </c>
       <c r="E45" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A45,Requerimientos!$A:$A,0)),"")</f>
@@ -8242,19 +8407,19 @@
     </row>
     <row r="46" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A46" s="26" t="s">
-        <v>161</v>
+        <v>132</v>
       </c>
       <c r="B46" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A46,Requerimientos!$A:$A,0)),"")</f>
-        <v>Responder los chats de clientes con reserva activa</v>
+        <v>Registrar hoteles y asignar un administrador a cada uno</v>
       </c>
       <c r="C46" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$C:$C,MATCH($A46,Requerimientos!$A:$A,0)),"")</f>
-        <v>Administrador de hotel</v>
+        <v>Superadmin</v>
       </c>
       <c r="D46" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A46,Requerimientos!$A:$A,0)),"")</f>
-        <v>M7 Chat</v>
+        <v>M2 Gestión de usuarios</v>
       </c>
       <c r="E46" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A46,Requerimientos!$A:$A,0)),"")</f>
@@ -8275,15 +8440,15 @@
     </row>
     <row r="47" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A47" s="26" t="s">
-        <v>168</v>
+        <v>135</v>
       </c>
       <c r="B47" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A47,Requerimientos!$A:$A,0)),"")</f>
-        <v>Reporte de ingresos por servicios adicionales ordenado de menor a mayor</v>
+        <v>Generar el reporte de reservas por hotel</v>
       </c>
       <c r="C47" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$C:$C,MATCH($A47,Requerimientos!$A:$A,0)),"")</f>
-        <v>Administrador de hotel</v>
+        <v>Superadmin</v>
       </c>
       <c r="D47" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A47,Requerimientos!$A:$A,0)),"")</f>
@@ -8308,27 +8473,27 @@
     </row>
     <row r="48" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A48" s="26" t="s">
-        <v>184</v>
+        <v>138</v>
       </c>
       <c r="B48" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A48,Requerimientos!$A:$A,0)),"")</f>
-        <v>Ver hoteles y pedidos disponibles</v>
+        <v>Consultar el visor de logs de eventos del sistema</v>
       </c>
       <c r="C48" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$C:$C,MATCH($A48,Requerimientos!$A:$A,0)),"")</f>
-        <v>Taxista</v>
+        <v>Superadmin</v>
       </c>
       <c r="D48" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A48,Requerimientos!$A:$A,0)),"")</f>
-        <v>M8 Taxi</v>
+        <v>M9 Reportes y logs</v>
       </c>
       <c r="E48" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A48,Requerimientos!$A:$A,0)),"")</f>
-        <v>Alta</v>
+        <v>Media</v>
       </c>
       <c r="F48" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$H:$H,MATCH($A48,Requerimientos!$A:$A,0)),"")</f>
-        <v>L3  ·  L4  ·  L5  ·  L6</v>
+        <v>L3  ·  L4  ·  L6</v>
       </c>
       <c r="G48" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$I:$I,MATCH($A48,Requerimientos!$A:$A,0)),"")</f>
@@ -8341,15 +8506,15 @@
     </row>
     <row r="49" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A49" s="26" t="s">
-        <v>211</v>
+        <v>145</v>
       </c>
       <c r="B49" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A49,Requerimientos!$A:$A,0)),"")</f>
-        <v>Consultar hoteles habitaciones servicios disponibilidad y valoraciones</v>
+        <v>Subir fotos del hotel con un mínimo de 4</v>
       </c>
       <c r="C49" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$C:$C,MATCH($A49,Requerimientos!$A:$A,0)),"")</f>
-        <v>Cliente</v>
+        <v>Administrador de hotel</v>
       </c>
       <c r="D49" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A49,Requerimientos!$A:$A,0)),"")</f>
@@ -8361,7 +8526,7 @@
       </c>
       <c r="F49" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$H:$H,MATCH($A49,Requerimientos!$A:$A,0)),"")</f>
-        <v>L3  ·  L4  ·  L6</v>
+        <v>L3  ·  L4  ·  L5  ·  L6</v>
       </c>
       <c r="G49" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$I:$I,MATCH($A49,Requerimientos!$A:$A,0)),"")</f>
@@ -8374,19 +8539,19 @@
     </row>
     <row r="50" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A50" s="26" t="s">
-        <v>225</v>
+        <v>151</v>
       </c>
       <c r="B50" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A50,Requerimientos!$A:$A,0)),"")</f>
-        <v>Chat privado con el hotel entre la confirmación de la reserva y el fin del checkout</v>
+        <v>Registrar habitaciones con tipo capacidad de adultos y niños y tamaño en m2</v>
       </c>
       <c r="C50" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$C:$C,MATCH($A50,Requerimientos!$A:$A,0)),"")</f>
-        <v>Cliente</v>
+        <v>Administrador de hotel</v>
       </c>
       <c r="D50" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A50,Requerimientos!$A:$A,0)),"")</f>
-        <v>M7 Chat</v>
+        <v>M3 Catálogo</v>
       </c>
       <c r="E50" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A50,Requerimientos!$A:$A,0)),"")</f>
@@ -8407,23 +8572,23 @@
     </row>
     <row r="51" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A51" s="26" t="s">
-        <v>229</v>
+        <v>154</v>
       </c>
       <c r="B51" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A51,Requerimientos!$A:$A,0)),"")</f>
-        <v>Ver el historial de sus reservas</v>
+        <v>Registrar servicios con nombre descripción precio imágenes y si tienen costo</v>
       </c>
       <c r="C51" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$C:$C,MATCH($A51,Requerimientos!$A:$A,0)),"")</f>
-        <v>Cliente</v>
+        <v>Administrador de hotel</v>
       </c>
       <c r="D51" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A51,Requerimientos!$A:$A,0)),"")</f>
-        <v>M4 Reservas</v>
+        <v>M3 Catálogo</v>
       </c>
       <c r="E51" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A51,Requerimientos!$A:$A,0)),"")</f>
-        <v>Media</v>
+        <v>Alta</v>
       </c>
       <c r="F51" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$H:$H,MATCH($A51,Requerimientos!$A:$A,0)),"")</f>
@@ -8438,33 +8603,87 @@
         <v>Pendiente</v>
       </c>
     </row>
-    <row r="53" spans="1:8" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="29" t="s">
-        <v>305</v>
-      </c>
-      <c r="B53" s="30"/>
-      <c r="C53" s="30"/>
-      <c r="D53" s="30"/>
-      <c r="E53" s="30"/>
-      <c r="F53" s="30"/>
-      <c r="G53" s="30"/>
-      <c r="H53" s="30"/>
+    <row r="52" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="26" t="s">
+        <v>161</v>
+      </c>
+      <c r="B52" s="3" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A52,Requerimientos!$A:$A,0)),"")</f>
+        <v>Responder los chats de clientes con reserva activa</v>
+      </c>
+      <c r="C52" s="24" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$C:$C,MATCH($A52,Requerimientos!$A:$A,0)),"")</f>
+        <v>Administrador de hotel</v>
+      </c>
+      <c r="D52" s="24" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A52,Requerimientos!$A:$A,0)),"")</f>
+        <v>M7 Chat</v>
+      </c>
+      <c r="E52" s="24" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A52,Requerimientos!$A:$A,0)),"")</f>
+        <v>Alta</v>
+      </c>
+      <c r="F52" s="24" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$H:$H,MATCH($A52,Requerimientos!$A:$A,0)),"")</f>
+        <v>L3  ·  L4  ·  L6</v>
+      </c>
+      <c r="G52" s="24" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$I:$I,MATCH($A52,Requerimientos!$A:$A,0)),"")</f>
+        <v>Lab 6</v>
+      </c>
+      <c r="H52" s="24" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$J:$J,MATCH($A52,Requerimientos!$A:$A,0)),"")</f>
+        <v>Pendiente</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="26" t="s">
+        <v>172</v>
+      </c>
+      <c r="B53" s="3" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A53,Requerimientos!$A:$A,0)),"")</f>
+        <v>Reporte de ingresos por servicios adicionales ordenado de menor a mayor</v>
+      </c>
+      <c r="C53" s="24" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$C:$C,MATCH($A53,Requerimientos!$A:$A,0)),"")</f>
+        <v>Administrador de hotel</v>
+      </c>
+      <c r="D53" s="24" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A53,Requerimientos!$A:$A,0)),"")</f>
+        <v>M9 Reportes y logs</v>
+      </c>
+      <c r="E53" s="24" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A53,Requerimientos!$A:$A,0)),"")</f>
+        <v>Media</v>
+      </c>
+      <c r="F53" s="24" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$H:$H,MATCH($A53,Requerimientos!$A:$A,0)),"")</f>
+        <v>L3  ·  L4  ·  L6</v>
+      </c>
+      <c r="G53" s="24" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$I:$I,MATCH($A53,Requerimientos!$A:$A,0)),"")</f>
+        <v>Lab 6</v>
+      </c>
+      <c r="H53" s="24" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$J:$J,MATCH($A53,Requerimientos!$A:$A,0)),"")</f>
+        <v>Pendiente</v>
+      </c>
     </row>
     <row r="54" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A54" s="26" t="s">
-        <v>145</v>
+        <v>188</v>
       </c>
       <c r="B54" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A54,Requerimientos!$A:$A,0)),"")</f>
-        <v>Subir fotos del hotel con un mínimo de 4</v>
+        <v>Ver hoteles y pedidos disponibles</v>
       </c>
       <c r="C54" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$C:$C,MATCH($A54,Requerimientos!$A:$A,0)),"")</f>
-        <v>Administrador de hotel</v>
+        <v>Taxista</v>
       </c>
       <c r="D54" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A54,Requerimientos!$A:$A,0)),"")</f>
-        <v>M3 Catálogo</v>
+        <v>M8 Taxi</v>
       </c>
       <c r="E54" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A54,Requerimientos!$A:$A,0)),"")</f>
@@ -8485,19 +8704,19 @@
     </row>
     <row r="55" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A55" s="26" t="s">
-        <v>157</v>
+        <v>215</v>
       </c>
       <c r="B55" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A55,Requerimientos!$A:$A,0)),"")</f>
-        <v>Recibir la alerta de checkout y procesar el cobro de la tarjeta registrada</v>
+        <v>Consultar hoteles habitaciones servicios disponibilidad y valoraciones</v>
       </c>
       <c r="C55" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$C:$C,MATCH($A55,Requerimientos!$A:$A,0)),"")</f>
-        <v>Administrador de hotel</v>
+        <v>Cliente</v>
       </c>
       <c r="D55" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A55,Requerimientos!$A:$A,0)),"")</f>
-        <v>M5 Pagos y cobros</v>
+        <v>M3 Catálogo</v>
       </c>
       <c r="E55" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A55,Requerimientos!$A:$A,0)),"")</f>
@@ -8505,7 +8724,7 @@
       </c>
       <c r="F55" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$H:$H,MATCH($A55,Requerimientos!$A:$A,0)),"")</f>
-        <v>L3  ·  L5  ·  L6</v>
+        <v>L3  ·  L4  ·  L6</v>
       </c>
       <c r="G55" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$I:$I,MATCH($A55,Requerimientos!$A:$A,0)),"")</f>
@@ -8518,19 +8737,19 @@
     </row>
     <row r="56" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A56" s="26" t="s">
-        <v>181</v>
+        <v>228</v>
       </c>
       <c r="B56" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A56,Requerimientos!$A:$A,0)),"")</f>
-        <v>Acceder a la app móvil una vez habilitado</v>
+        <v>Chat privado con el hotel entre la confirmación de la reserva y el fin del checkout</v>
       </c>
       <c r="C56" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$C:$C,MATCH($A56,Requerimientos!$A:$A,0)),"")</f>
-        <v>Taxista</v>
+        <v>Cliente</v>
       </c>
       <c r="D56" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A56,Requerimientos!$A:$A,0)),"")</f>
-        <v>M1 Autenticación</v>
+        <v>M7 Chat</v>
       </c>
       <c r="E56" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A56,Requerimientos!$A:$A,0)),"")</f>
@@ -8538,7 +8757,7 @@
       </c>
       <c r="F56" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$H:$H,MATCH($A56,Requerimientos!$A:$A,0)),"")</f>
-        <v>L3  ·  L5  ·  L6</v>
+        <v>L3  ·  L4  ·  L6</v>
       </c>
       <c r="G56" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$I:$I,MATCH($A56,Requerimientos!$A:$A,0)),"")</f>
@@ -8551,27 +8770,27 @@
     </row>
     <row r="57" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A57" s="26" t="s">
-        <v>184</v>
+        <v>232</v>
       </c>
       <c r="B57" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A57,Requerimientos!$A:$A,0)),"")</f>
-        <v>Ver hoteles y pedidos disponibles</v>
+        <v>Ver el historial de sus reservas</v>
       </c>
       <c r="C57" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$C:$C,MATCH($A57,Requerimientos!$A:$A,0)),"")</f>
-        <v>Taxista</v>
+        <v>Cliente</v>
       </c>
       <c r="D57" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A57,Requerimientos!$A:$A,0)),"")</f>
-        <v>M8 Taxi</v>
+        <v>M4 Reservas</v>
       </c>
       <c r="E57" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A57,Requerimientos!$A:$A,0)),"")</f>
-        <v>Alta</v>
+        <v>Media</v>
       </c>
       <c r="F57" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$H:$H,MATCH($A57,Requerimientos!$A:$A,0)),"")</f>
-        <v>L3  ·  L4  ·  L5  ·  L6</v>
+        <v>L3  ·  L4  ·  L6</v>
       </c>
       <c r="G57" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$I:$I,MATCH($A57,Requerimientos!$A:$A,0)),"")</f>
@@ -8584,11 +8803,11 @@
     </row>
     <row r="58" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A58" s="26" t="s">
-        <v>207</v>
+        <v>235</v>
       </c>
       <c r="B58" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A58,Requerimientos!$A:$A,0)),"")</f>
-        <v>Autoregistrarse y quedar habilitado automáticamente</v>
+        <v>Consultar los lugares históricos cercanos al hotel</v>
       </c>
       <c r="C58" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$C:$C,MATCH($A58,Requerimientos!$A:$A,0)),"")</f>
@@ -8596,15 +8815,15 @@
       </c>
       <c r="D58" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A58,Requerimientos!$A:$A,0)),"")</f>
-        <v>M1 Autenticación</v>
+        <v>M3 Catálogo</v>
       </c>
       <c r="E58" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A58,Requerimientos!$A:$A,0)),"")</f>
-        <v>Alta</v>
+        <v>Media</v>
       </c>
       <c r="F58" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$H:$H,MATCH($A58,Requerimientos!$A:$A,0)),"")</f>
-        <v>L3  ·  L5  ·  L6</v>
+        <v>L3  ·  L4  ·  L6</v>
       </c>
       <c r="G58" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$I:$I,MATCH($A58,Requerimientos!$A:$A,0)),"")</f>
@@ -8617,19 +8836,19 @@
     </row>
     <row r="59" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A59" s="26" t="s">
-        <v>220</v>
+        <v>268</v>
       </c>
       <c r="B59" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A59,Requerimientos!$A:$A,0)),"")</f>
-        <v>Recibir notificación cuando se le hace el cobro</v>
+        <v>Los mensajes de chat persisten con fecha y hora</v>
       </c>
       <c r="C59" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$C:$C,MATCH($A59,Requerimientos!$A:$A,0)),"")</f>
-        <v>Cliente</v>
+        <v>Transversal</v>
       </c>
       <c r="D59" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A59,Requerimientos!$A:$A,0)),"")</f>
-        <v>M5 Pagos y cobros</v>
+        <v>M7 Chat</v>
       </c>
       <c r="E59" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A59,Requerimientos!$A:$A,0)),"")</f>
@@ -8637,7 +8856,7 @@
       </c>
       <c r="F59" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$H:$H,MATCH($A59,Requerimientos!$A:$A,0)),"")</f>
-        <v>L5  ·  L6</v>
+        <v>L3  ·  L4  ·  L6</v>
       </c>
       <c r="G59" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$I:$I,MATCH($A59,Requerimientos!$A:$A,0)),"")</f>
@@ -8650,7 +8869,7 @@
     </row>
     <row r="61" spans="1:8" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="29" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="B61" s="30"/>
       <c r="C61" s="30"/>
@@ -8662,19 +8881,19 @@
     </row>
     <row r="62" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A62" s="26" t="s">
-        <v>126</v>
+        <v>145</v>
       </c>
       <c r="B62" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A62,Requerimientos!$A:$A,0)),"")</f>
-        <v>Activar y desactivar administradores de hotel taxistas y clientes</v>
+        <v>Subir fotos del hotel con un mínimo de 4</v>
       </c>
       <c r="C62" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$C:$C,MATCH($A62,Requerimientos!$A:$A,0)),"")</f>
-        <v>Superadmin</v>
+        <v>Administrador de hotel</v>
       </c>
       <c r="D62" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A62,Requerimientos!$A:$A,0)),"")</f>
-        <v>M2 Gestión de usuarios</v>
+        <v>M3 Catálogo</v>
       </c>
       <c r="E62" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A62,Requerimientos!$A:$A,0)),"")</f>
@@ -8682,7 +8901,7 @@
       </c>
       <c r="F62" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$H:$H,MATCH($A62,Requerimientos!$A:$A,0)),"")</f>
-        <v>L3  ·  L4  ·  L6</v>
+        <v>L3  ·  L4  ·  L5  ·  L6</v>
       </c>
       <c r="G62" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$I:$I,MATCH($A62,Requerimientos!$A:$A,0)),"")</f>
@@ -8695,19 +8914,19 @@
     </row>
     <row r="63" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A63" s="26" t="s">
-        <v>132</v>
+        <v>157</v>
       </c>
       <c r="B63" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A63,Requerimientos!$A:$A,0)),"")</f>
-        <v>Registrar hoteles y asignar un administrador a cada uno</v>
+        <v>Recibir la alerta de checkout y procesar el cobro de la tarjeta registrada</v>
       </c>
       <c r="C63" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$C:$C,MATCH($A63,Requerimientos!$A:$A,0)),"")</f>
-        <v>Superadmin</v>
+        <v>Administrador de hotel</v>
       </c>
       <c r="D63" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A63,Requerimientos!$A:$A,0)),"")</f>
-        <v>M2 Gestión de usuarios</v>
+        <v>M5 Pagos y cobros</v>
       </c>
       <c r="E63" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A63,Requerimientos!$A:$A,0)),"")</f>
@@ -8715,7 +8934,7 @@
       </c>
       <c r="F63" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$H:$H,MATCH($A63,Requerimientos!$A:$A,0)),"")</f>
-        <v>L3  ·  L4  ·  L6</v>
+        <v>L3  ·  L5  ·  L6</v>
       </c>
       <c r="G63" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$I:$I,MATCH($A63,Requerimientos!$A:$A,0)),"")</f>
@@ -8728,27 +8947,27 @@
     </row>
     <row r="64" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A64" s="26" t="s">
-        <v>135</v>
+        <v>185</v>
       </c>
       <c r="B64" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A64,Requerimientos!$A:$A,0)),"")</f>
-        <v>Generar el reporte de reservas por hotel</v>
+        <v>Acceder a la app móvil una vez habilitado</v>
       </c>
       <c r="C64" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$C:$C,MATCH($A64,Requerimientos!$A:$A,0)),"")</f>
-        <v>Superadmin</v>
+        <v>Taxista</v>
       </c>
       <c r="D64" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A64,Requerimientos!$A:$A,0)),"")</f>
-        <v>M9 Reportes y logs</v>
+        <v>M1 Autenticación</v>
       </c>
       <c r="E64" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A64,Requerimientos!$A:$A,0)),"")</f>
-        <v>Media</v>
+        <v>Alta</v>
       </c>
       <c r="F64" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$H:$H,MATCH($A64,Requerimientos!$A:$A,0)),"")</f>
-        <v>L3  ·  L4  ·  L6</v>
+        <v>L3  ·  L5  ·  L6</v>
       </c>
       <c r="G64" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$I:$I,MATCH($A64,Requerimientos!$A:$A,0)),"")</f>
@@ -8761,27 +8980,27 @@
     </row>
     <row r="65" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A65" s="26" t="s">
-        <v>138</v>
+        <v>188</v>
       </c>
       <c r="B65" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A65,Requerimientos!$A:$A,0)),"")</f>
-        <v>Consultar el visor de logs de eventos del sistema</v>
+        <v>Ver hoteles y pedidos disponibles</v>
       </c>
       <c r="C65" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$C:$C,MATCH($A65,Requerimientos!$A:$A,0)),"")</f>
-        <v>Superadmin</v>
+        <v>Taxista</v>
       </c>
       <c r="D65" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A65,Requerimientos!$A:$A,0)),"")</f>
-        <v>M9 Reportes y logs</v>
+        <v>M8 Taxi</v>
       </c>
       <c r="E65" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A65,Requerimientos!$A:$A,0)),"")</f>
-        <v>Media</v>
+        <v>Alta</v>
       </c>
       <c r="F65" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$H:$H,MATCH($A65,Requerimientos!$A:$A,0)),"")</f>
-        <v>L3  ·  L4  ·  L6</v>
+        <v>L3  ·  L4  ·  L5  ·  L6</v>
       </c>
       <c r="G65" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$I:$I,MATCH($A65,Requerimientos!$A:$A,0)),"")</f>
@@ -8794,19 +9013,19 @@
     </row>
     <row r="66" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A66" s="26" t="s">
-        <v>145</v>
+        <v>211</v>
       </c>
       <c r="B66" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A66,Requerimientos!$A:$A,0)),"")</f>
-        <v>Subir fotos del hotel con un mínimo de 4</v>
+        <v>Autoregistrarse y quedar habilitado automáticamente</v>
       </c>
       <c r="C66" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$C:$C,MATCH($A66,Requerimientos!$A:$A,0)),"")</f>
-        <v>Administrador de hotel</v>
+        <v>Cliente</v>
       </c>
       <c r="D66" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A66,Requerimientos!$A:$A,0)),"")</f>
-        <v>M3 Catálogo</v>
+        <v>M1 Autenticación</v>
       </c>
       <c r="E66" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A66,Requerimientos!$A:$A,0)),"")</f>
@@ -8814,7 +9033,7 @@
       </c>
       <c r="F66" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$H:$H,MATCH($A66,Requerimientos!$A:$A,0)),"")</f>
-        <v>L3  ·  L4  ·  L5  ·  L6</v>
+        <v>L3  ·  L5  ·  L6</v>
       </c>
       <c r="G66" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$I:$I,MATCH($A66,Requerimientos!$A:$A,0)),"")</f>
@@ -8827,19 +9046,19 @@
     </row>
     <row r="67" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A67" s="26" t="s">
-        <v>151</v>
+        <v>224</v>
       </c>
       <c r="B67" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A67,Requerimientos!$A:$A,0)),"")</f>
-        <v>Registrar habitaciones con tipo capacidad de adultos y niños y tamaño en m2</v>
+        <v>Recibir notificación cuando se le hace el cobro</v>
       </c>
       <c r="C67" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$C:$C,MATCH($A67,Requerimientos!$A:$A,0)),"")</f>
-        <v>Administrador de hotel</v>
+        <v>Cliente</v>
       </c>
       <c r="D67" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A67,Requerimientos!$A:$A,0)),"")</f>
-        <v>M3 Catálogo</v>
+        <v>M5 Pagos y cobros</v>
       </c>
       <c r="E67" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A67,Requerimientos!$A:$A,0)),"")</f>
@@ -8847,7 +9066,7 @@
       </c>
       <c r="F67" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$H:$H,MATCH($A67,Requerimientos!$A:$A,0)),"")</f>
-        <v>L3  ·  L4  ·  L6</v>
+        <v>L3  ·  L5  ·  L6</v>
       </c>
       <c r="G67" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$I:$I,MATCH($A67,Requerimientos!$A:$A,0)),"")</f>
@@ -8858,87 +9077,33 @@
         <v>Pendiente</v>
       </c>
     </row>
-    <row r="68" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="26" t="s">
-        <v>154</v>
-      </c>
-      <c r="B68" s="3" t="str">
-        <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A68,Requerimientos!$A:$A,0)),"")</f>
-        <v>Registrar servicios con nombre descripción precio imágenes y si tienen costo</v>
-      </c>
-      <c r="C68" s="24" t="str">
-        <f>IFERROR(INDEX(Requerimientos!$C:$C,MATCH($A68,Requerimientos!$A:$A,0)),"")</f>
-        <v>Administrador de hotel</v>
-      </c>
-      <c r="D68" s="24" t="str">
-        <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A68,Requerimientos!$A:$A,0)),"")</f>
-        <v>M3 Catálogo</v>
-      </c>
-      <c r="E68" s="24" t="str">
-        <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A68,Requerimientos!$A:$A,0)),"")</f>
-        <v>Alta</v>
-      </c>
-      <c r="F68" s="24" t="str">
-        <f>IFERROR(INDEX(Requerimientos!$H:$H,MATCH($A68,Requerimientos!$A:$A,0)),"")</f>
-        <v>L3  ·  L4  ·  L6</v>
-      </c>
-      <c r="G68" s="24" t="str">
-        <f>IFERROR(INDEX(Requerimientos!$I:$I,MATCH($A68,Requerimientos!$A:$A,0)),"")</f>
-        <v>Lab 6</v>
-      </c>
-      <c r="H68" s="24" t="str">
-        <f>IFERROR(INDEX(Requerimientos!$J:$J,MATCH($A68,Requerimientos!$A:$A,0)),"")</f>
-        <v>Pendiente</v>
-      </c>
-    </row>
-    <row r="69" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="26" t="s">
-        <v>157</v>
-      </c>
-      <c r="B69" s="3" t="str">
-        <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A69,Requerimientos!$A:$A,0)),"")</f>
-        <v>Recibir la alerta de checkout y procesar el cobro de la tarjeta registrada</v>
-      </c>
-      <c r="C69" s="24" t="str">
-        <f>IFERROR(INDEX(Requerimientos!$C:$C,MATCH($A69,Requerimientos!$A:$A,0)),"")</f>
-        <v>Administrador de hotel</v>
-      </c>
-      <c r="D69" s="24" t="str">
-        <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A69,Requerimientos!$A:$A,0)),"")</f>
-        <v>M5 Pagos y cobros</v>
-      </c>
-      <c r="E69" s="24" t="str">
-        <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A69,Requerimientos!$A:$A,0)),"")</f>
-        <v>Alta</v>
-      </c>
-      <c r="F69" s="24" t="str">
-        <f>IFERROR(INDEX(Requerimientos!$H:$H,MATCH($A69,Requerimientos!$A:$A,0)),"")</f>
-        <v>L3  ·  L5  ·  L6</v>
-      </c>
-      <c r="G69" s="24" t="str">
-        <f>IFERROR(INDEX(Requerimientos!$I:$I,MATCH($A69,Requerimientos!$A:$A,0)),"")</f>
-        <v>Lab 6</v>
-      </c>
-      <c r="H69" s="24" t="str">
-        <f>IFERROR(INDEX(Requerimientos!$J:$J,MATCH($A69,Requerimientos!$A:$A,0)),"")</f>
-        <v>Pendiente</v>
-      </c>
+    <row r="69" spans="1:8" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A69" s="29" t="s">
+        <v>313</v>
+      </c>
+      <c r="B69" s="30"/>
+      <c r="C69" s="30"/>
+      <c r="D69" s="30"/>
+      <c r="E69" s="30"/>
+      <c r="F69" s="30"/>
+      <c r="G69" s="30"/>
+      <c r="H69" s="30"/>
     </row>
     <row r="70" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A70" s="26" t="s">
-        <v>161</v>
+        <v>126</v>
       </c>
       <c r="B70" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A70,Requerimientos!$A:$A,0)),"")</f>
-        <v>Responder los chats de clientes con reserva activa</v>
+        <v>Activar y desactivar administradores de hotel taxistas y clientes</v>
       </c>
       <c r="C70" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$C:$C,MATCH($A70,Requerimientos!$A:$A,0)),"")</f>
-        <v>Administrador de hotel</v>
+        <v>Superadmin</v>
       </c>
       <c r="D70" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A70,Requerimientos!$A:$A,0)),"")</f>
-        <v>M7 Chat</v>
+        <v>M2 Gestión de usuarios</v>
       </c>
       <c r="E70" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A70,Requerimientos!$A:$A,0)),"")</f>
@@ -8959,27 +9124,27 @@
     </row>
     <row r="71" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A71" s="26" t="s">
-        <v>164</v>
+        <v>132</v>
       </c>
       <c r="B71" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A71,Requerimientos!$A:$A,0)),"")</f>
-        <v>Añadir cobros adicionales por daños con monto motivo y observación</v>
+        <v>Registrar hoteles y asignar un administrador a cada uno</v>
       </c>
       <c r="C71" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$C:$C,MATCH($A71,Requerimientos!$A:$A,0)),"")</f>
-        <v>Administrador de hotel</v>
+        <v>Superadmin</v>
       </c>
       <c r="D71" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A71,Requerimientos!$A:$A,0)),"")</f>
-        <v>M5 Pagos y cobros</v>
+        <v>M2 Gestión de usuarios</v>
       </c>
       <c r="E71" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A71,Requerimientos!$A:$A,0)),"")</f>
-        <v>Media</v>
+        <v>Alta</v>
       </c>
       <c r="F71" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$H:$H,MATCH($A71,Requerimientos!$A:$A,0)),"")</f>
-        <v>L3  ·  L6</v>
+        <v>L3  ·  L4  ·  L6</v>
       </c>
       <c r="G71" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$I:$I,MATCH($A71,Requerimientos!$A:$A,0)),"")</f>
@@ -8992,15 +9157,15 @@
     </row>
     <row r="72" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A72" s="26" t="s">
-        <v>168</v>
+        <v>135</v>
       </c>
       <c r="B72" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A72,Requerimientos!$A:$A,0)),"")</f>
-        <v>Reporte de ingresos por servicios adicionales ordenado de menor a mayor</v>
+        <v>Generar el reporte de reservas por hotel</v>
       </c>
       <c r="C72" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$C:$C,MATCH($A72,Requerimientos!$A:$A,0)),"")</f>
-        <v>Administrador de hotel</v>
+        <v>Superadmin</v>
       </c>
       <c r="D72" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A72,Requerimientos!$A:$A,0)),"")</f>
@@ -9025,31 +9190,31 @@
     </row>
     <row r="73" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A73" s="26" t="s">
-        <v>173</v>
+        <v>138</v>
       </c>
       <c r="B73" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A73,Requerimientos!$A:$A,0)),"")</f>
-        <v>Registrar la ubicación del hotel y los lugares históricos cercanos</v>
+        <v>Consultar el visor de logs de eventos del sistema</v>
       </c>
       <c r="C73" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$C:$C,MATCH($A73,Requerimientos!$A:$A,0)),"")</f>
-        <v>Administrador de hotel</v>
+        <v>Superadmin</v>
       </c>
       <c r="D73" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A73,Requerimientos!$A:$A,0)),"")</f>
-        <v>M3 Catálogo</v>
+        <v>M9 Reportes y logs</v>
       </c>
       <c r="E73" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A73,Requerimientos!$A:$A,0)),"")</f>
-        <v>Alta</v>
+        <v>Media</v>
       </c>
       <c r="F73" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$H:$H,MATCH($A73,Requerimientos!$A:$A,0)),"")</f>
-        <v>L3  ·  L6  ·  L7</v>
+        <v>L3  ·  L4  ·  L6</v>
       </c>
       <c r="G73" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$I:$I,MATCH($A73,Requerimientos!$A:$A,0)),"")</f>
-        <v>Lab 7</v>
+        <v>Lab 6</v>
       </c>
       <c r="H73" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$J:$J,MATCH($A73,Requerimientos!$A:$A,0)),"")</f>
@@ -9058,11 +9223,11 @@
     </row>
     <row r="74" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A74" s="26" t="s">
-        <v>178</v>
+        <v>145</v>
       </c>
       <c r="B74" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A74,Requerimientos!$A:$A,0)),"")</f>
-        <v>Ver el estado del taxista asignado en camino a recoger y llegó al destino</v>
+        <v>Subir fotos del hotel con un mínimo de 4</v>
       </c>
       <c r="C74" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$C:$C,MATCH($A74,Requerimientos!$A:$A,0)),"")</f>
@@ -9070,19 +9235,19 @@
       </c>
       <c r="D74" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A74,Requerimientos!$A:$A,0)),"")</f>
-        <v>M8 Taxi</v>
+        <v>M3 Catálogo</v>
       </c>
       <c r="E74" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A74,Requerimientos!$A:$A,0)),"")</f>
-        <v>Media</v>
+        <v>Alta</v>
       </c>
       <c r="F74" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$H:$H,MATCH($A74,Requerimientos!$A:$A,0)),"")</f>
-        <v>L3  ·  L6  ·  L7</v>
+        <v>L3  ·  L4  ·  L5  ·  L6</v>
       </c>
       <c r="G74" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$I:$I,MATCH($A74,Requerimientos!$A:$A,0)),"")</f>
-        <v>Lab 7</v>
+        <v>Lab 6</v>
       </c>
       <c r="H74" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$J:$J,MATCH($A74,Requerimientos!$A:$A,0)),"")</f>
@@ -9091,19 +9256,19 @@
     </row>
     <row r="75" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A75" s="26" t="s">
-        <v>181</v>
+        <v>151</v>
       </c>
       <c r="B75" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A75,Requerimientos!$A:$A,0)),"")</f>
-        <v>Acceder a la app móvil una vez habilitado</v>
+        <v>Registrar habitaciones con tipo capacidad de adultos y niños y tamaño en m2</v>
       </c>
       <c r="C75" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$C:$C,MATCH($A75,Requerimientos!$A:$A,0)),"")</f>
-        <v>Taxista</v>
+        <v>Administrador de hotel</v>
       </c>
       <c r="D75" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A75,Requerimientos!$A:$A,0)),"")</f>
-        <v>M1 Autenticación</v>
+        <v>M3 Catálogo</v>
       </c>
       <c r="E75" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A75,Requerimientos!$A:$A,0)),"")</f>
@@ -9111,7 +9276,7 @@
       </c>
       <c r="F75" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$H:$H,MATCH($A75,Requerimientos!$A:$A,0)),"")</f>
-        <v>L3  ·  L5  ·  L6</v>
+        <v>L3  ·  L4  ·  L6</v>
       </c>
       <c r="G75" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$I:$I,MATCH($A75,Requerimientos!$A:$A,0)),"")</f>
@@ -9124,19 +9289,19 @@
     </row>
     <row r="76" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A76" s="26" t="s">
-        <v>184</v>
+        <v>154</v>
       </c>
       <c r="B76" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A76,Requerimientos!$A:$A,0)),"")</f>
-        <v>Ver hoteles y pedidos disponibles</v>
+        <v>Registrar servicios con nombre descripción precio imágenes y si tienen costo</v>
       </c>
       <c r="C76" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$C:$C,MATCH($A76,Requerimientos!$A:$A,0)),"")</f>
-        <v>Taxista</v>
+        <v>Administrador de hotel</v>
       </c>
       <c r="D76" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A76,Requerimientos!$A:$A,0)),"")</f>
-        <v>M8 Taxi</v>
+        <v>M3 Catálogo</v>
       </c>
       <c r="E76" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A76,Requerimientos!$A:$A,0)),"")</f>
@@ -9144,7 +9309,7 @@
       </c>
       <c r="F76" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$H:$H,MATCH($A76,Requerimientos!$A:$A,0)),"")</f>
-        <v>L3  ·  L4  ·  L5  ·  L6</v>
+        <v>L3  ·  L4  ·  L6</v>
       </c>
       <c r="G76" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$I:$I,MATCH($A76,Requerimientos!$A:$A,0)),"")</f>
@@ -9157,19 +9322,19 @@
     </row>
     <row r="77" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A77" s="26" t="s">
-        <v>187</v>
+        <v>157</v>
       </c>
       <c r="B77" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A77,Requerimientos!$A:$A,0)),"")</f>
-        <v>Aceptar un pedido que deja de estar disponible para los demás</v>
+        <v>Recibir la alerta de checkout y procesar el cobro de la tarjeta registrada</v>
       </c>
       <c r="C77" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$C:$C,MATCH($A77,Requerimientos!$A:$A,0)),"")</f>
-        <v>Taxista</v>
+        <v>Administrador de hotel</v>
       </c>
       <c r="D77" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A77,Requerimientos!$A:$A,0)),"")</f>
-        <v>M8 Taxi</v>
+        <v>M5 Pagos y cobros</v>
       </c>
       <c r="E77" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A77,Requerimientos!$A:$A,0)),"")</f>
@@ -9177,7 +9342,7 @@
       </c>
       <c r="F77" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$H:$H,MATCH($A77,Requerimientos!$A:$A,0)),"")</f>
-        <v>L3  ·  L6</v>
+        <v>L3  ·  L5  ·  L6</v>
       </c>
       <c r="G77" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$I:$I,MATCH($A77,Requerimientos!$A:$A,0)),"")</f>
@@ -9190,19 +9355,19 @@
     </row>
     <row r="78" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A78" s="26" t="s">
-        <v>191</v>
+        <v>161</v>
       </c>
       <c r="B78" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A78,Requerimientos!$A:$A,0)),"")</f>
-        <v>Actualizar los estados del servicio</v>
+        <v>Responder los chats de clientes con reserva activa</v>
       </c>
       <c r="C78" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$C:$C,MATCH($A78,Requerimientos!$A:$A,0)),"")</f>
-        <v>Taxista</v>
+        <v>Administrador de hotel</v>
       </c>
       <c r="D78" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A78,Requerimientos!$A:$A,0)),"")</f>
-        <v>M8 Taxi</v>
+        <v>M7 Chat</v>
       </c>
       <c r="E78" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A78,Requerimientos!$A:$A,0)),"")</f>
@@ -9210,7 +9375,7 @@
       </c>
       <c r="F78" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$H:$H,MATCH($A78,Requerimientos!$A:$A,0)),"")</f>
-        <v>L3  ·  L6</v>
+        <v>L3  ·  L4  ·  L6</v>
       </c>
       <c r="G78" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$I:$I,MATCH($A78,Requerimientos!$A:$A,0)),"")</f>
@@ -9223,15 +9388,15 @@
     </row>
     <row r="79" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A79" s="26" t="s">
-        <v>194</v>
+        <v>164</v>
       </c>
       <c r="B79" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A79,Requerimientos!$A:$A,0)),"")</f>
-        <v>Registrar automáticamente su ubicación durante el servicio activo</v>
+        <v>Establecer el monto mínimo de reserva que da derecho al taxi gratuito al aeropuerto</v>
       </c>
       <c r="C79" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$C:$C,MATCH($A79,Requerimientos!$A:$A,0)),"")</f>
-        <v>Taxista</v>
+        <v>Administrador de hotel</v>
       </c>
       <c r="D79" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A79,Requerimientos!$A:$A,0)),"")</f>
@@ -9243,11 +9408,11 @@
       </c>
       <c r="F79" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$H:$H,MATCH($A79,Requerimientos!$A:$A,0)),"")</f>
-        <v>L6  ·  L7</v>
+        <v>L3  ·  L6</v>
       </c>
       <c r="G79" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$I:$I,MATCH($A79,Requerimientos!$A:$A,0)),"")</f>
-        <v>Lab 7</v>
+        <v>Lab 6</v>
       </c>
       <c r="H79" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$J:$J,MATCH($A79,Requerimientos!$A:$A,0)),"")</f>
@@ -9256,27 +9421,27 @@
     </row>
     <row r="80" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A80" s="26" t="s">
-        <v>207</v>
+        <v>169</v>
       </c>
       <c r="B80" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A80,Requerimientos!$A:$A,0)),"")</f>
-        <v>Autoregistrarse y quedar habilitado automáticamente</v>
+        <v>Añadir cobros adicionales por daños con monto motivo y observación</v>
       </c>
       <c r="C80" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$C:$C,MATCH($A80,Requerimientos!$A:$A,0)),"")</f>
-        <v>Cliente</v>
+        <v>Administrador de hotel</v>
       </c>
       <c r="D80" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A80,Requerimientos!$A:$A,0)),"")</f>
-        <v>M1 Autenticación</v>
+        <v>M5 Pagos y cobros</v>
       </c>
       <c r="E80" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A80,Requerimientos!$A:$A,0)),"")</f>
-        <v>Alta</v>
+        <v>Media</v>
       </c>
       <c r="F80" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$H:$H,MATCH($A80,Requerimientos!$A:$A,0)),"")</f>
-        <v>L3  ·  L5  ·  L6</v>
+        <v>L3  ·  L6</v>
       </c>
       <c r="G80" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$I:$I,MATCH($A80,Requerimientos!$A:$A,0)),"")</f>
@@ -9289,23 +9454,23 @@
     </row>
     <row r="81" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A81" s="26" t="s">
-        <v>211</v>
+        <v>172</v>
       </c>
       <c r="B81" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A81,Requerimientos!$A:$A,0)),"")</f>
-        <v>Consultar hoteles habitaciones servicios disponibilidad y valoraciones</v>
+        <v>Reporte de ingresos por servicios adicionales ordenado de menor a mayor</v>
       </c>
       <c r="C81" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$C:$C,MATCH($A81,Requerimientos!$A:$A,0)),"")</f>
-        <v>Cliente</v>
+        <v>Administrador de hotel</v>
       </c>
       <c r="D81" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A81,Requerimientos!$A:$A,0)),"")</f>
-        <v>M3 Catálogo</v>
+        <v>M9 Reportes y logs</v>
       </c>
       <c r="E81" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A81,Requerimientos!$A:$A,0)),"")</f>
-        <v>Alta</v>
+        <v>Media</v>
       </c>
       <c r="F81" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$H:$H,MATCH($A81,Requerimientos!$A:$A,0)),"")</f>
@@ -9322,19 +9487,19 @@
     </row>
     <row r="82" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A82" s="26" t="s">
-        <v>214</v>
+        <v>177</v>
       </c>
       <c r="B82" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A82,Requerimientos!$A:$A,0)),"")</f>
-        <v>Reservar con tarjeta de crédito o débito simulada</v>
+        <v>Registrar la ubicación del hotel y los lugares históricos cercanos</v>
       </c>
       <c r="C82" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$C:$C,MATCH($A82,Requerimientos!$A:$A,0)),"")</f>
-        <v>Cliente</v>
+        <v>Administrador de hotel</v>
       </c>
       <c r="D82" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A82,Requerimientos!$A:$A,0)),"")</f>
-        <v>M4 Reservas</v>
+        <v>M3 Catálogo</v>
       </c>
       <c r="E82" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A82,Requerimientos!$A:$A,0)),"")</f>
@@ -9342,11 +9507,11 @@
       </c>
       <c r="F82" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$H:$H,MATCH($A82,Requerimientos!$A:$A,0)),"")</f>
-        <v>L3  ·  L6</v>
+        <v>L3  ·  L6  ·  L7</v>
       </c>
       <c r="G82" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$I:$I,MATCH($A82,Requerimientos!$A:$A,0)),"")</f>
-        <v>Lab 6</v>
+        <v>Lab 7</v>
       </c>
       <c r="H82" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$J:$J,MATCH($A82,Requerimientos!$A:$A,0)),"")</f>
@@ -9355,31 +9520,31 @@
     </row>
     <row r="83" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A83" s="26" t="s">
-        <v>217</v>
+        <v>182</v>
       </c>
       <c r="B83" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A83,Requerimientos!$A:$A,0)),"")</f>
-        <v>Hacer checkout y registrar valoración y observaciones obligatorias</v>
+        <v>Ver el estado del taxista asignado en camino a recoger y llegó al destino</v>
       </c>
       <c r="C83" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$C:$C,MATCH($A83,Requerimientos!$A:$A,0)),"")</f>
-        <v>Cliente</v>
+        <v>Administrador de hotel</v>
       </c>
       <c r="D83" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A83,Requerimientos!$A:$A,0)),"")</f>
-        <v>M6 Checkout y valoraciones</v>
+        <v>M8 Taxi</v>
       </c>
       <c r="E83" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A83,Requerimientos!$A:$A,0)),"")</f>
-        <v>Alta</v>
+        <v>Media</v>
       </c>
       <c r="F83" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$H:$H,MATCH($A83,Requerimientos!$A:$A,0)),"")</f>
-        <v>L3  ·  L6</v>
+        <v>L3  ·  L6  ·  L7</v>
       </c>
       <c r="G83" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$I:$I,MATCH($A83,Requerimientos!$A:$A,0)),"")</f>
-        <v>Lab 6</v>
+        <v>Lab 7</v>
       </c>
       <c r="H83" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$J:$J,MATCH($A83,Requerimientos!$A:$A,0)),"")</f>
@@ -9388,19 +9553,19 @@
     </row>
     <row r="84" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A84" s="26" t="s">
-        <v>220</v>
+        <v>185</v>
       </c>
       <c r="B84" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A84,Requerimientos!$A:$A,0)),"")</f>
-        <v>Recibir notificación cuando se le hace el cobro</v>
+        <v>Acceder a la app móvil una vez habilitado</v>
       </c>
       <c r="C84" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$C:$C,MATCH($A84,Requerimientos!$A:$A,0)),"")</f>
-        <v>Cliente</v>
+        <v>Taxista</v>
       </c>
       <c r="D84" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A84,Requerimientos!$A:$A,0)),"")</f>
-        <v>M5 Pagos y cobros</v>
+        <v>M1 Autenticación</v>
       </c>
       <c r="E84" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A84,Requerimientos!$A:$A,0)),"")</f>
@@ -9408,7 +9573,7 @@
       </c>
       <c r="F84" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$H:$H,MATCH($A84,Requerimientos!$A:$A,0)),"")</f>
-        <v>L5  ·  L6</v>
+        <v>L3  ·  L5  ·  L6</v>
       </c>
       <c r="G84" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$I:$I,MATCH($A84,Requerimientos!$A:$A,0)),"")</f>
@@ -9421,19 +9586,19 @@
     </row>
     <row r="85" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A85" s="26" t="s">
-        <v>225</v>
+        <v>188</v>
       </c>
       <c r="B85" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A85,Requerimientos!$A:$A,0)),"")</f>
-        <v>Chat privado con el hotel entre la confirmación de la reserva y el fin del checkout</v>
+        <v>Ver hoteles y pedidos disponibles</v>
       </c>
       <c r="C85" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$C:$C,MATCH($A85,Requerimientos!$A:$A,0)),"")</f>
-        <v>Cliente</v>
+        <v>Taxista</v>
       </c>
       <c r="D85" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A85,Requerimientos!$A:$A,0)),"")</f>
-        <v>M7 Chat</v>
+        <v>M8 Taxi</v>
       </c>
       <c r="E85" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A85,Requerimientos!$A:$A,0)),"")</f>
@@ -9441,7 +9606,7 @@
       </c>
       <c r="F85" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$H:$H,MATCH($A85,Requerimientos!$A:$A,0)),"")</f>
-        <v>L3  ·  L4  ·  L6</v>
+        <v>L3  ·  L4  ·  L5  ·  L6</v>
       </c>
       <c r="G85" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$I:$I,MATCH($A85,Requerimientos!$A:$A,0)),"")</f>
@@ -9454,27 +9619,27 @@
     </row>
     <row r="86" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A86" s="26" t="s">
-        <v>229</v>
+        <v>191</v>
       </c>
       <c r="B86" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A86,Requerimientos!$A:$A,0)),"")</f>
-        <v>Ver el historial de sus reservas</v>
+        <v>Aceptar un pedido que deja de estar disponible para los demás</v>
       </c>
       <c r="C86" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$C:$C,MATCH($A86,Requerimientos!$A:$A,0)),"")</f>
-        <v>Cliente</v>
+        <v>Taxista</v>
       </c>
       <c r="D86" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A86,Requerimientos!$A:$A,0)),"")</f>
-        <v>M4 Reservas</v>
+        <v>M8 Taxi</v>
       </c>
       <c r="E86" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A86,Requerimientos!$A:$A,0)),"")</f>
-        <v>Media</v>
+        <v>Alta</v>
       </c>
       <c r="F86" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$H:$H,MATCH($A86,Requerimientos!$A:$A,0)),"")</f>
-        <v>L3  ·  L4  ·  L6</v>
+        <v>L3  ·  L6</v>
       </c>
       <c r="G86" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$I:$I,MATCH($A86,Requerimientos!$A:$A,0)),"")</f>
@@ -9487,15 +9652,15 @@
     </row>
     <row r="87" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A87" s="26" t="s">
-        <v>232</v>
+        <v>195</v>
       </c>
       <c r="B87" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A87,Requerimientos!$A:$A,0)),"")</f>
-        <v>Solicitar el taxi gratuito al aeropuerto si la reserva alcanza el monto mínimo</v>
+        <v>Actualizar los estados del servicio</v>
       </c>
       <c r="C87" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$C:$C,MATCH($A87,Requerimientos!$A:$A,0)),"")</f>
-        <v>Cliente</v>
+        <v>Taxista</v>
       </c>
       <c r="D87" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A87,Requerimientos!$A:$A,0)),"")</f>
@@ -9507,11 +9672,11 @@
       </c>
       <c r="F87" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$H:$H,MATCH($A87,Requerimientos!$A:$A,0)),"")</f>
-        <v>L3  ·  L6  ·  L7</v>
+        <v>L3  ·  L6</v>
       </c>
       <c r="G87" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$I:$I,MATCH($A87,Requerimientos!$A:$A,0)),"")</f>
-        <v>Lab 7</v>
+        <v>Lab 6</v>
       </c>
       <c r="H87" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$J:$J,MATCH($A87,Requerimientos!$A:$A,0)),"")</f>
@@ -9520,15 +9685,15 @@
     </row>
     <row r="88" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A88" s="26" t="s">
-        <v>242</v>
+        <v>198</v>
       </c>
       <c r="B88" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A88,Requerimientos!$A:$A,0)),"")</f>
-        <v>Calificar al taxista al finalizar el servicio</v>
+        <v>Registrar automáticamente su ubicación durante el servicio activo</v>
       </c>
       <c r="C88" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$C:$C,MATCH($A88,Requerimientos!$A:$A,0)),"")</f>
-        <v>Cliente</v>
+        <v>Taxista</v>
       </c>
       <c r="D88" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A88,Requerimientos!$A:$A,0)),"")</f>
@@ -9536,11 +9701,11 @@
       </c>
       <c r="E88" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A88,Requerimientos!$A:$A,0)),"")</f>
-        <v>Media</v>
+        <v>Alta</v>
       </c>
       <c r="F88" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$H:$H,MATCH($A88,Requerimientos!$A:$A,0)),"")</f>
-        <v>L3  ·  L6  ·  L7</v>
+        <v>L6  ·  L7</v>
       </c>
       <c r="G88" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$I:$I,MATCH($A88,Requerimientos!$A:$A,0)),"")</f>
@@ -9553,19 +9718,19 @@
     </row>
     <row r="89" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A89" s="26" t="s">
-        <v>251</v>
+        <v>211</v>
       </c>
       <c r="B89" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A89,Requerimientos!$A:$A,0)),"")</f>
-        <v>Una habitación no puede tener reservas de distintos clientes con períodos superpuestos</v>
+        <v>Autoregistrarse y quedar habilitado automáticamente</v>
       </c>
       <c r="C89" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$C:$C,MATCH($A89,Requerimientos!$A:$A,0)),"")</f>
-        <v>Transversal</v>
+        <v>Cliente</v>
       </c>
       <c r="D89" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A89,Requerimientos!$A:$A,0)),"")</f>
-        <v>M4 Reservas</v>
+        <v>M1 Autenticación</v>
       </c>
       <c r="E89" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A89,Requerimientos!$A:$A,0)),"")</f>
@@ -9573,7 +9738,7 @@
       </c>
       <c r="F89" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$H:$H,MATCH($A89,Requerimientos!$A:$A,0)),"")</f>
-        <v>L6</v>
+        <v>L3  ·  L5  ·  L6</v>
       </c>
       <c r="G89" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$I:$I,MATCH($A89,Requerimientos!$A:$A,0)),"")</f>
@@ -9586,19 +9751,19 @@
     </row>
     <row r="90" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A90" s="26" t="s">
-        <v>256</v>
+        <v>215</v>
       </c>
       <c r="B90" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A90,Requerimientos!$A:$A,0)),"")</f>
-        <v>Un mismo cliente no puede tener reservas con fechas de alojamiento superpuestas</v>
+        <v>Consultar hoteles habitaciones servicios disponibilidad y valoraciones</v>
       </c>
       <c r="C90" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$C:$C,MATCH($A90,Requerimientos!$A:$A,0)),"")</f>
-        <v>Transversal</v>
+        <v>Cliente</v>
       </c>
       <c r="D90" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A90,Requerimientos!$A:$A,0)),"")</f>
-        <v>M4 Reservas</v>
+        <v>M3 Catálogo</v>
       </c>
       <c r="E90" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A90,Requerimientos!$A:$A,0)),"")</f>
@@ -9606,7 +9771,7 @@
       </c>
       <c r="F90" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$H:$H,MATCH($A90,Requerimientos!$A:$A,0)),"")</f>
-        <v>L6</v>
+        <v>L3  ·  L4  ·  L6</v>
       </c>
       <c r="G90" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$I:$I,MATCH($A90,Requerimientos!$A:$A,0)),"")</f>
@@ -9619,19 +9784,19 @@
     </row>
     <row r="91" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A91" s="26" t="s">
-        <v>259</v>
+        <v>218</v>
       </c>
       <c r="B91" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A91,Requerimientos!$A:$A,0)),"")</f>
-        <v>Login único: tras autenticar se resuelve el rol y se navega al flujo correspondiente</v>
+        <v>Reservar con tarjeta de crédito o débito simulada</v>
       </c>
       <c r="C91" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$C:$C,MATCH($A91,Requerimientos!$A:$A,0)),"")</f>
-        <v>Transversal</v>
+        <v>Cliente</v>
       </c>
       <c r="D91" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A91,Requerimientos!$A:$A,0)),"")</f>
-        <v>M1 Autenticación</v>
+        <v>M4 Reservas</v>
       </c>
       <c r="E91" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A91,Requerimientos!$A:$A,0)),"")</f>
@@ -9652,19 +9817,19 @@
     </row>
     <row r="92" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A92" s="26" t="s">
-        <v>262</v>
+        <v>221</v>
       </c>
       <c r="B92" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A92,Requerimientos!$A:$A,0)),"")</f>
-        <v>Los mensajes de chat persisten con fecha y hora</v>
+        <v>Hacer checkout y registrar valoración y observaciones obligatorias</v>
       </c>
       <c r="C92" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$C:$C,MATCH($A92,Requerimientos!$A:$A,0)),"")</f>
-        <v>Transversal</v>
+        <v>Cliente</v>
       </c>
       <c r="D92" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A92,Requerimientos!$A:$A,0)),"")</f>
-        <v>M7 Chat</v>
+        <v>M6 Checkout y valoraciones</v>
       </c>
       <c r="E92" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A92,Requerimientos!$A:$A,0)),"")</f>
@@ -9672,7 +9837,7 @@
       </c>
       <c r="F92" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$H:$H,MATCH($A92,Requerimientos!$A:$A,0)),"")</f>
-        <v>L6</v>
+        <v>L3  ·  L6</v>
       </c>
       <c r="G92" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$I:$I,MATCH($A92,Requerimientos!$A:$A,0)),"")</f>
@@ -9685,19 +9850,19 @@
     </row>
     <row r="93" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A93" s="26" t="s">
-        <v>265</v>
+        <v>224</v>
       </c>
       <c r="B93" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A93,Requerimientos!$A:$A,0)),"")</f>
-        <v>Las contraseñas nunca se almacenan en texto plano</v>
+        <v>Recibir notificación cuando se le hace el cobro</v>
       </c>
       <c r="C93" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$C:$C,MATCH($A93,Requerimientos!$A:$A,0)),"")</f>
-        <v>Transversal</v>
+        <v>Cliente</v>
       </c>
       <c r="D93" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A93,Requerimientos!$A:$A,0)),"")</f>
-        <v>M10 Calidad</v>
+        <v>M5 Pagos y cobros</v>
       </c>
       <c r="E93" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A93,Requerimientos!$A:$A,0)),"")</f>
@@ -9705,7 +9870,7 @@
       </c>
       <c r="F93" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$H:$H,MATCH($A93,Requerimientos!$A:$A,0)),"")</f>
-        <v>L6</v>
+        <v>L3  ·  L5  ·  L6</v>
       </c>
       <c r="G93" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$I:$I,MATCH($A93,Requerimientos!$A:$A,0)),"")</f>
@@ -9718,19 +9883,19 @@
     </row>
     <row r="94" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A94" s="26" t="s">
-        <v>268</v>
+        <v>228</v>
       </c>
       <c r="B94" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A94,Requerimientos!$A:$A,0)),"")</f>
-        <v>Las operaciones están restringidas según el rol autenticado</v>
+        <v>Chat privado con el hotel entre la confirmación de la reserva y el fin del checkout</v>
       </c>
       <c r="C94" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$C:$C,MATCH($A94,Requerimientos!$A:$A,0)),"")</f>
-        <v>Transversal</v>
+        <v>Cliente</v>
       </c>
       <c r="D94" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A94,Requerimientos!$A:$A,0)),"")</f>
-        <v>M10 Calidad</v>
+        <v>M7 Chat</v>
       </c>
       <c r="E94" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A94,Requerimientos!$A:$A,0)),"")</f>
@@ -9738,7 +9903,7 @@
       </c>
       <c r="F94" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$H:$H,MATCH($A94,Requerimientos!$A:$A,0)),"")</f>
-        <v>L6</v>
+        <v>L3  ·  L4  ·  L6</v>
       </c>
       <c r="G94" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$I:$I,MATCH($A94,Requerimientos!$A:$A,0)),"")</f>
@@ -9751,27 +9916,27 @@
     </row>
     <row r="95" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A95" s="26" t="s">
-        <v>271</v>
+        <v>232</v>
       </c>
       <c r="B95" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A95,Requerimientos!$A:$A,0)),"")</f>
-        <v>Un cliente solo accede a sus propios datos</v>
+        <v>Ver el historial de sus reservas</v>
       </c>
       <c r="C95" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$C:$C,MATCH($A95,Requerimientos!$A:$A,0)),"")</f>
-        <v>Transversal</v>
+        <v>Cliente</v>
       </c>
       <c r="D95" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A95,Requerimientos!$A:$A,0)),"")</f>
-        <v>M10 Calidad</v>
+        <v>M4 Reservas</v>
       </c>
       <c r="E95" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A95,Requerimientos!$A:$A,0)),"")</f>
-        <v>Alta</v>
+        <v>Media</v>
       </c>
       <c r="F95" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$H:$H,MATCH($A95,Requerimientos!$A:$A,0)),"")</f>
-        <v>L6</v>
+        <v>L3  ·  L4  ·  L6</v>
       </c>
       <c r="G95" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$I:$I,MATCH($A95,Requerimientos!$A:$A,0)),"")</f>
@@ -9784,27 +9949,27 @@
     </row>
     <row r="96" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A96" s="26" t="s">
-        <v>274</v>
+        <v>235</v>
       </c>
       <c r="B96" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A96,Requerimientos!$A:$A,0)),"")</f>
-        <v>La persistencia de la app principal es una base de datos NoSQL</v>
+        <v>Consultar los lugares históricos cercanos al hotel</v>
       </c>
       <c r="C96" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$C:$C,MATCH($A96,Requerimientos!$A:$A,0)),"")</f>
-        <v>Transversal</v>
+        <v>Cliente</v>
       </c>
       <c r="D96" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A96,Requerimientos!$A:$A,0)),"")</f>
-        <v>M10 Calidad</v>
+        <v>M3 Catálogo</v>
       </c>
       <c r="E96" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A96,Requerimientos!$A:$A,0)),"")</f>
-        <v>Alta</v>
+        <v>Media</v>
       </c>
       <c r="F96" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$H:$H,MATCH($A96,Requerimientos!$A:$A,0)),"")</f>
-        <v>L6</v>
+        <v>L3  ·  L4  ·  L6</v>
       </c>
       <c r="G96" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$I:$I,MATCH($A96,Requerimientos!$A:$A,0)),"")</f>
@@ -9817,64 +9982,118 @@
     </row>
     <row r="97" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A97" s="26" t="s">
-        <v>277</v>
+        <v>239</v>
       </c>
       <c r="B97" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A97,Requerimientos!$A:$A,0)),"")</f>
-        <v>El sistema registra los eventos relevantes en logs consultables por el Superadmin</v>
+        <v>Solicitar el taxi gratuito al aeropuerto si la reserva alcanza el monto mínimo</v>
       </c>
       <c r="C97" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$C:$C,MATCH($A97,Requerimientos!$A:$A,0)),"")</f>
-        <v>Transversal</v>
+        <v>Cliente</v>
       </c>
       <c r="D97" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A97,Requerimientos!$A:$A,0)),"")</f>
-        <v>M10 Calidad</v>
+        <v>M8 Taxi</v>
       </c>
       <c r="E97" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A97,Requerimientos!$A:$A,0)),"")</f>
-        <v>Media</v>
+        <v>Alta</v>
       </c>
       <c r="F97" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$H:$H,MATCH($A97,Requerimientos!$A:$A,0)),"")</f>
-        <v>L6</v>
+        <v>L3  ·  L6  ·  L7</v>
       </c>
       <c r="G97" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$I:$I,MATCH($A97,Requerimientos!$A:$A,0)),"")</f>
-        <v>Lab 6</v>
+        <v>Lab 7</v>
       </c>
       <c r="H97" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$J:$J,MATCH($A97,Requerimientos!$A:$A,0)),"")</f>
         <v>Pendiente</v>
       </c>
     </row>
-    <row r="99" spans="1:8" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="29" t="s">
-        <v>307</v>
-      </c>
-      <c r="B99" s="30"/>
-      <c r="C99" s="30"/>
-      <c r="D99" s="30"/>
-      <c r="E99" s="30"/>
-      <c r="F99" s="30"/>
-      <c r="G99" s="30"/>
-      <c r="H99" s="30"/>
+    <row r="98" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A98" s="26" t="s">
+        <v>249</v>
+      </c>
+      <c r="B98" s="3" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A98,Requerimientos!$A:$A,0)),"")</f>
+        <v>Calificar al taxista al finalizar el servicio</v>
+      </c>
+      <c r="C98" s="24" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$C:$C,MATCH($A98,Requerimientos!$A:$A,0)),"")</f>
+        <v>Cliente</v>
+      </c>
+      <c r="D98" s="24" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A98,Requerimientos!$A:$A,0)),"")</f>
+        <v>M8 Taxi</v>
+      </c>
+      <c r="E98" s="24" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A98,Requerimientos!$A:$A,0)),"")</f>
+        <v>Media</v>
+      </c>
+      <c r="F98" s="24" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$H:$H,MATCH($A98,Requerimientos!$A:$A,0)),"")</f>
+        <v>L3  ·  L6  ·  L7</v>
+      </c>
+      <c r="G98" s="24" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$I:$I,MATCH($A98,Requerimientos!$A:$A,0)),"")</f>
+        <v>Lab 7</v>
+      </c>
+      <c r="H98" s="24" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$J:$J,MATCH($A98,Requerimientos!$A:$A,0)),"")</f>
+        <v>Pendiente</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A99" s="26" t="s">
+        <v>258</v>
+      </c>
+      <c r="B99" s="3" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A99,Requerimientos!$A:$A,0)),"")</f>
+        <v>Una habitación no puede tener reservas de distintos clientes con períodos superpuestos</v>
+      </c>
+      <c r="C99" s="24" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$C:$C,MATCH($A99,Requerimientos!$A:$A,0)),"")</f>
+        <v>Transversal</v>
+      </c>
+      <c r="D99" s="24" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A99,Requerimientos!$A:$A,0)),"")</f>
+        <v>M4 Reservas</v>
+      </c>
+      <c r="E99" s="24" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A99,Requerimientos!$A:$A,0)),"")</f>
+        <v>Alta</v>
+      </c>
+      <c r="F99" s="24" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$H:$H,MATCH($A99,Requerimientos!$A:$A,0)),"")</f>
+        <v>L3  ·  L6</v>
+      </c>
+      <c r="G99" s="24" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$I:$I,MATCH($A99,Requerimientos!$A:$A,0)),"")</f>
+        <v>Lab 6</v>
+      </c>
+      <c r="H99" s="24" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$J:$J,MATCH($A99,Requerimientos!$A:$A,0)),"")</f>
+        <v>Pendiente</v>
+      </c>
     </row>
     <row r="100" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A100" s="26" t="s">
-        <v>173</v>
+        <v>262</v>
       </c>
       <c r="B100" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A100,Requerimientos!$A:$A,0)),"")</f>
-        <v>Registrar la ubicación del hotel y los lugares históricos cercanos</v>
+        <v>Un mismo cliente no puede tener reservas con fechas de alojamiento superpuestas</v>
       </c>
       <c r="C100" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$C:$C,MATCH($A100,Requerimientos!$A:$A,0)),"")</f>
-        <v>Administrador de hotel</v>
+        <v>Transversal</v>
       </c>
       <c r="D100" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A100,Requerimientos!$A:$A,0)),"")</f>
-        <v>M3 Catálogo</v>
+        <v>M4 Reservas</v>
       </c>
       <c r="E100" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A100,Requerimientos!$A:$A,0)),"")</f>
@@ -9882,11 +10101,11 @@
       </c>
       <c r="F100" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$H:$H,MATCH($A100,Requerimientos!$A:$A,0)),"")</f>
-        <v>L3  ·  L6  ·  L7</v>
+        <v>L3  ·  L6</v>
       </c>
       <c r="G100" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$I:$I,MATCH($A100,Requerimientos!$A:$A,0)),"")</f>
-        <v>Lab 7</v>
+        <v>Lab 6</v>
       </c>
       <c r="H100" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$J:$J,MATCH($A100,Requerimientos!$A:$A,0)),"")</f>
@@ -9895,31 +10114,31 @@
     </row>
     <row r="101" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A101" s="26" t="s">
-        <v>178</v>
+        <v>265</v>
       </c>
       <c r="B101" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A101,Requerimientos!$A:$A,0)),"")</f>
-        <v>Ver el estado del taxista asignado en camino a recoger y llegó al destino</v>
+        <v>Login único: tras autenticar se resuelve el rol y se navega al flujo correspondiente</v>
       </c>
       <c r="C101" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$C:$C,MATCH($A101,Requerimientos!$A:$A,0)),"")</f>
-        <v>Administrador de hotel</v>
+        <v>Transversal</v>
       </c>
       <c r="D101" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A101,Requerimientos!$A:$A,0)),"")</f>
-        <v>M8 Taxi</v>
+        <v>M1 Autenticación</v>
       </c>
       <c r="E101" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A101,Requerimientos!$A:$A,0)),"")</f>
-        <v>Media</v>
+        <v>Alta</v>
       </c>
       <c r="F101" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$H:$H,MATCH($A101,Requerimientos!$A:$A,0)),"")</f>
-        <v>L3  ·  L6  ·  L7</v>
+        <v>L3  ·  L6</v>
       </c>
       <c r="G101" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$I:$I,MATCH($A101,Requerimientos!$A:$A,0)),"")</f>
-        <v>Lab 7</v>
+        <v>Lab 6</v>
       </c>
       <c r="H101" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$J:$J,MATCH($A101,Requerimientos!$A:$A,0)),"")</f>
@@ -9928,19 +10147,19 @@
     </row>
     <row r="102" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A102" s="26" t="s">
-        <v>194</v>
+        <v>268</v>
       </c>
       <c r="B102" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A102,Requerimientos!$A:$A,0)),"")</f>
-        <v>Registrar automáticamente su ubicación durante el servicio activo</v>
+        <v>Los mensajes de chat persisten con fecha y hora</v>
       </c>
       <c r="C102" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$C:$C,MATCH($A102,Requerimientos!$A:$A,0)),"")</f>
-        <v>Taxista</v>
+        <v>Transversal</v>
       </c>
       <c r="D102" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A102,Requerimientos!$A:$A,0)),"")</f>
-        <v>M8 Taxi</v>
+        <v>M7 Chat</v>
       </c>
       <c r="E102" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A102,Requerimientos!$A:$A,0)),"")</f>
@@ -9948,11 +10167,11 @@
       </c>
       <c r="F102" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$H:$H,MATCH($A102,Requerimientos!$A:$A,0)),"")</f>
-        <v>L6  ·  L7</v>
+        <v>L3  ·  L4  ·  L6</v>
       </c>
       <c r="G102" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$I:$I,MATCH($A102,Requerimientos!$A:$A,0)),"")</f>
-        <v>Lab 7</v>
+        <v>Lab 6</v>
       </c>
       <c r="H102" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$J:$J,MATCH($A102,Requerimientos!$A:$A,0)),"")</f>
@@ -9961,19 +10180,19 @@
     </row>
     <row r="103" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A103" s="26" t="s">
-        <v>199</v>
+        <v>271</v>
       </c>
       <c r="B103" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A103,Requerimientos!$A:$A,0)),"")</f>
-        <v>Registrar FINALIZADO únicamente escaneando el QR del cliente</v>
+        <v>Las contraseñas nunca se almacenan en texto plano</v>
       </c>
       <c r="C103" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$C:$C,MATCH($A103,Requerimientos!$A:$A,0)),"")</f>
-        <v>Taxista</v>
+        <v>Transversal</v>
       </c>
       <c r="D103" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A103,Requerimientos!$A:$A,0)),"")</f>
-        <v>M8 Taxi</v>
+        <v>M10 Calidad</v>
       </c>
       <c r="E103" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A103,Requerimientos!$A:$A,0)),"")</f>
@@ -9981,11 +10200,11 @@
       </c>
       <c r="F103" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$H:$H,MATCH($A103,Requerimientos!$A:$A,0)),"")</f>
-        <v>L3  ·  L7</v>
+        <v>L6</v>
       </c>
       <c r="G103" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$I:$I,MATCH($A103,Requerimientos!$A:$A,0)),"")</f>
-        <v>Lab 7</v>
+        <v>Lab 6</v>
       </c>
       <c r="H103" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$J:$J,MATCH($A103,Requerimientos!$A:$A,0)),"")</f>
@@ -9994,19 +10213,19 @@
     </row>
     <row r="104" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A104" s="26" t="s">
-        <v>232</v>
+        <v>275</v>
       </c>
       <c r="B104" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A104,Requerimientos!$A:$A,0)),"")</f>
-        <v>Solicitar el taxi gratuito al aeropuerto si la reserva alcanza el monto mínimo</v>
+        <v>Las operaciones están restringidas según el rol autenticado</v>
       </c>
       <c r="C104" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$C:$C,MATCH($A104,Requerimientos!$A:$A,0)),"")</f>
-        <v>Cliente</v>
+        <v>Transversal</v>
       </c>
       <c r="D104" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A104,Requerimientos!$A:$A,0)),"")</f>
-        <v>M8 Taxi</v>
+        <v>M10 Calidad</v>
       </c>
       <c r="E104" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A104,Requerimientos!$A:$A,0)),"")</f>
@@ -10014,11 +10233,11 @@
       </c>
       <c r="F104" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$H:$H,MATCH($A104,Requerimientos!$A:$A,0)),"")</f>
-        <v>L3  ·  L6  ·  L7</v>
+        <v>L6</v>
       </c>
       <c r="G104" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$I:$I,MATCH($A104,Requerimientos!$A:$A,0)),"")</f>
-        <v>Lab 7</v>
+        <v>Lab 6</v>
       </c>
       <c r="H104" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$J:$J,MATCH($A104,Requerimientos!$A:$A,0)),"")</f>
@@ -10027,19 +10246,19 @@
     </row>
     <row r="105" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A105" s="26" t="s">
-        <v>235</v>
+        <v>278</v>
       </c>
       <c r="B105" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A105,Requerimientos!$A:$A,0)),"")</f>
-        <v>Ver datos vehículo valoración y ubicación del taxista en un mapa</v>
+        <v>Un cliente solo accede a sus propios datos</v>
       </c>
       <c r="C105" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$C:$C,MATCH($A105,Requerimientos!$A:$A,0)),"")</f>
-        <v>Cliente</v>
+        <v>Transversal</v>
       </c>
       <c r="D105" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A105,Requerimientos!$A:$A,0)),"")</f>
-        <v>M8 Taxi</v>
+        <v>M10 Calidad</v>
       </c>
       <c r="E105" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A105,Requerimientos!$A:$A,0)),"")</f>
@@ -10047,11 +10266,11 @@
       </c>
       <c r="F105" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$H:$H,MATCH($A105,Requerimientos!$A:$A,0)),"")</f>
-        <v>L3  ·  L7</v>
+        <v>L6</v>
       </c>
       <c r="G105" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$I:$I,MATCH($A105,Requerimientos!$A:$A,0)),"")</f>
-        <v>Lab 7</v>
+        <v>Lab 6</v>
       </c>
       <c r="H105" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$J:$J,MATCH($A105,Requerimientos!$A:$A,0)),"")</f>
@@ -10060,19 +10279,19 @@
     </row>
     <row r="106" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A106" s="26" t="s">
-        <v>239</v>
+        <v>281</v>
       </c>
       <c r="B106" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A106,Requerimientos!$A:$A,0)),"")</f>
-        <v>Recibir el QR del hotel y mostrarlo al llegar</v>
+        <v>La persistencia de la app principal es una base de datos NoSQL</v>
       </c>
       <c r="C106" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$C:$C,MATCH($A106,Requerimientos!$A:$A,0)),"")</f>
-        <v>Cliente</v>
+        <v>Transversal</v>
       </c>
       <c r="D106" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A106,Requerimientos!$A:$A,0)),"")</f>
-        <v>M8 Taxi</v>
+        <v>M10 Calidad</v>
       </c>
       <c r="E106" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A106,Requerimientos!$A:$A,0)),"")</f>
@@ -10080,11 +10299,11 @@
       </c>
       <c r="F106" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$H:$H,MATCH($A106,Requerimientos!$A:$A,0)),"")</f>
-        <v>L3  ·  L7</v>
+        <v>L6</v>
       </c>
       <c r="G106" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$I:$I,MATCH($A106,Requerimientos!$A:$A,0)),"")</f>
-        <v>Lab 7</v>
+        <v>Lab 6</v>
       </c>
       <c r="H106" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$J:$J,MATCH($A106,Requerimientos!$A:$A,0)),"")</f>
@@ -10093,19 +10312,19 @@
     </row>
     <row r="107" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A107" s="26" t="s">
-        <v>242</v>
+        <v>284</v>
       </c>
       <c r="B107" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A107,Requerimientos!$A:$A,0)),"")</f>
-        <v>Calificar al taxista al finalizar el servicio</v>
+        <v>El sistema registra los eventos relevantes en logs consultables por el Superadmin</v>
       </c>
       <c r="C107" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$C:$C,MATCH($A107,Requerimientos!$A:$A,0)),"")</f>
-        <v>Cliente</v>
+        <v>Transversal</v>
       </c>
       <c r="D107" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A107,Requerimientos!$A:$A,0)),"")</f>
-        <v>M8 Taxi</v>
+        <v>M10 Calidad</v>
       </c>
       <c r="E107" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A107,Requerimientos!$A:$A,0)),"")</f>
@@ -10113,98 +10332,44 @@
       </c>
       <c r="F107" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$H:$H,MATCH($A107,Requerimientos!$A:$A,0)),"")</f>
-        <v>L3  ·  L6  ·  L7</v>
+        <v>L6</v>
       </c>
       <c r="G107" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$I:$I,MATCH($A107,Requerimientos!$A:$A,0)),"")</f>
-        <v>Lab 7</v>
+        <v>Lab 6</v>
       </c>
       <c r="H107" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$J:$J,MATCH($A107,Requerimientos!$A:$A,0)),"")</f>
         <v>Pendiente</v>
       </c>
     </row>
-    <row r="108" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A108" s="26" t="s">
-        <v>280</v>
-      </c>
-      <c r="B108" s="3" t="str">
-        <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A108,Requerimientos!$A:$A,0)),"")</f>
-        <v>La ubicación del taxista se actualiza periódicamente durante un servicio activo</v>
-      </c>
-      <c r="C108" s="24" t="str">
-        <f>IFERROR(INDEX(Requerimientos!$C:$C,MATCH($A108,Requerimientos!$A:$A,0)),"")</f>
-        <v>Transversal</v>
-      </c>
-      <c r="D108" s="24" t="str">
-        <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A108,Requerimientos!$A:$A,0)),"")</f>
-        <v>M10 Calidad</v>
-      </c>
-      <c r="E108" s="24" t="str">
-        <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A108,Requerimientos!$A:$A,0)),"")</f>
-        <v>Alta</v>
-      </c>
-      <c r="F108" s="24" t="str">
-        <f>IFERROR(INDEX(Requerimientos!$H:$H,MATCH($A108,Requerimientos!$A:$A,0)),"")</f>
-        <v>L7</v>
-      </c>
-      <c r="G108" s="24" t="str">
-        <f>IFERROR(INDEX(Requerimientos!$I:$I,MATCH($A108,Requerimientos!$A:$A,0)),"")</f>
-        <v>Lab 7</v>
-      </c>
-      <c r="H108" s="24" t="str">
-        <f>IFERROR(INDEX(Requerimientos!$J:$J,MATCH($A108,Requerimientos!$A:$A,0)),"")</f>
-        <v>Pendiente</v>
-      </c>
-    </row>
-    <row r="109" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A109" s="26" t="s">
-        <v>284</v>
-      </c>
-      <c r="B109" s="3" t="str">
-        <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A109,Requerimientos!$A:$A,0)),"")</f>
-        <v>Si la API de taxistas está caída la app lo informa sin afectar el resto del sistema</v>
-      </c>
-      <c r="C109" s="24" t="str">
-        <f>IFERROR(INDEX(Requerimientos!$C:$C,MATCH($A109,Requerimientos!$A:$A,0)),"")</f>
-        <v>Transversal</v>
-      </c>
-      <c r="D109" s="24" t="str">
-        <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A109,Requerimientos!$A:$A,0)),"")</f>
-        <v>M10 Calidad</v>
-      </c>
-      <c r="E109" s="24" t="str">
-        <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A109,Requerimientos!$A:$A,0)),"")</f>
-        <v>Alta</v>
-      </c>
-      <c r="F109" s="24" t="str">
-        <f>IFERROR(INDEX(Requerimientos!$H:$H,MATCH($A109,Requerimientos!$A:$A,0)),"")</f>
-        <v>L7</v>
-      </c>
-      <c r="G109" s="24" t="str">
-        <f>IFERROR(INDEX(Requerimientos!$I:$I,MATCH($A109,Requerimientos!$A:$A,0)),"")</f>
-        <v>Lab 7</v>
-      </c>
-      <c r="H109" s="24" t="str">
-        <f>IFERROR(INDEX(Requerimientos!$J:$J,MATCH($A109,Requerimientos!$A:$A,0)),"")</f>
-        <v>Pendiente</v>
-      </c>
+    <row r="109" spans="1:8" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A109" s="29" t="s">
+        <v>314</v>
+      </c>
+      <c r="B109" s="30"/>
+      <c r="C109" s="30"/>
+      <c r="D109" s="30"/>
+      <c r="E109" s="30"/>
+      <c r="F109" s="30"/>
+      <c r="G109" s="30"/>
+      <c r="H109" s="30"/>
     </row>
     <row r="110" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A110" s="26" t="s">
-        <v>288</v>
+        <v>177</v>
       </c>
       <c r="B110" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A110,Requerimientos!$A:$A,0)),"")</f>
-        <v>La app móvil no accede directamente a la base de datos del sistema de taxistas</v>
+        <v>Registrar la ubicación del hotel y los lugares históricos cercanos</v>
       </c>
       <c r="C110" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$C:$C,MATCH($A110,Requerimientos!$A:$A,0)),"")</f>
-        <v>Transversal</v>
+        <v>Administrador de hotel</v>
       </c>
       <c r="D110" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A110,Requerimientos!$A:$A,0)),"")</f>
-        <v>M10 Calidad</v>
+        <v>M3 Catálogo</v>
       </c>
       <c r="E110" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A110,Requerimientos!$A:$A,0)),"")</f>
@@ -10212,44 +10377,98 @@
       </c>
       <c r="F110" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$H:$H,MATCH($A110,Requerimientos!$A:$A,0)),"")</f>
-        <v>L7  ·  Web</v>
+        <v>L3  ·  L6  ·  L7</v>
       </c>
       <c r="G110" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$I:$I,MATCH($A110,Requerimientos!$A:$A,0)),"")</f>
-        <v>App web</v>
+        <v>Lab 7</v>
       </c>
       <c r="H110" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$J:$J,MATCH($A110,Requerimientos!$A:$A,0)),"")</f>
         <v>Pendiente</v>
       </c>
     </row>
-    <row r="112" spans="1:8" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A112" s="29" t="s">
-        <v>308</v>
-      </c>
-      <c r="B112" s="30"/>
-      <c r="C112" s="30"/>
-      <c r="D112" s="30"/>
-      <c r="E112" s="30"/>
-      <c r="F112" s="30"/>
-      <c r="G112" s="30"/>
-      <c r="H112" s="30"/>
+    <row r="111" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A111" s="26" t="s">
+        <v>182</v>
+      </c>
+      <c r="B111" s="3" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A111,Requerimientos!$A:$A,0)),"")</f>
+        <v>Ver el estado del taxista asignado en camino a recoger y llegó al destino</v>
+      </c>
+      <c r="C111" s="24" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$C:$C,MATCH($A111,Requerimientos!$A:$A,0)),"")</f>
+        <v>Administrador de hotel</v>
+      </c>
+      <c r="D111" s="24" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A111,Requerimientos!$A:$A,0)),"")</f>
+        <v>M8 Taxi</v>
+      </c>
+      <c r="E111" s="24" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A111,Requerimientos!$A:$A,0)),"")</f>
+        <v>Media</v>
+      </c>
+      <c r="F111" s="24" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$H:$H,MATCH($A111,Requerimientos!$A:$A,0)),"")</f>
+        <v>L3  ·  L6  ·  L7</v>
+      </c>
+      <c r="G111" s="24" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$I:$I,MATCH($A111,Requerimientos!$A:$A,0)),"")</f>
+        <v>Lab 7</v>
+      </c>
+      <c r="H111" s="24" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$J:$J,MATCH($A111,Requerimientos!$A:$A,0)),"")</f>
+        <v>Pendiente</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A112" s="26" t="s">
+        <v>198</v>
+      </c>
+      <c r="B112" s="3" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A112,Requerimientos!$A:$A,0)),"")</f>
+        <v>Registrar automáticamente su ubicación durante el servicio activo</v>
+      </c>
+      <c r="C112" s="24" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$C:$C,MATCH($A112,Requerimientos!$A:$A,0)),"")</f>
+        <v>Taxista</v>
+      </c>
+      <c r="D112" s="24" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A112,Requerimientos!$A:$A,0)),"")</f>
+        <v>M8 Taxi</v>
+      </c>
+      <c r="E112" s="24" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A112,Requerimientos!$A:$A,0)),"")</f>
+        <v>Alta</v>
+      </c>
+      <c r="F112" s="24" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$H:$H,MATCH($A112,Requerimientos!$A:$A,0)),"")</f>
+        <v>L6  ·  L7</v>
+      </c>
+      <c r="G112" s="24" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$I:$I,MATCH($A112,Requerimientos!$A:$A,0)),"")</f>
+        <v>Lab 7</v>
+      </c>
+      <c r="H112" s="24" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$J:$J,MATCH($A112,Requerimientos!$A:$A,0)),"")</f>
+        <v>Pendiente</v>
+      </c>
     </row>
     <row r="113" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A113" s="26" t="s">
-        <v>141</v>
+        <v>203</v>
       </c>
       <c r="B113" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A113,Requerimientos!$A:$A,0)),"")</f>
-        <v>Aprobar o habilitar taxistas desde la app web</v>
+        <v>Registrar FINALIZADO únicamente escaneando el QR del cliente</v>
       </c>
       <c r="C113" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$C:$C,MATCH($A113,Requerimientos!$A:$A,0)),"")</f>
-        <v>Superadmin</v>
+        <v>Taxista</v>
       </c>
       <c r="D113" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A113,Requerimientos!$A:$A,0)),"")</f>
-        <v>M2 Gestión de usuarios</v>
+        <v>M8 Taxi</v>
       </c>
       <c r="E113" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A113,Requerimientos!$A:$A,0)),"")</f>
@@ -10257,11 +10476,11 @@
       </c>
       <c r="F113" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$H:$H,MATCH($A113,Requerimientos!$A:$A,0)),"")</f>
-        <v>Web</v>
+        <v>L3  ·  L7</v>
       </c>
       <c r="G113" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$I:$I,MATCH($A113,Requerimientos!$A:$A,0)),"")</f>
-        <v>App web</v>
+        <v>Lab 7</v>
       </c>
       <c r="H113" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$J:$J,MATCH($A113,Requerimientos!$A:$A,0)),"")</f>
@@ -10270,19 +10489,19 @@
     </row>
     <row r="114" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A114" s="26" t="s">
-        <v>204</v>
+        <v>239</v>
       </c>
       <c r="B114" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A114,Requerimientos!$A:$A,0)),"")</f>
-        <v>Autoregistrarse en la app web con todos sus datos y fotos</v>
+        <v>Solicitar el taxi gratuito al aeropuerto si la reserva alcanza el monto mínimo</v>
       </c>
       <c r="C114" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$C:$C,MATCH($A114,Requerimientos!$A:$A,0)),"")</f>
-        <v>Taxista</v>
+        <v>Cliente</v>
       </c>
       <c r="D114" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A114,Requerimientos!$A:$A,0)),"")</f>
-        <v>M1 Autenticación</v>
+        <v>M8 Taxi</v>
       </c>
       <c r="E114" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A114,Requerimientos!$A:$A,0)),"")</f>
@@ -10290,11 +10509,11 @@
       </c>
       <c r="F114" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$H:$H,MATCH($A114,Requerimientos!$A:$A,0)),"")</f>
-        <v>Web</v>
+        <v>L3  ·  L6  ·  L7</v>
       </c>
       <c r="G114" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$I:$I,MATCH($A114,Requerimientos!$A:$A,0)),"")</f>
-        <v>App web</v>
+        <v>Lab 7</v>
       </c>
       <c r="H114" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$J:$J,MATCH($A114,Requerimientos!$A:$A,0)),"")</f>
@@ -10303,19 +10522,19 @@
     </row>
     <row r="115" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A115" s="26" t="s">
-        <v>288</v>
+        <v>242</v>
       </c>
       <c r="B115" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A115,Requerimientos!$A:$A,0)),"")</f>
-        <v>La app móvil no accede directamente a la base de datos del sistema de taxistas</v>
+        <v>Ver datos vehículo valoración y ubicación del taxista en un mapa</v>
       </c>
       <c r="C115" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$C:$C,MATCH($A115,Requerimientos!$A:$A,0)),"")</f>
-        <v>Transversal</v>
+        <v>Cliente</v>
       </c>
       <c r="D115" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A115,Requerimientos!$A:$A,0)),"")</f>
-        <v>M10 Calidad</v>
+        <v>M8 Taxi</v>
       </c>
       <c r="E115" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A115,Requerimientos!$A:$A,0)),"")</f>
@@ -10323,30 +10542,306 @@
       </c>
       <c r="F115" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$H:$H,MATCH($A115,Requerimientos!$A:$A,0)),"")</f>
-        <v>L7  ·  Web</v>
+        <v>L3  ·  L7</v>
       </c>
       <c r="G115" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$I:$I,MATCH($A115,Requerimientos!$A:$A,0)),"")</f>
-        <v>App web</v>
+        <v>Lab 7</v>
       </c>
       <c r="H115" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$J:$J,MATCH($A115,Requerimientos!$A:$A,0)),"")</f>
         <v>Pendiente</v>
       </c>
     </row>
+    <row r="116" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A116" s="26" t="s">
+        <v>246</v>
+      </c>
+      <c r="B116" s="3" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A116,Requerimientos!$A:$A,0)),"")</f>
+        <v>Recibir el QR del hotel y mostrarlo al llegar</v>
+      </c>
+      <c r="C116" s="24" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$C:$C,MATCH($A116,Requerimientos!$A:$A,0)),"")</f>
+        <v>Cliente</v>
+      </c>
+      <c r="D116" s="24" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A116,Requerimientos!$A:$A,0)),"")</f>
+        <v>M8 Taxi</v>
+      </c>
+      <c r="E116" s="24" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A116,Requerimientos!$A:$A,0)),"")</f>
+        <v>Alta</v>
+      </c>
+      <c r="F116" s="24" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$H:$H,MATCH($A116,Requerimientos!$A:$A,0)),"")</f>
+        <v>L3  ·  L7</v>
+      </c>
+      <c r="G116" s="24" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$I:$I,MATCH($A116,Requerimientos!$A:$A,0)),"")</f>
+        <v>Lab 7</v>
+      </c>
+      <c r="H116" s="24" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$J:$J,MATCH($A116,Requerimientos!$A:$A,0)),"")</f>
+        <v>Pendiente</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A117" s="26" t="s">
+        <v>249</v>
+      </c>
+      <c r="B117" s="3" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A117,Requerimientos!$A:$A,0)),"")</f>
+        <v>Calificar al taxista al finalizar el servicio</v>
+      </c>
+      <c r="C117" s="24" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$C:$C,MATCH($A117,Requerimientos!$A:$A,0)),"")</f>
+        <v>Cliente</v>
+      </c>
+      <c r="D117" s="24" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A117,Requerimientos!$A:$A,0)),"")</f>
+        <v>M8 Taxi</v>
+      </c>
+      <c r="E117" s="24" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A117,Requerimientos!$A:$A,0)),"")</f>
+        <v>Media</v>
+      </c>
+      <c r="F117" s="24" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$H:$H,MATCH($A117,Requerimientos!$A:$A,0)),"")</f>
+        <v>L3  ·  L6  ·  L7</v>
+      </c>
+      <c r="G117" s="24" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$I:$I,MATCH($A117,Requerimientos!$A:$A,0)),"")</f>
+        <v>Lab 7</v>
+      </c>
+      <c r="H117" s="24" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$J:$J,MATCH($A117,Requerimientos!$A:$A,0)),"")</f>
+        <v>Pendiente</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A118" s="26" t="s">
+        <v>287</v>
+      </c>
+      <c r="B118" s="3" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A118,Requerimientos!$A:$A,0)),"")</f>
+        <v>La ubicación del taxista se actualiza periódicamente durante un servicio activo</v>
+      </c>
+      <c r="C118" s="24" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$C:$C,MATCH($A118,Requerimientos!$A:$A,0)),"")</f>
+        <v>Transversal</v>
+      </c>
+      <c r="D118" s="24" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A118,Requerimientos!$A:$A,0)),"")</f>
+        <v>M10 Calidad</v>
+      </c>
+      <c r="E118" s="24" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A118,Requerimientos!$A:$A,0)),"")</f>
+        <v>Alta</v>
+      </c>
+      <c r="F118" s="24" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$H:$H,MATCH($A118,Requerimientos!$A:$A,0)),"")</f>
+        <v>L7</v>
+      </c>
+      <c r="G118" s="24" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$I:$I,MATCH($A118,Requerimientos!$A:$A,0)),"")</f>
+        <v>Lab 7</v>
+      </c>
+      <c r="H118" s="24" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$J:$J,MATCH($A118,Requerimientos!$A:$A,0)),"")</f>
+        <v>Pendiente</v>
+      </c>
+    </row>
+    <row r="119" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A119" s="26" t="s">
+        <v>291</v>
+      </c>
+      <c r="B119" s="3" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A119,Requerimientos!$A:$A,0)),"")</f>
+        <v>Si la API de taxistas está caída la app lo informa sin afectar el resto del sistema</v>
+      </c>
+      <c r="C119" s="24" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$C:$C,MATCH($A119,Requerimientos!$A:$A,0)),"")</f>
+        <v>Transversal</v>
+      </c>
+      <c r="D119" s="24" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A119,Requerimientos!$A:$A,0)),"")</f>
+        <v>M10 Calidad</v>
+      </c>
+      <c r="E119" s="24" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A119,Requerimientos!$A:$A,0)),"")</f>
+        <v>Alta</v>
+      </c>
+      <c r="F119" s="24" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$H:$H,MATCH($A119,Requerimientos!$A:$A,0)),"")</f>
+        <v>L7</v>
+      </c>
+      <c r="G119" s="24" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$I:$I,MATCH($A119,Requerimientos!$A:$A,0)),"")</f>
+        <v>Lab 7</v>
+      </c>
+      <c r="H119" s="24" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$J:$J,MATCH($A119,Requerimientos!$A:$A,0)),"")</f>
+        <v>Pendiente</v>
+      </c>
+    </row>
+    <row r="120" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A120" s="26" t="s">
+        <v>295</v>
+      </c>
+      <c r="B120" s="3" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A120,Requerimientos!$A:$A,0)),"")</f>
+        <v>La app móvil no accede directamente a la base de datos del sistema de taxistas</v>
+      </c>
+      <c r="C120" s="24" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$C:$C,MATCH($A120,Requerimientos!$A:$A,0)),"")</f>
+        <v>Transversal</v>
+      </c>
+      <c r="D120" s="24" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A120,Requerimientos!$A:$A,0)),"")</f>
+        <v>M10 Calidad</v>
+      </c>
+      <c r="E120" s="24" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A120,Requerimientos!$A:$A,0)),"")</f>
+        <v>Alta</v>
+      </c>
+      <c r="F120" s="24" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$H:$H,MATCH($A120,Requerimientos!$A:$A,0)),"")</f>
+        <v>L7  ·  Web</v>
+      </c>
+      <c r="G120" s="24" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$I:$I,MATCH($A120,Requerimientos!$A:$A,0)),"")</f>
+        <v>App web</v>
+      </c>
+      <c r="H120" s="24" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$J:$J,MATCH($A120,Requerimientos!$A:$A,0)),"")</f>
+        <v>Pendiente</v>
+      </c>
+    </row>
+    <row r="122" spans="1:8" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A122" s="29" t="s">
+        <v>315</v>
+      </c>
+      <c r="B122" s="30"/>
+      <c r="C122" s="30"/>
+      <c r="D122" s="30"/>
+      <c r="E122" s="30"/>
+      <c r="F122" s="30"/>
+      <c r="G122" s="30"/>
+      <c r="H122" s="30"/>
+    </row>
+    <row r="123" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A123" s="26" t="s">
+        <v>141</v>
+      </c>
+      <c r="B123" s="3" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A123,Requerimientos!$A:$A,0)),"")</f>
+        <v>Aprobar o habilitar taxistas desde la app web</v>
+      </c>
+      <c r="C123" s="24" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$C:$C,MATCH($A123,Requerimientos!$A:$A,0)),"")</f>
+        <v>Superadmin</v>
+      </c>
+      <c r="D123" s="24" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A123,Requerimientos!$A:$A,0)),"")</f>
+        <v>M2 Gestión de usuarios</v>
+      </c>
+      <c r="E123" s="24" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A123,Requerimientos!$A:$A,0)),"")</f>
+        <v>Alta</v>
+      </c>
+      <c r="F123" s="24" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$H:$H,MATCH($A123,Requerimientos!$A:$A,0)),"")</f>
+        <v>Web</v>
+      </c>
+      <c r="G123" s="24" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$I:$I,MATCH($A123,Requerimientos!$A:$A,0)),"")</f>
+        <v>App web</v>
+      </c>
+      <c r="H123" s="24" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$J:$J,MATCH($A123,Requerimientos!$A:$A,0)),"")</f>
+        <v>Pendiente</v>
+      </c>
+    </row>
+    <row r="124" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A124" s="26" t="s">
+        <v>208</v>
+      </c>
+      <c r="B124" s="3" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A124,Requerimientos!$A:$A,0)),"")</f>
+        <v>Autoregistrarse en la app web con todos sus datos y fotos</v>
+      </c>
+      <c r="C124" s="24" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$C:$C,MATCH($A124,Requerimientos!$A:$A,0)),"")</f>
+        <v>Taxista</v>
+      </c>
+      <c r="D124" s="24" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A124,Requerimientos!$A:$A,0)),"")</f>
+        <v>M1 Autenticación</v>
+      </c>
+      <c r="E124" s="24" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A124,Requerimientos!$A:$A,0)),"")</f>
+        <v>Alta</v>
+      </c>
+      <c r="F124" s="24" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$H:$H,MATCH($A124,Requerimientos!$A:$A,0)),"")</f>
+        <v>Web</v>
+      </c>
+      <c r="G124" s="24" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$I:$I,MATCH($A124,Requerimientos!$A:$A,0)),"")</f>
+        <v>App web</v>
+      </c>
+      <c r="H124" s="24" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$J:$J,MATCH($A124,Requerimientos!$A:$A,0)),"")</f>
+        <v>Pendiente</v>
+      </c>
+    </row>
+    <row r="125" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A125" s="26" t="s">
+        <v>295</v>
+      </c>
+      <c r="B125" s="3" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A125,Requerimientos!$A:$A,0)),"")</f>
+        <v>La app móvil no accede directamente a la base de datos del sistema de taxistas</v>
+      </c>
+      <c r="C125" s="24" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$C:$C,MATCH($A125,Requerimientos!$A:$A,0)),"")</f>
+        <v>Transversal</v>
+      </c>
+      <c r="D125" s="24" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A125,Requerimientos!$A:$A,0)),"")</f>
+        <v>M10 Calidad</v>
+      </c>
+      <c r="E125" s="24" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A125,Requerimientos!$A:$A,0)),"")</f>
+        <v>Alta</v>
+      </c>
+      <c r="F125" s="24" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$H:$H,MATCH($A125,Requerimientos!$A:$A,0)),"")</f>
+        <v>L7  ·  Web</v>
+      </c>
+      <c r="G125" s="24" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$I:$I,MATCH($A125,Requerimientos!$A:$A,0)),"")</f>
+        <v>App web</v>
+      </c>
+      <c r="H125" s="24" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$J:$J,MATCH($A125,Requerimientos!$A:$A,0)),"")</f>
+        <v>Pendiente</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="A112:H112"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A61:H61"/>
     <mergeCell ref="A6:H6"/>
     <mergeCell ref="A3:H3"/>
-    <mergeCell ref="A53:H53"/>
-    <mergeCell ref="A38:H38"/>
+    <mergeCell ref="A122:H122"/>
+    <mergeCell ref="A69:H69"/>
+    <mergeCell ref="A109:H109"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A99:H99"/>
+    <mergeCell ref="A44:H44"/>
   </mergeCells>
-  <conditionalFormatting sqref="H6:H115">
+  <conditionalFormatting sqref="H6:H125">
     <cfRule type="cellIs" dxfId="5" priority="1" operator="equal">
       <formula>"Hecho"</formula>
     </cfRule>
@@ -10360,7 +10855,7 @@
       <formula>"Pendiente"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E6:E115">
+  <conditionalFormatting sqref="E6:E125">
     <cfRule type="cellIs" dxfId="1" priority="5" operator="equal">
       <formula>"Alta"</formula>
     </cfRule>

--- a/docs/requerimientos.xlsx
+++ b/docs/requerimientos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USUARIO\Desktop\roomtrip\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67C40F07-F2BB-4AD3-9B4C-0E54D1133DC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49937ABE-C5FD-4683-A2F0-2E13C30F46A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="390" yWindow="195" windowWidth="21600" windowHeight="15405" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="876" uniqueCount="316">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="879" uniqueCount="317">
   <si>
     <t>RoomTrip · Cómo usar este libro</t>
   </si>
@@ -582,21 +582,24 @@
     <t>La ubicación se selecciona en un mapa y se listan los lugares históricos cercanos asociados</t>
   </si>
   <si>
+    <t>L3  ·  L4  ·  L6  ·  L7</t>
+  </si>
+  <si>
+    <t>Los lugares históricos cercanos aún no están en el mockup.</t>
+  </si>
+  <si>
+    <t>RF-AH-05</t>
+  </si>
+  <si>
+    <t>Ver el estado del taxista asignado en camino a recoger y llegó al destino</t>
+  </si>
+  <si>
+    <t>El hotel ve el estado actualizado del servicio de taxi de sus huéspedes</t>
+  </si>
+  <si>
     <t>L3  ·  L6  ·  L7</t>
   </si>
   <si>
-    <t>Los lugares históricos cercanos aún no están en el mockup.</t>
-  </si>
-  <si>
-    <t>RF-AH-05</t>
-  </si>
-  <si>
-    <t>Ver el estado del taxista asignado en camino a recoger y llegó al destino</t>
-  </si>
-  <si>
-    <t>El hotel ve el estado actualizado del servicio de taxi de sus huéspedes</t>
-  </si>
-  <si>
     <t>RF-TX-02</t>
   </si>
   <si>
@@ -975,10 +978,10 @@
     <t>Lab 3    ·    15/09/2026    ·    Implementación de mockups: navigation, menús y elementos UI    ·    36 requerimientos, 1 cierra aquí</t>
   </si>
   <si>
-    <t>Lab 4    ·    29/09/2026    ·    RecyclerView: listado de elementos con data estática    ·    15 requerimientos, 0 cierran aquí</t>
-  </si>
-  <si>
-    <t>Lab 5    ·    20/10/2026    ·    Storage local y notificaciones    ·    6 requerimientos, 0 cierran aquí</t>
+    <t>Lab 4    ·    29/09/2026    ·    RecyclerView: listado de elementos con data estática    ·    17 requerimientos, 0 cierran aquí</t>
+  </si>
+  <si>
+    <t>Lab 5    ·    20/10/2026    ·    Storage local y notificaciones    ·    7 requerimientos, 0 cierran aquí</t>
   </si>
   <si>
     <t>Lab 6    ·    03/11/2026    ·    Firebase Authentication y Firebase Database    ·    38 requerimientos, 33 cierran aquí</t>
@@ -1629,7 +1632,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-B1AD-40AB-A069-E5D523AED9EF}"/>
+              <c16:uniqueId val="{00000000-75F8-4C25-962A-C8A1C179A207}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2914,7 +2917,7 @@
       </c>
       <c r="D22" s="13">
         <f>COUNTIF(Requerimientos!$H$6:$H$52,"*L4*")</f>
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E22" s="13">
         <f>COUNTIF(Requerimientos!$I$6:$I$52,$A22)</f>
@@ -2950,7 +2953,7 @@
       </c>
       <c r="D23" s="10">
         <f>COUNTIF(Requerimientos!$H$6:$H$52,"*L5*")</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E23" s="10">
         <f>COUNTIF(Requerimientos!$I$6:$I$52,$A23)</f>
@@ -3949,7 +3952,7 @@
         <v>87</v>
       </c>
       <c r="H17" s="25" t="s">
-        <v>167</v>
+        <v>130</v>
       </c>
       <c r="I17" s="24" t="s">
         <v>107</v>
@@ -4064,7 +4067,7 @@
         <v>87</v>
       </c>
       <c r="H20" s="25" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="I20" s="24" t="s">
         <v>108</v>
@@ -4080,7 +4083,7 @@
     </row>
     <row r="21" spans="1:13" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="22" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B21" s="23" t="s">
         <v>113</v>
@@ -4092,10 +4095,10 @@
         <v>127</v>
       </c>
       <c r="E21" s="23" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F21" s="23" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="G21" s="24" t="s">
         <v>86</v>
@@ -4117,7 +4120,7 @@
     </row>
     <row r="22" spans="1:13" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="22" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B22" s="23" t="s">
         <v>120</v>
@@ -4129,10 +4132,10 @@
         <v>127</v>
       </c>
       <c r="E22" s="23" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F22" s="23" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="G22" s="24" t="s">
         <v>86</v>
@@ -4154,7 +4157,7 @@
     </row>
     <row r="23" spans="1:13" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="22" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B23" s="23" t="s">
         <v>120</v>
@@ -4166,10 +4169,10 @@
         <v>127</v>
       </c>
       <c r="E23" s="23" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F23" s="23" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="G23" s="24" t="s">
         <v>86</v>
@@ -4188,12 +4191,12 @@
       </c>
       <c r="L23" s="23"/>
       <c r="M23" s="23" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="24" spans="1:13" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="22" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B24" s="23" t="s">
         <v>120</v>
@@ -4205,10 +4208,10 @@
         <v>127</v>
       </c>
       <c r="E24" s="23" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F24" s="23" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="G24" s="24" t="s">
         <v>86</v>
@@ -4230,7 +4233,7 @@
     </row>
     <row r="25" spans="1:13" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="22" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B25" s="23" t="s">
         <v>120</v>
@@ -4242,16 +4245,16 @@
         <v>127</v>
       </c>
       <c r="E25" s="23" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F25" s="23" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="G25" s="24" t="s">
         <v>86</v>
       </c>
       <c r="H25" s="25" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="I25" s="24" t="s">
         <v>108</v>
@@ -4264,12 +4267,12 @@
       </c>
       <c r="L25" s="23"/>
       <c r="M25" s="23" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="26" spans="1:13" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="22" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B26" s="23" t="s">
         <v>120</v>
@@ -4281,16 +4284,16 @@
         <v>127</v>
       </c>
       <c r="E26" s="23" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F26" s="23" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="G26" s="24" t="s">
         <v>86</v>
       </c>
       <c r="H26" s="25" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="I26" s="24" t="s">
         <v>108</v>
@@ -4303,12 +4306,12 @@
       </c>
       <c r="L26" s="23"/>
       <c r="M26" s="23" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="27" spans="1:13" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="22" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B27" s="23" t="s">
         <v>113</v>
@@ -4320,10 +4323,10 @@
         <v>127</v>
       </c>
       <c r="E27" s="23" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F27" s="23" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G27" s="24" t="s">
         <v>86</v>
@@ -4345,7 +4348,7 @@
     </row>
     <row r="28" spans="1:13" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="22" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B28" s="23" t="s">
         <v>113</v>
@@ -4357,10 +4360,10 @@
         <v>127</v>
       </c>
       <c r="E28" s="23" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F28" s="23" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="G28" s="24" t="s">
         <v>86</v>
@@ -4379,12 +4382,12 @@
       </c>
       <c r="L28" s="23"/>
       <c r="M28" s="23" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="29" spans="1:13" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="22" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B29" s="23" t="s">
         <v>115</v>
@@ -4396,10 +4399,10 @@
         <v>127</v>
       </c>
       <c r="E29" s="23" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F29" s="23" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="G29" s="24" t="s">
         <v>86</v>
@@ -4421,7 +4424,7 @@
     </row>
     <row r="30" spans="1:13" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="22" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B30" s="23" t="s">
         <v>116</v>
@@ -4433,10 +4436,10 @@
         <v>127</v>
       </c>
       <c r="E30" s="23" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F30" s="23" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="G30" s="24" t="s">
         <v>86</v>
@@ -4458,7 +4461,7 @@
     </row>
     <row r="31" spans="1:13" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="22" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B31" s="23" t="s">
         <v>118</v>
@@ -4470,10 +4473,10 @@
         <v>127</v>
       </c>
       <c r="E31" s="23" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F31" s="23" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="G31" s="24" t="s">
         <v>86</v>
@@ -4495,7 +4498,7 @@
     </row>
     <row r="32" spans="1:13" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="22" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B32" s="23" t="s">
         <v>117</v>
@@ -4507,10 +4510,10 @@
         <v>127</v>
       </c>
       <c r="E32" s="23" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F32" s="23" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="G32" s="24" t="s">
         <v>86</v>
@@ -4529,12 +4532,12 @@
       </c>
       <c r="L32" s="23"/>
       <c r="M32" s="23" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="33" spans="1:13" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="22" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B33" s="23" t="s">
         <v>119</v>
@@ -4546,10 +4549,10 @@
         <v>127</v>
       </c>
       <c r="E33" s="23" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="F33" s="23" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="G33" s="24" t="s">
         <v>86</v>
@@ -4568,12 +4571,12 @@
       </c>
       <c r="L33" s="23"/>
       <c r="M33" s="23" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="34" spans="1:13" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="22" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B34" s="23" t="s">
         <v>116</v>
@@ -4585,10 +4588,10 @@
         <v>127</v>
       </c>
       <c r="E34" s="23" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F34" s="23" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="G34" s="24" t="s">
         <v>87</v>
@@ -4610,7 +4613,7 @@
     </row>
     <row r="35" spans="1:13" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="22" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B35" s="23" t="s">
         <v>115</v>
@@ -4622,10 +4625,10 @@
         <v>127</v>
       </c>
       <c r="E35" s="23" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F35" s="23" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="G35" s="24" t="s">
         <v>87</v>
@@ -4644,12 +4647,12 @@
       </c>
       <c r="L35" s="23"/>
       <c r="M35" s="23" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="36" spans="1:13" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="22" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B36" s="23" t="s">
         <v>120</v>
@@ -4661,16 +4664,16 @@
         <v>127</v>
       </c>
       <c r="E36" s="23" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="F36" s="23" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="G36" s="24" t="s">
         <v>86</v>
       </c>
       <c r="H36" s="25" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="I36" s="24" t="s">
         <v>108</v>
@@ -4686,7 +4689,7 @@
     </row>
     <row r="37" spans="1:13" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="22" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B37" s="23" t="s">
         <v>120</v>
@@ -4698,16 +4701,16 @@
         <v>127</v>
       </c>
       <c r="E37" s="23" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="F37" s="23" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="G37" s="24" t="s">
         <v>86</v>
       </c>
       <c r="H37" s="25" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="I37" s="24" t="s">
         <v>108</v>
@@ -4720,12 +4723,12 @@
       </c>
       <c r="L37" s="23"/>
       <c r="M37" s="23" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="38" spans="1:13" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="22" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B38" s="23" t="s">
         <v>120</v>
@@ -4737,16 +4740,16 @@
         <v>127</v>
       </c>
       <c r="E38" s="23" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F38" s="23" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="G38" s="24" t="s">
         <v>86</v>
       </c>
       <c r="H38" s="25" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="I38" s="24" t="s">
         <v>108</v>
@@ -4762,7 +4765,7 @@
     </row>
     <row r="39" spans="1:13" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="22" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B39" s="23" t="s">
         <v>120</v>
@@ -4774,16 +4777,16 @@
         <v>127</v>
       </c>
       <c r="E39" s="23" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F39" s="23" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="G39" s="24" t="s">
         <v>87</v>
       </c>
       <c r="H39" s="25" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="I39" s="24" t="s">
         <v>108</v>
@@ -4799,7 +4802,7 @@
     </row>
     <row r="40" spans="1:13" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="22" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B40" s="23" t="s">
         <v>122</v>
@@ -4808,19 +4811,19 @@
         <v>96</v>
       </c>
       <c r="D40" s="24" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E40" s="23" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F40" s="23" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="G40" s="24" t="s">
         <v>86</v>
       </c>
       <c r="H40" s="25" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="I40" s="24" t="s">
         <v>104</v>
@@ -4829,14 +4832,14 @@
         <v>88</v>
       </c>
       <c r="K40" s="24" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="L40" s="23"/>
       <c r="M40" s="23"/>
     </row>
     <row r="41" spans="1:13" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="22" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B41" s="23" t="s">
         <v>116</v>
@@ -4848,10 +4851,10 @@
         <v>127</v>
       </c>
       <c r="E41" s="23" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F41" s="23" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="G41" s="24" t="s">
         <v>86</v>
@@ -4870,12 +4873,12 @@
       </c>
       <c r="L41" s="23"/>
       <c r="M41" s="23" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="42" spans="1:13" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="22" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B42" s="23" t="s">
         <v>116</v>
@@ -4887,10 +4890,10 @@
         <v>127</v>
       </c>
       <c r="E42" s="23" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="F42" s="23" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="G42" s="24" t="s">
         <v>86</v>
@@ -4909,12 +4912,12 @@
       </c>
       <c r="L42" s="23"/>
       <c r="M42" s="23" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="43" spans="1:13" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="22" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B43" s="23" t="s">
         <v>113</v>
@@ -4926,16 +4929,16 @@
         <v>127</v>
       </c>
       <c r="E43" s="23" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F43" s="23" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="G43" s="24" t="s">
         <v>86</v>
       </c>
       <c r="H43" s="25" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="I43" s="24" t="s">
         <v>107</v>
@@ -4951,7 +4954,7 @@
     </row>
     <row r="44" spans="1:13" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="22" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B44" s="23" t="s">
         <v>119</v>
@@ -4963,10 +4966,10 @@
         <v>127</v>
       </c>
       <c r="E44" s="23" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="F44" s="23" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="G44" s="24" t="s">
         <v>86</v>
@@ -4988,7 +4991,7 @@
     </row>
     <row r="45" spans="1:13" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="22" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B45" s="23" t="s">
         <v>122</v>
@@ -4997,19 +5000,19 @@
         <v>96</v>
       </c>
       <c r="D45" s="24" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E45" s="23" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F45" s="23" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="G45" s="24" t="s">
         <v>86</v>
       </c>
       <c r="H45" s="25" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="I45" s="24" t="s">
         <v>107</v>
@@ -5018,14 +5021,14 @@
         <v>88</v>
       </c>
       <c r="K45" s="24" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="L45" s="23"/>
       <c r="M45" s="23"/>
     </row>
     <row r="46" spans="1:13" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="22" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B46" s="23" t="s">
         <v>122</v>
@@ -5034,19 +5037,19 @@
         <v>96</v>
       </c>
       <c r="D46" s="24" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E46" s="23" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="F46" s="23" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="G46" s="24" t="s">
         <v>86</v>
       </c>
       <c r="H46" s="25" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="I46" s="24" t="s">
         <v>107</v>
@@ -5055,14 +5058,14 @@
         <v>88</v>
       </c>
       <c r="K46" s="24" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="L46" s="23"/>
       <c r="M46" s="23"/>
     </row>
     <row r="47" spans="1:13" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="22" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B47" s="23" t="s">
         <v>122</v>
@@ -5071,19 +5074,19 @@
         <v>96</v>
       </c>
       <c r="D47" s="24" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E47" s="23" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F47" s="23" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="G47" s="24" t="s">
         <v>86</v>
       </c>
       <c r="H47" s="25" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="I47" s="24" t="s">
         <v>107</v>
@@ -5092,14 +5095,14 @@
         <v>88</v>
       </c>
       <c r="K47" s="24" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="L47" s="23"/>
       <c r="M47" s="23"/>
     </row>
     <row r="48" spans="1:13" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="22" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B48" s="23" t="s">
         <v>122</v>
@@ -5108,19 +5111,19 @@
         <v>96</v>
       </c>
       <c r="D48" s="24" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E48" s="23" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F48" s="23" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="G48" s="24" t="s">
         <v>86</v>
       </c>
       <c r="H48" s="25" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="I48" s="24" t="s">
         <v>107</v>
@@ -5129,14 +5132,14 @@
         <v>88</v>
       </c>
       <c r="K48" s="24" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="L48" s="23"/>
       <c r="M48" s="23"/>
     </row>
     <row r="49" spans="1:13" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="22" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B49" s="23" t="s">
         <v>122</v>
@@ -5145,19 +5148,19 @@
         <v>96</v>
       </c>
       <c r="D49" s="24" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E49" s="23" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="F49" s="23" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="G49" s="24" t="s">
         <v>87</v>
       </c>
       <c r="H49" s="25" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="I49" s="24" t="s">
         <v>107</v>
@@ -5166,14 +5169,14 @@
         <v>88</v>
       </c>
       <c r="K49" s="24" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="L49" s="23"/>
       <c r="M49" s="23"/>
     </row>
     <row r="50" spans="1:13" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="22" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B50" s="23" t="s">
         <v>122</v>
@@ -5182,19 +5185,19 @@
         <v>96</v>
       </c>
       <c r="D50" s="24" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E50" s="23" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="F50" s="23" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="G50" s="24" t="s">
         <v>86</v>
       </c>
       <c r="H50" s="25" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="I50" s="24" t="s">
         <v>108</v>
@@ -5203,14 +5206,14 @@
         <v>88</v>
       </c>
       <c r="K50" s="24" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="L50" s="23"/>
       <c r="M50" s="23"/>
     </row>
     <row r="51" spans="1:13" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="22" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B51" s="23" t="s">
         <v>122</v>
@@ -5219,19 +5222,19 @@
         <v>96</v>
       </c>
       <c r="D51" s="24" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E51" s="23" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="F51" s="23" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="G51" s="24" t="s">
         <v>86</v>
       </c>
       <c r="H51" s="25" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="I51" s="24" t="s">
         <v>108</v>
@@ -5240,16 +5243,16 @@
         <v>88</v>
       </c>
       <c r="K51" s="24" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="L51" s="23"/>
       <c r="M51" s="23" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="52" spans="1:13" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="22" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B52" s="23" t="s">
         <v>122</v>
@@ -5258,19 +5261,19 @@
         <v>96</v>
       </c>
       <c r="D52" s="24" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E52" s="23" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="F52" s="23" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="G52" s="24" t="s">
         <v>86</v>
       </c>
       <c r="H52" s="25" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="I52" s="24" t="s">
         <v>109</v>
@@ -5279,7 +5282,7 @@
         <v>88</v>
       </c>
       <c r="K52" s="24" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="L52" s="23"/>
       <c r="M52" s="23"/>
@@ -5360,7 +5363,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="27" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B1" s="28"/>
       <c r="C1" s="28"/>
@@ -5372,7 +5375,7 @@
     </row>
     <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="33" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B2" s="34"/>
       <c r="C2" s="34"/>
@@ -5384,7 +5387,7 @@
     </row>
     <row r="3" spans="1:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="36" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B3" s="32"/>
       <c r="C3" s="32"/>
@@ -5422,7 +5425,7 @@
     </row>
     <row r="6" spans="1:8" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="29" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B6" s="30"/>
       <c r="C6" s="30"/>
@@ -5599,7 +5602,7 @@
     </row>
     <row r="13" spans="1:8" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="29" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B13" s="30"/>
       <c r="C13" s="30"/>
@@ -5941,7 +5944,7 @@
     </row>
     <row r="25" spans="1:8" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="29" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B25" s="30"/>
       <c r="C25" s="30"/>
@@ -5953,7 +5956,7 @@
     </row>
     <row r="26" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A26" s="26" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B26" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A26,Requerimientos!$A:$A,0)),"")</f>
@@ -5986,7 +5989,7 @@
     </row>
     <row r="27" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A27" s="26" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B27" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A27,Requerimientos!$A:$A,0)),"")</f>
@@ -6019,7 +6022,7 @@
     </row>
     <row r="28" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A28" s="26" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B28" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A28,Requerimientos!$A:$A,0)),"")</f>
@@ -6052,7 +6055,7 @@
     </row>
     <row r="29" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A29" s="26" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B29" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A29,Requerimientos!$A:$A,0)),"")</f>
@@ -6085,7 +6088,7 @@
     </row>
     <row r="30" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A30" s="26" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B30" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A30,Requerimientos!$A:$A,0)),"")</f>
@@ -6118,7 +6121,7 @@
     </row>
     <row r="31" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A31" s="26" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B31" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A31,Requerimientos!$A:$A,0)),"")</f>
@@ -6151,7 +6154,7 @@
     </row>
     <row r="32" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A32" s="26" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B32" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A32,Requerimientos!$A:$A,0)),"")</f>
@@ -6184,7 +6187,7 @@
     </row>
     <row r="34" spans="1:8" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="29" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B34" s="30"/>
       <c r="C34" s="30"/>
@@ -6196,7 +6199,7 @@
     </row>
     <row r="35" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A35" s="26" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B35" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A35,Requerimientos!$A:$A,0)),"")</f>
@@ -6229,7 +6232,7 @@
     </row>
     <row r="36" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A36" s="26" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B36" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A36,Requerimientos!$A:$A,0)),"")</f>
@@ -6262,7 +6265,7 @@
     </row>
     <row r="37" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A37" s="26" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B37" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A37,Requerimientos!$A:$A,0)),"")</f>
@@ -6295,7 +6298,7 @@
     </row>
     <row r="38" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A38" s="26" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B38" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A38,Requerimientos!$A:$A,0)),"")</f>
@@ -6328,7 +6331,7 @@
     </row>
     <row r="39" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A39" s="26" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B39" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A39,Requerimientos!$A:$A,0)),"")</f>
@@ -6361,7 +6364,7 @@
     </row>
     <row r="40" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A40" s="26" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B40" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A40,Requerimientos!$A:$A,0)),"")</f>
@@ -6394,7 +6397,7 @@
     </row>
     <row r="41" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A41" s="26" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B41" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A41,Requerimientos!$A:$A,0)),"")</f>
@@ -6427,7 +6430,7 @@
     </row>
     <row r="42" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A42" s="26" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B42" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A42,Requerimientos!$A:$A,0)),"")</f>
@@ -6460,7 +6463,7 @@
     </row>
     <row r="43" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A43" s="26" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B43" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A43,Requerimientos!$A:$A,0)),"")</f>
@@ -6493,7 +6496,7 @@
     </row>
     <row r="44" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A44" s="26" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B44" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A44,Requerimientos!$A:$A,0)),"")</f>
@@ -6526,7 +6529,7 @@
     </row>
     <row r="45" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A45" s="26" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B45" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A45,Requerimientos!$A:$A,0)),"")</f>
@@ -6559,7 +6562,7 @@
     </row>
     <row r="46" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A46" s="26" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B46" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A46,Requerimientos!$A:$A,0)),"")</f>
@@ -6592,7 +6595,7 @@
     </row>
     <row r="48" spans="1:8" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="29" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B48" s="30"/>
       <c r="C48" s="30"/>
@@ -6604,7 +6607,7 @@
     </row>
     <row r="49" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A49" s="26" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B49" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A49,Requerimientos!$A:$A,0)),"")</f>
@@ -6637,7 +6640,7 @@
     </row>
     <row r="50" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A50" s="26" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B50" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A50,Requerimientos!$A:$A,0)),"")</f>
@@ -6670,7 +6673,7 @@
     </row>
     <row r="51" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A51" s="26" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B51" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A51,Requerimientos!$A:$A,0)),"")</f>
@@ -6703,7 +6706,7 @@
     </row>
     <row r="52" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A52" s="26" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B52" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A52,Requerimientos!$A:$A,0)),"")</f>
@@ -6736,7 +6739,7 @@
     </row>
     <row r="53" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A53" s="26" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B53" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A53,Requerimientos!$A:$A,0)),"")</f>
@@ -6769,7 +6772,7 @@
     </row>
     <row r="54" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A54" s="26" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B54" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A54,Requerimientos!$A:$A,0)),"")</f>
@@ -6802,7 +6805,7 @@
     </row>
     <row r="55" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A55" s="26" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B55" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A55,Requerimientos!$A:$A,0)),"")</f>
@@ -6835,7 +6838,7 @@
     </row>
     <row r="56" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A56" s="26" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B56" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A56,Requerimientos!$A:$A,0)),"")</f>
@@ -6868,7 +6871,7 @@
     </row>
     <row r="57" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A57" s="26" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B57" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A57,Requerimientos!$A:$A,0)),"")</f>
@@ -6901,7 +6904,7 @@
     </row>
     <row r="58" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A58" s="26" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B58" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A58,Requerimientos!$A:$A,0)),"")</f>
@@ -6934,7 +6937,7 @@
     </row>
     <row r="59" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A59" s="26" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B59" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A59,Requerimientos!$A:$A,0)),"")</f>
@@ -6967,7 +6970,7 @@
     </row>
     <row r="60" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A60" s="26" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B60" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A60,Requerimientos!$A:$A,0)),"")</f>
@@ -7000,7 +7003,7 @@
     </row>
     <row r="61" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A61" s="26" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B61" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A61,Requerimientos!$A:$A,0)),"")</f>
@@ -7085,7 +7088,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H125"/>
+  <dimension ref="A1:H128"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" outlineLevelRow="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
@@ -7100,7 +7103,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="27" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B1" s="28"/>
       <c r="C1" s="28"/>
@@ -7112,7 +7115,7 @@
     </row>
     <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="33" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B2" s="34"/>
       <c r="C2" s="34"/>
@@ -7124,7 +7127,7 @@
     </row>
     <row r="3" spans="1:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="36" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B3" s="32"/>
       <c r="C3" s="32"/>
@@ -7162,7 +7165,7 @@
     </row>
     <row r="6" spans="1:8" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="29" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B6" s="30"/>
       <c r="C6" s="30"/>
@@ -7524,7 +7527,7 @@
       </c>
       <c r="F17" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$H:$H,MATCH($A17,Requerimientos!$A:$A,0)),"")</f>
-        <v>L3  ·  L6</v>
+        <v>L3  ·  L4  ·  L6</v>
       </c>
       <c r="G17" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$I:$I,MATCH($A17,Requerimientos!$A:$A,0)),"")</f>
@@ -7590,7 +7593,7 @@
       </c>
       <c r="F19" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$H:$H,MATCH($A19,Requerimientos!$A:$A,0)),"")</f>
-        <v>L3  ·  L6  ·  L7</v>
+        <v>L3  ·  L4  ·  L6  ·  L7</v>
       </c>
       <c r="G19" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$I:$I,MATCH($A19,Requerimientos!$A:$A,0)),"")</f>
@@ -7636,7 +7639,7 @@
     </row>
     <row r="21" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A21" s="26" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B21" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A21,Requerimientos!$A:$A,0)),"")</f>
@@ -7669,7 +7672,7 @@
     </row>
     <row r="22" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A22" s="26" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B22" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A22,Requerimientos!$A:$A,0)),"")</f>
@@ -7702,7 +7705,7 @@
     </row>
     <row r="23" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A23" s="26" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B23" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A23,Requerimientos!$A:$A,0)),"")</f>
@@ -7735,7 +7738,7 @@
     </row>
     <row r="24" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A24" s="26" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B24" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A24,Requerimientos!$A:$A,0)),"")</f>
@@ -7768,7 +7771,7 @@
     </row>
     <row r="25" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A25" s="26" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B25" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A25,Requerimientos!$A:$A,0)),"")</f>
@@ -7801,7 +7804,7 @@
     </row>
     <row r="26" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A26" s="26" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B26" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A26,Requerimientos!$A:$A,0)),"")</f>
@@ -7834,7 +7837,7 @@
     </row>
     <row r="27" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A27" s="26" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B27" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A27,Requerimientos!$A:$A,0)),"")</f>
@@ -7867,7 +7870,7 @@
     </row>
     <row r="28" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A28" s="26" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B28" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A28,Requerimientos!$A:$A,0)),"")</f>
@@ -7900,7 +7903,7 @@
     </row>
     <row r="29" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A29" s="26" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B29" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A29,Requerimientos!$A:$A,0)),"")</f>
@@ -7933,7 +7936,7 @@
     </row>
     <row r="30" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A30" s="26" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B30" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A30,Requerimientos!$A:$A,0)),"")</f>
@@ -7966,7 +7969,7 @@
     </row>
     <row r="31" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A31" s="26" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B31" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A31,Requerimientos!$A:$A,0)),"")</f>
@@ -7999,7 +8002,7 @@
     </row>
     <row r="32" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A32" s="26" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B32" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A32,Requerimientos!$A:$A,0)),"")</f>
@@ -8032,7 +8035,7 @@
     </row>
     <row r="33" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A33" s="26" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B33" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A33,Requerimientos!$A:$A,0)),"")</f>
@@ -8065,7 +8068,7 @@
     </row>
     <row r="34" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A34" s="26" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B34" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A34,Requerimientos!$A:$A,0)),"")</f>
@@ -8098,7 +8101,7 @@
     </row>
     <row r="35" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A35" s="26" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B35" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A35,Requerimientos!$A:$A,0)),"")</f>
@@ -8131,7 +8134,7 @@
     </row>
     <row r="36" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A36" s="26" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B36" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A36,Requerimientos!$A:$A,0)),"")</f>
@@ -8164,7 +8167,7 @@
     </row>
     <row r="37" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A37" s="26" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B37" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A37,Requerimientos!$A:$A,0)),"")</f>
@@ -8197,7 +8200,7 @@
     </row>
     <row r="38" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A38" s="26" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B38" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A38,Requerimientos!$A:$A,0)),"")</f>
@@ -8230,7 +8233,7 @@
     </row>
     <row r="39" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A39" s="26" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B39" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A39,Requerimientos!$A:$A,0)),"")</f>
@@ -8263,7 +8266,7 @@
     </row>
     <row r="40" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A40" s="26" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B40" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A40,Requerimientos!$A:$A,0)),"")</f>
@@ -8296,7 +8299,7 @@
     </row>
     <row r="41" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A41" s="26" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B41" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A41,Requerimientos!$A:$A,0)),"")</f>
@@ -8316,7 +8319,7 @@
       </c>
       <c r="F41" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$H:$H,MATCH($A41,Requerimientos!$A:$A,0)),"")</f>
-        <v>L3  ·  L6</v>
+        <v>L3  ·  L5  ·  L6</v>
       </c>
       <c r="G41" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$I:$I,MATCH($A41,Requerimientos!$A:$A,0)),"")</f>
@@ -8329,7 +8332,7 @@
     </row>
     <row r="42" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A42" s="26" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B42" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A42,Requerimientos!$A:$A,0)),"")</f>
@@ -8362,7 +8365,7 @@
     </row>
     <row r="44" spans="1:8" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="29" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B44" s="30"/>
       <c r="C44" s="30"/>
@@ -8638,11 +8641,11 @@
     </row>
     <row r="53" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A53" s="26" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="B53" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A53,Requerimientos!$A:$A,0)),"")</f>
-        <v>Reporte de ingresos por servicios adicionales ordenado de menor a mayor</v>
+        <v>Añadir cobros adicionales por daños con monto motivo y observación</v>
       </c>
       <c r="C53" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$C:$C,MATCH($A53,Requerimientos!$A:$A,0)),"")</f>
@@ -8650,7 +8653,7 @@
       </c>
       <c r="D53" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A53,Requerimientos!$A:$A,0)),"")</f>
-        <v>M9 Reportes y logs</v>
+        <v>M5 Pagos y cobros</v>
       </c>
       <c r="E53" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A53,Requerimientos!$A:$A,0)),"")</f>
@@ -8671,27 +8674,27 @@
     </row>
     <row r="54" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A54" s="26" t="s">
-        <v>188</v>
+        <v>172</v>
       </c>
       <c r="B54" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A54,Requerimientos!$A:$A,0)),"")</f>
-        <v>Ver hoteles y pedidos disponibles</v>
+        <v>Reporte de ingresos por servicios adicionales ordenado de menor a mayor</v>
       </c>
       <c r="C54" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$C:$C,MATCH($A54,Requerimientos!$A:$A,0)),"")</f>
-        <v>Taxista</v>
+        <v>Administrador de hotel</v>
       </c>
       <c r="D54" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A54,Requerimientos!$A:$A,0)),"")</f>
-        <v>M8 Taxi</v>
+        <v>M9 Reportes y logs</v>
       </c>
       <c r="E54" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A54,Requerimientos!$A:$A,0)),"")</f>
-        <v>Alta</v>
+        <v>Media</v>
       </c>
       <c r="F54" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$H:$H,MATCH($A54,Requerimientos!$A:$A,0)),"")</f>
-        <v>L3  ·  L4  ·  L5  ·  L6</v>
+        <v>L3  ·  L4  ·  L6</v>
       </c>
       <c r="G54" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$I:$I,MATCH($A54,Requerimientos!$A:$A,0)),"")</f>
@@ -8704,15 +8707,15 @@
     </row>
     <row r="55" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A55" s="26" t="s">
-        <v>215</v>
+        <v>177</v>
       </c>
       <c r="B55" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A55,Requerimientos!$A:$A,0)),"")</f>
-        <v>Consultar hoteles habitaciones servicios disponibilidad y valoraciones</v>
+        <v>Registrar la ubicación del hotel y los lugares históricos cercanos</v>
       </c>
       <c r="C55" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$C:$C,MATCH($A55,Requerimientos!$A:$A,0)),"")</f>
-        <v>Cliente</v>
+        <v>Administrador de hotel</v>
       </c>
       <c r="D55" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A55,Requerimientos!$A:$A,0)),"")</f>
@@ -8724,11 +8727,11 @@
       </c>
       <c r="F55" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$H:$H,MATCH($A55,Requerimientos!$A:$A,0)),"")</f>
-        <v>L3  ·  L4  ·  L6</v>
+        <v>L3  ·  L4  ·  L6  ·  L7</v>
       </c>
       <c r="G55" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$I:$I,MATCH($A55,Requerimientos!$A:$A,0)),"")</f>
-        <v>Lab 6</v>
+        <v>Lab 7</v>
       </c>
       <c r="H55" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$J:$J,MATCH($A55,Requerimientos!$A:$A,0)),"")</f>
@@ -8737,19 +8740,19 @@
     </row>
     <row r="56" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A56" s="26" t="s">
-        <v>228</v>
+        <v>189</v>
       </c>
       <c r="B56" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A56,Requerimientos!$A:$A,0)),"")</f>
-        <v>Chat privado con el hotel entre la confirmación de la reserva y el fin del checkout</v>
+        <v>Ver hoteles y pedidos disponibles</v>
       </c>
       <c r="C56" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$C:$C,MATCH($A56,Requerimientos!$A:$A,0)),"")</f>
-        <v>Cliente</v>
+        <v>Taxista</v>
       </c>
       <c r="D56" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A56,Requerimientos!$A:$A,0)),"")</f>
-        <v>M7 Chat</v>
+        <v>M8 Taxi</v>
       </c>
       <c r="E56" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A56,Requerimientos!$A:$A,0)),"")</f>
@@ -8757,7 +8760,7 @@
       </c>
       <c r="F56" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$H:$H,MATCH($A56,Requerimientos!$A:$A,0)),"")</f>
-        <v>L3  ·  L4  ·  L6</v>
+        <v>L3  ·  L4  ·  L5  ·  L6</v>
       </c>
       <c r="G56" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$I:$I,MATCH($A56,Requerimientos!$A:$A,0)),"")</f>
@@ -8770,11 +8773,11 @@
     </row>
     <row r="57" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A57" s="26" t="s">
-        <v>232</v>
+        <v>216</v>
       </c>
       <c r="B57" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A57,Requerimientos!$A:$A,0)),"")</f>
-        <v>Ver el historial de sus reservas</v>
+        <v>Consultar hoteles habitaciones servicios disponibilidad y valoraciones</v>
       </c>
       <c r="C57" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$C:$C,MATCH($A57,Requerimientos!$A:$A,0)),"")</f>
@@ -8782,11 +8785,11 @@
       </c>
       <c r="D57" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A57,Requerimientos!$A:$A,0)),"")</f>
-        <v>M4 Reservas</v>
+        <v>M3 Catálogo</v>
       </c>
       <c r="E57" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A57,Requerimientos!$A:$A,0)),"")</f>
-        <v>Media</v>
+        <v>Alta</v>
       </c>
       <c r="F57" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$H:$H,MATCH($A57,Requerimientos!$A:$A,0)),"")</f>
@@ -8803,11 +8806,11 @@
     </row>
     <row r="58" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A58" s="26" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="B58" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A58,Requerimientos!$A:$A,0)),"")</f>
-        <v>Consultar los lugares históricos cercanos al hotel</v>
+        <v>Chat privado con el hotel entre la confirmación de la reserva y el fin del checkout</v>
       </c>
       <c r="C58" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$C:$C,MATCH($A58,Requerimientos!$A:$A,0)),"")</f>
@@ -8815,11 +8818,11 @@
       </c>
       <c r="D58" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A58,Requerimientos!$A:$A,0)),"")</f>
-        <v>M3 Catálogo</v>
+        <v>M7 Chat</v>
       </c>
       <c r="E58" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A58,Requerimientos!$A:$A,0)),"")</f>
-        <v>Media</v>
+        <v>Alta</v>
       </c>
       <c r="F58" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$H:$H,MATCH($A58,Requerimientos!$A:$A,0)),"")</f>
@@ -8836,23 +8839,23 @@
     </row>
     <row r="59" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A59" s="26" t="s">
-        <v>268</v>
+        <v>233</v>
       </c>
       <c r="B59" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A59,Requerimientos!$A:$A,0)),"")</f>
-        <v>Los mensajes de chat persisten con fecha y hora</v>
+        <v>Ver el historial de sus reservas</v>
       </c>
       <c r="C59" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$C:$C,MATCH($A59,Requerimientos!$A:$A,0)),"")</f>
-        <v>Transversal</v>
+        <v>Cliente</v>
       </c>
       <c r="D59" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A59,Requerimientos!$A:$A,0)),"")</f>
-        <v>M7 Chat</v>
+        <v>M4 Reservas</v>
       </c>
       <c r="E59" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A59,Requerimientos!$A:$A,0)),"")</f>
-        <v>Alta</v>
+        <v>Media</v>
       </c>
       <c r="F59" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$H:$H,MATCH($A59,Requerimientos!$A:$A,0)),"")</f>
@@ -8867,99 +8870,99 @@
         <v>Pendiente</v>
       </c>
     </row>
-    <row r="61" spans="1:8" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="29" t="s">
-        <v>312</v>
-      </c>
-      <c r="B61" s="30"/>
-      <c r="C61" s="30"/>
-      <c r="D61" s="30"/>
-      <c r="E61" s="30"/>
-      <c r="F61" s="30"/>
-      <c r="G61" s="30"/>
-      <c r="H61" s="30"/>
-    </row>
-    <row r="62" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="26" t="s">
-        <v>145</v>
-      </c>
-      <c r="B62" s="3" t="str">
-        <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A62,Requerimientos!$A:$A,0)),"")</f>
-        <v>Subir fotos del hotel con un mínimo de 4</v>
-      </c>
-      <c r="C62" s="24" t="str">
-        <f>IFERROR(INDEX(Requerimientos!$C:$C,MATCH($A62,Requerimientos!$A:$A,0)),"")</f>
-        <v>Administrador de hotel</v>
-      </c>
-      <c r="D62" s="24" t="str">
-        <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A62,Requerimientos!$A:$A,0)),"")</f>
+    <row r="60" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="26" t="s">
+        <v>236</v>
+      </c>
+      <c r="B60" s="3" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A60,Requerimientos!$A:$A,0)),"")</f>
+        <v>Consultar los lugares históricos cercanos al hotel</v>
+      </c>
+      <c r="C60" s="24" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$C:$C,MATCH($A60,Requerimientos!$A:$A,0)),"")</f>
+        <v>Cliente</v>
+      </c>
+      <c r="D60" s="24" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A60,Requerimientos!$A:$A,0)),"")</f>
         <v>M3 Catálogo</v>
       </c>
-      <c r="E62" s="24" t="str">
-        <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A62,Requerimientos!$A:$A,0)),"")</f>
-        <v>Alta</v>
-      </c>
-      <c r="F62" s="24" t="str">
-        <f>IFERROR(INDEX(Requerimientos!$H:$H,MATCH($A62,Requerimientos!$A:$A,0)),"")</f>
-        <v>L3  ·  L4  ·  L5  ·  L6</v>
-      </c>
-      <c r="G62" s="24" t="str">
-        <f>IFERROR(INDEX(Requerimientos!$I:$I,MATCH($A62,Requerimientos!$A:$A,0)),"")</f>
-        <v>Lab 6</v>
-      </c>
-      <c r="H62" s="24" t="str">
-        <f>IFERROR(INDEX(Requerimientos!$J:$J,MATCH($A62,Requerimientos!$A:$A,0)),"")</f>
-        <v>Pendiente</v>
-      </c>
-    </row>
-    <row r="63" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="26" t="s">
-        <v>157</v>
-      </c>
-      <c r="B63" s="3" t="str">
-        <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A63,Requerimientos!$A:$A,0)),"")</f>
-        <v>Recibir la alerta de checkout y procesar el cobro de la tarjeta registrada</v>
-      </c>
-      <c r="C63" s="24" t="str">
-        <f>IFERROR(INDEX(Requerimientos!$C:$C,MATCH($A63,Requerimientos!$A:$A,0)),"")</f>
-        <v>Administrador de hotel</v>
-      </c>
-      <c r="D63" s="24" t="str">
-        <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A63,Requerimientos!$A:$A,0)),"")</f>
-        <v>M5 Pagos y cobros</v>
-      </c>
-      <c r="E63" s="24" t="str">
-        <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A63,Requerimientos!$A:$A,0)),"")</f>
-        <v>Alta</v>
-      </c>
-      <c r="F63" s="24" t="str">
-        <f>IFERROR(INDEX(Requerimientos!$H:$H,MATCH($A63,Requerimientos!$A:$A,0)),"")</f>
-        <v>L3  ·  L5  ·  L6</v>
-      </c>
-      <c r="G63" s="24" t="str">
-        <f>IFERROR(INDEX(Requerimientos!$I:$I,MATCH($A63,Requerimientos!$A:$A,0)),"")</f>
-        <v>Lab 6</v>
-      </c>
-      <c r="H63" s="24" t="str">
-        <f>IFERROR(INDEX(Requerimientos!$J:$J,MATCH($A63,Requerimientos!$A:$A,0)),"")</f>
-        <v>Pendiente</v>
-      </c>
+      <c r="E60" s="24" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A60,Requerimientos!$A:$A,0)),"")</f>
+        <v>Media</v>
+      </c>
+      <c r="F60" s="24" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$H:$H,MATCH($A60,Requerimientos!$A:$A,0)),"")</f>
+        <v>L3  ·  L4  ·  L6</v>
+      </c>
+      <c r="G60" s="24" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$I:$I,MATCH($A60,Requerimientos!$A:$A,0)),"")</f>
+        <v>Lab 6</v>
+      </c>
+      <c r="H60" s="24" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$J:$J,MATCH($A60,Requerimientos!$A:$A,0)),"")</f>
+        <v>Pendiente</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="26" t="s">
+        <v>269</v>
+      </c>
+      <c r="B61" s="3" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A61,Requerimientos!$A:$A,0)),"")</f>
+        <v>Los mensajes de chat persisten con fecha y hora</v>
+      </c>
+      <c r="C61" s="24" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$C:$C,MATCH($A61,Requerimientos!$A:$A,0)),"")</f>
+        <v>Transversal</v>
+      </c>
+      <c r="D61" s="24" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A61,Requerimientos!$A:$A,0)),"")</f>
+        <v>M7 Chat</v>
+      </c>
+      <c r="E61" s="24" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A61,Requerimientos!$A:$A,0)),"")</f>
+        <v>Alta</v>
+      </c>
+      <c r="F61" s="24" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$H:$H,MATCH($A61,Requerimientos!$A:$A,0)),"")</f>
+        <v>L3  ·  L4  ·  L6</v>
+      </c>
+      <c r="G61" s="24" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$I:$I,MATCH($A61,Requerimientos!$A:$A,0)),"")</f>
+        <v>Lab 6</v>
+      </c>
+      <c r="H61" s="24" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$J:$J,MATCH($A61,Requerimientos!$A:$A,0)),"")</f>
+        <v>Pendiente</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A63" s="29" t="s">
+        <v>313</v>
+      </c>
+      <c r="B63" s="30"/>
+      <c r="C63" s="30"/>
+      <c r="D63" s="30"/>
+      <c r="E63" s="30"/>
+      <c r="F63" s="30"/>
+      <c r="G63" s="30"/>
+      <c r="H63" s="30"/>
     </row>
     <row r="64" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A64" s="26" t="s">
-        <v>185</v>
+        <v>145</v>
       </c>
       <c r="B64" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A64,Requerimientos!$A:$A,0)),"")</f>
-        <v>Acceder a la app móvil una vez habilitado</v>
+        <v>Subir fotos del hotel con un mínimo de 4</v>
       </c>
       <c r="C64" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$C:$C,MATCH($A64,Requerimientos!$A:$A,0)),"")</f>
-        <v>Taxista</v>
+        <v>Administrador de hotel</v>
       </c>
       <c r="D64" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A64,Requerimientos!$A:$A,0)),"")</f>
-        <v>M1 Autenticación</v>
+        <v>M3 Catálogo</v>
       </c>
       <c r="E64" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A64,Requerimientos!$A:$A,0)),"")</f>
@@ -8967,7 +8970,7 @@
       </c>
       <c r="F64" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$H:$H,MATCH($A64,Requerimientos!$A:$A,0)),"")</f>
-        <v>L3  ·  L5  ·  L6</v>
+        <v>L3  ·  L4  ·  L5  ·  L6</v>
       </c>
       <c r="G64" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$I:$I,MATCH($A64,Requerimientos!$A:$A,0)),"")</f>
@@ -8980,19 +8983,19 @@
     </row>
     <row r="65" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A65" s="26" t="s">
-        <v>188</v>
+        <v>157</v>
       </c>
       <c r="B65" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A65,Requerimientos!$A:$A,0)),"")</f>
-        <v>Ver hoteles y pedidos disponibles</v>
+        <v>Recibir la alerta de checkout y procesar el cobro de la tarjeta registrada</v>
       </c>
       <c r="C65" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$C:$C,MATCH($A65,Requerimientos!$A:$A,0)),"")</f>
-        <v>Taxista</v>
+        <v>Administrador de hotel</v>
       </c>
       <c r="D65" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A65,Requerimientos!$A:$A,0)),"")</f>
-        <v>M8 Taxi</v>
+        <v>M5 Pagos y cobros</v>
       </c>
       <c r="E65" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A65,Requerimientos!$A:$A,0)),"")</f>
@@ -9000,7 +9003,7 @@
       </c>
       <c r="F65" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$H:$H,MATCH($A65,Requerimientos!$A:$A,0)),"")</f>
-        <v>L3  ·  L4  ·  L5  ·  L6</v>
+        <v>L3  ·  L5  ·  L6</v>
       </c>
       <c r="G65" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$I:$I,MATCH($A65,Requerimientos!$A:$A,0)),"")</f>
@@ -9013,15 +9016,15 @@
     </row>
     <row r="66" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A66" s="26" t="s">
-        <v>211</v>
+        <v>186</v>
       </c>
       <c r="B66" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A66,Requerimientos!$A:$A,0)),"")</f>
-        <v>Autoregistrarse y quedar habilitado automáticamente</v>
+        <v>Acceder a la app móvil una vez habilitado</v>
       </c>
       <c r="C66" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$C:$C,MATCH($A66,Requerimientos!$A:$A,0)),"")</f>
-        <v>Cliente</v>
+        <v>Taxista</v>
       </c>
       <c r="D66" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A66,Requerimientos!$A:$A,0)),"")</f>
@@ -9046,19 +9049,19 @@
     </row>
     <row r="67" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A67" s="26" t="s">
-        <v>224</v>
+        <v>189</v>
       </c>
       <c r="B67" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A67,Requerimientos!$A:$A,0)),"")</f>
-        <v>Recibir notificación cuando se le hace el cobro</v>
+        <v>Ver hoteles y pedidos disponibles</v>
       </c>
       <c r="C67" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$C:$C,MATCH($A67,Requerimientos!$A:$A,0)),"")</f>
-        <v>Cliente</v>
+        <v>Taxista</v>
       </c>
       <c r="D67" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A67,Requerimientos!$A:$A,0)),"")</f>
-        <v>M5 Pagos y cobros</v>
+        <v>M8 Taxi</v>
       </c>
       <c r="E67" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A67,Requerimientos!$A:$A,0)),"")</f>
@@ -9066,7 +9069,7 @@
       </c>
       <c r="F67" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$H:$H,MATCH($A67,Requerimientos!$A:$A,0)),"")</f>
-        <v>L3  ·  L5  ·  L6</v>
+        <v>L3  ·  L4  ·  L5  ·  L6</v>
       </c>
       <c r="G67" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$I:$I,MATCH($A67,Requerimientos!$A:$A,0)),"")</f>
@@ -9077,33 +9080,87 @@
         <v>Pendiente</v>
       </c>
     </row>
-    <row r="69" spans="1:8" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="29" t="s">
-        <v>313</v>
-      </c>
-      <c r="B69" s="30"/>
-      <c r="C69" s="30"/>
-      <c r="D69" s="30"/>
-      <c r="E69" s="30"/>
-      <c r="F69" s="30"/>
-      <c r="G69" s="30"/>
-      <c r="H69" s="30"/>
+    <row r="68" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A68" s="26" t="s">
+        <v>212</v>
+      </c>
+      <c r="B68" s="3" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A68,Requerimientos!$A:$A,0)),"")</f>
+        <v>Autoregistrarse y quedar habilitado automáticamente</v>
+      </c>
+      <c r="C68" s="24" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$C:$C,MATCH($A68,Requerimientos!$A:$A,0)),"")</f>
+        <v>Cliente</v>
+      </c>
+      <c r="D68" s="24" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A68,Requerimientos!$A:$A,0)),"")</f>
+        <v>M1 Autenticación</v>
+      </c>
+      <c r="E68" s="24" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A68,Requerimientos!$A:$A,0)),"")</f>
+        <v>Alta</v>
+      </c>
+      <c r="F68" s="24" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$H:$H,MATCH($A68,Requerimientos!$A:$A,0)),"")</f>
+        <v>L3  ·  L5  ·  L6</v>
+      </c>
+      <c r="G68" s="24" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$I:$I,MATCH($A68,Requerimientos!$A:$A,0)),"")</f>
+        <v>Lab 6</v>
+      </c>
+      <c r="H68" s="24" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$J:$J,MATCH($A68,Requerimientos!$A:$A,0)),"")</f>
+        <v>Pendiente</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A69" s="26" t="s">
+        <v>225</v>
+      </c>
+      <c r="B69" s="3" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A69,Requerimientos!$A:$A,0)),"")</f>
+        <v>Recibir notificación cuando se le hace el cobro</v>
+      </c>
+      <c r="C69" s="24" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$C:$C,MATCH($A69,Requerimientos!$A:$A,0)),"")</f>
+        <v>Cliente</v>
+      </c>
+      <c r="D69" s="24" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A69,Requerimientos!$A:$A,0)),"")</f>
+        <v>M5 Pagos y cobros</v>
+      </c>
+      <c r="E69" s="24" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A69,Requerimientos!$A:$A,0)),"")</f>
+        <v>Alta</v>
+      </c>
+      <c r="F69" s="24" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$H:$H,MATCH($A69,Requerimientos!$A:$A,0)),"")</f>
+        <v>L3  ·  L5  ·  L6</v>
+      </c>
+      <c r="G69" s="24" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$I:$I,MATCH($A69,Requerimientos!$A:$A,0)),"")</f>
+        <v>Lab 6</v>
+      </c>
+      <c r="H69" s="24" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$J:$J,MATCH($A69,Requerimientos!$A:$A,0)),"")</f>
+        <v>Pendiente</v>
+      </c>
     </row>
     <row r="70" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A70" s="26" t="s">
-        <v>126</v>
+        <v>266</v>
       </c>
       <c r="B70" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A70,Requerimientos!$A:$A,0)),"")</f>
-        <v>Activar y desactivar administradores de hotel taxistas y clientes</v>
+        <v>Login único: tras autenticar se resuelve el rol y se navega al flujo correspondiente</v>
       </c>
       <c r="C70" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$C:$C,MATCH($A70,Requerimientos!$A:$A,0)),"")</f>
-        <v>Superadmin</v>
+        <v>Transversal</v>
       </c>
       <c r="D70" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A70,Requerimientos!$A:$A,0)),"")</f>
-        <v>M2 Gestión de usuarios</v>
+        <v>M1 Autenticación</v>
       </c>
       <c r="E70" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A70,Requerimientos!$A:$A,0)),"")</f>
@@ -9111,7 +9168,7 @@
       </c>
       <c r="F70" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$H:$H,MATCH($A70,Requerimientos!$A:$A,0)),"")</f>
-        <v>L3  ·  L4  ·  L6</v>
+        <v>L3  ·  L5  ·  L6</v>
       </c>
       <c r="G70" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$I:$I,MATCH($A70,Requerimientos!$A:$A,0)),"")</f>
@@ -9122,79 +9179,25 @@
         <v>Pendiente</v>
       </c>
     </row>
-    <row r="71" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="26" t="s">
-        <v>132</v>
-      </c>
-      <c r="B71" s="3" t="str">
-        <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A71,Requerimientos!$A:$A,0)),"")</f>
-        <v>Registrar hoteles y asignar un administrador a cada uno</v>
-      </c>
-      <c r="C71" s="24" t="str">
-        <f>IFERROR(INDEX(Requerimientos!$C:$C,MATCH($A71,Requerimientos!$A:$A,0)),"")</f>
-        <v>Superadmin</v>
-      </c>
-      <c r="D71" s="24" t="str">
-        <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A71,Requerimientos!$A:$A,0)),"")</f>
-        <v>M2 Gestión de usuarios</v>
-      </c>
-      <c r="E71" s="24" t="str">
-        <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A71,Requerimientos!$A:$A,0)),"")</f>
-        <v>Alta</v>
-      </c>
-      <c r="F71" s="24" t="str">
-        <f>IFERROR(INDEX(Requerimientos!$H:$H,MATCH($A71,Requerimientos!$A:$A,0)),"")</f>
-        <v>L3  ·  L4  ·  L6</v>
-      </c>
-      <c r="G71" s="24" t="str">
-        <f>IFERROR(INDEX(Requerimientos!$I:$I,MATCH($A71,Requerimientos!$A:$A,0)),"")</f>
-        <v>Lab 6</v>
-      </c>
-      <c r="H71" s="24" t="str">
-        <f>IFERROR(INDEX(Requerimientos!$J:$J,MATCH($A71,Requerimientos!$A:$A,0)),"")</f>
-        <v>Pendiente</v>
-      </c>
-    </row>
-    <row r="72" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="26" t="s">
-        <v>135</v>
-      </c>
-      <c r="B72" s="3" t="str">
-        <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A72,Requerimientos!$A:$A,0)),"")</f>
-        <v>Generar el reporte de reservas por hotel</v>
-      </c>
-      <c r="C72" s="24" t="str">
-        <f>IFERROR(INDEX(Requerimientos!$C:$C,MATCH($A72,Requerimientos!$A:$A,0)),"")</f>
-        <v>Superadmin</v>
-      </c>
-      <c r="D72" s="24" t="str">
-        <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A72,Requerimientos!$A:$A,0)),"")</f>
-        <v>M9 Reportes y logs</v>
-      </c>
-      <c r="E72" s="24" t="str">
-        <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A72,Requerimientos!$A:$A,0)),"")</f>
-        <v>Media</v>
-      </c>
-      <c r="F72" s="24" t="str">
-        <f>IFERROR(INDEX(Requerimientos!$H:$H,MATCH($A72,Requerimientos!$A:$A,0)),"")</f>
-        <v>L3  ·  L4  ·  L6</v>
-      </c>
-      <c r="G72" s="24" t="str">
-        <f>IFERROR(INDEX(Requerimientos!$I:$I,MATCH($A72,Requerimientos!$A:$A,0)),"")</f>
-        <v>Lab 6</v>
-      </c>
-      <c r="H72" s="24" t="str">
-        <f>IFERROR(INDEX(Requerimientos!$J:$J,MATCH($A72,Requerimientos!$A:$A,0)),"")</f>
-        <v>Pendiente</v>
-      </c>
+    <row r="72" spans="1:8" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A72" s="29" t="s">
+        <v>314</v>
+      </c>
+      <c r="B72" s="30"/>
+      <c r="C72" s="30"/>
+      <c r="D72" s="30"/>
+      <c r="E72" s="30"/>
+      <c r="F72" s="30"/>
+      <c r="G72" s="30"/>
+      <c r="H72" s="30"/>
     </row>
     <row r="73" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A73" s="26" t="s">
-        <v>138</v>
+        <v>126</v>
       </c>
       <c r="B73" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A73,Requerimientos!$A:$A,0)),"")</f>
-        <v>Consultar el visor de logs de eventos del sistema</v>
+        <v>Activar y desactivar administradores de hotel taxistas y clientes</v>
       </c>
       <c r="C73" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$C:$C,MATCH($A73,Requerimientos!$A:$A,0)),"")</f>
@@ -9202,11 +9205,11 @@
       </c>
       <c r="D73" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A73,Requerimientos!$A:$A,0)),"")</f>
-        <v>M9 Reportes y logs</v>
+        <v>M2 Gestión de usuarios</v>
       </c>
       <c r="E73" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A73,Requerimientos!$A:$A,0)),"")</f>
-        <v>Media</v>
+        <v>Alta</v>
       </c>
       <c r="F73" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$H:$H,MATCH($A73,Requerimientos!$A:$A,0)),"")</f>
@@ -9223,19 +9226,19 @@
     </row>
     <row r="74" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A74" s="26" t="s">
-        <v>145</v>
+        <v>132</v>
       </c>
       <c r="B74" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A74,Requerimientos!$A:$A,0)),"")</f>
-        <v>Subir fotos del hotel con un mínimo de 4</v>
+        <v>Registrar hoteles y asignar un administrador a cada uno</v>
       </c>
       <c r="C74" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$C:$C,MATCH($A74,Requerimientos!$A:$A,0)),"")</f>
-        <v>Administrador de hotel</v>
+        <v>Superadmin</v>
       </c>
       <c r="D74" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A74,Requerimientos!$A:$A,0)),"")</f>
-        <v>M3 Catálogo</v>
+        <v>M2 Gestión de usuarios</v>
       </c>
       <c r="E74" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A74,Requerimientos!$A:$A,0)),"")</f>
@@ -9243,7 +9246,7 @@
       </c>
       <c r="F74" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$H:$H,MATCH($A74,Requerimientos!$A:$A,0)),"")</f>
-        <v>L3  ·  L4  ·  L5  ·  L6</v>
+        <v>L3  ·  L4  ·  L6</v>
       </c>
       <c r="G74" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$I:$I,MATCH($A74,Requerimientos!$A:$A,0)),"")</f>
@@ -9256,23 +9259,23 @@
     </row>
     <row r="75" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A75" s="26" t="s">
-        <v>151</v>
+        <v>135</v>
       </c>
       <c r="B75" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A75,Requerimientos!$A:$A,0)),"")</f>
-        <v>Registrar habitaciones con tipo capacidad de adultos y niños y tamaño en m2</v>
+        <v>Generar el reporte de reservas por hotel</v>
       </c>
       <c r="C75" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$C:$C,MATCH($A75,Requerimientos!$A:$A,0)),"")</f>
-        <v>Administrador de hotel</v>
+        <v>Superadmin</v>
       </c>
       <c r="D75" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A75,Requerimientos!$A:$A,0)),"")</f>
-        <v>M3 Catálogo</v>
+        <v>M9 Reportes y logs</v>
       </c>
       <c r="E75" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A75,Requerimientos!$A:$A,0)),"")</f>
-        <v>Alta</v>
+        <v>Media</v>
       </c>
       <c r="F75" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$H:$H,MATCH($A75,Requerimientos!$A:$A,0)),"")</f>
@@ -9289,23 +9292,23 @@
     </row>
     <row r="76" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A76" s="26" t="s">
-        <v>154</v>
+        <v>138</v>
       </c>
       <c r="B76" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A76,Requerimientos!$A:$A,0)),"")</f>
-        <v>Registrar servicios con nombre descripción precio imágenes y si tienen costo</v>
+        <v>Consultar el visor de logs de eventos del sistema</v>
       </c>
       <c r="C76" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$C:$C,MATCH($A76,Requerimientos!$A:$A,0)),"")</f>
-        <v>Administrador de hotel</v>
+        <v>Superadmin</v>
       </c>
       <c r="D76" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A76,Requerimientos!$A:$A,0)),"")</f>
-        <v>M3 Catálogo</v>
+        <v>M9 Reportes y logs</v>
       </c>
       <c r="E76" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A76,Requerimientos!$A:$A,0)),"")</f>
-        <v>Alta</v>
+        <v>Media</v>
       </c>
       <c r="F76" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$H:$H,MATCH($A76,Requerimientos!$A:$A,0)),"")</f>
@@ -9322,11 +9325,11 @@
     </row>
     <row r="77" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A77" s="26" t="s">
-        <v>157</v>
+        <v>145</v>
       </c>
       <c r="B77" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A77,Requerimientos!$A:$A,0)),"")</f>
-        <v>Recibir la alerta de checkout y procesar el cobro de la tarjeta registrada</v>
+        <v>Subir fotos del hotel con un mínimo de 4</v>
       </c>
       <c r="C77" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$C:$C,MATCH($A77,Requerimientos!$A:$A,0)),"")</f>
@@ -9334,7 +9337,7 @@
       </c>
       <c r="D77" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A77,Requerimientos!$A:$A,0)),"")</f>
-        <v>M5 Pagos y cobros</v>
+        <v>M3 Catálogo</v>
       </c>
       <c r="E77" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A77,Requerimientos!$A:$A,0)),"")</f>
@@ -9342,7 +9345,7 @@
       </c>
       <c r="F77" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$H:$H,MATCH($A77,Requerimientos!$A:$A,0)),"")</f>
-        <v>L3  ·  L5  ·  L6</v>
+        <v>L3  ·  L4  ·  L5  ·  L6</v>
       </c>
       <c r="G77" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$I:$I,MATCH($A77,Requerimientos!$A:$A,0)),"")</f>
@@ -9355,11 +9358,11 @@
     </row>
     <row r="78" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A78" s="26" t="s">
-        <v>161</v>
+        <v>151</v>
       </c>
       <c r="B78" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A78,Requerimientos!$A:$A,0)),"")</f>
-        <v>Responder los chats de clientes con reserva activa</v>
+        <v>Registrar habitaciones con tipo capacidad de adultos y niños y tamaño en m2</v>
       </c>
       <c r="C78" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$C:$C,MATCH($A78,Requerimientos!$A:$A,0)),"")</f>
@@ -9367,7 +9370,7 @@
       </c>
       <c r="D78" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A78,Requerimientos!$A:$A,0)),"")</f>
-        <v>M7 Chat</v>
+        <v>M3 Catálogo</v>
       </c>
       <c r="E78" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A78,Requerimientos!$A:$A,0)),"")</f>
@@ -9388,11 +9391,11 @@
     </row>
     <row r="79" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A79" s="26" t="s">
-        <v>164</v>
+        <v>154</v>
       </c>
       <c r="B79" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A79,Requerimientos!$A:$A,0)),"")</f>
-        <v>Establecer el monto mínimo de reserva que da derecho al taxi gratuito al aeropuerto</v>
+        <v>Registrar servicios con nombre descripción precio imágenes y si tienen costo</v>
       </c>
       <c r="C79" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$C:$C,MATCH($A79,Requerimientos!$A:$A,0)),"")</f>
@@ -9400,7 +9403,7 @@
       </c>
       <c r="D79" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A79,Requerimientos!$A:$A,0)),"")</f>
-        <v>M8 Taxi</v>
+        <v>M3 Catálogo</v>
       </c>
       <c r="E79" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A79,Requerimientos!$A:$A,0)),"")</f>
@@ -9408,7 +9411,7 @@
       </c>
       <c r="F79" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$H:$H,MATCH($A79,Requerimientos!$A:$A,0)),"")</f>
-        <v>L3  ·  L6</v>
+        <v>L3  ·  L4  ·  L6</v>
       </c>
       <c r="G79" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$I:$I,MATCH($A79,Requerimientos!$A:$A,0)),"")</f>
@@ -9421,11 +9424,11 @@
     </row>
     <row r="80" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A80" s="26" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="B80" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A80,Requerimientos!$A:$A,0)),"")</f>
-        <v>Añadir cobros adicionales por daños con monto motivo y observación</v>
+        <v>Recibir la alerta de checkout y procesar el cobro de la tarjeta registrada</v>
       </c>
       <c r="C80" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$C:$C,MATCH($A80,Requerimientos!$A:$A,0)),"")</f>
@@ -9437,11 +9440,11 @@
       </c>
       <c r="E80" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A80,Requerimientos!$A:$A,0)),"")</f>
-        <v>Media</v>
+        <v>Alta</v>
       </c>
       <c r="F80" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$H:$H,MATCH($A80,Requerimientos!$A:$A,0)),"")</f>
-        <v>L3  ·  L6</v>
+        <v>L3  ·  L5  ·  L6</v>
       </c>
       <c r="G80" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$I:$I,MATCH($A80,Requerimientos!$A:$A,0)),"")</f>
@@ -9454,11 +9457,11 @@
     </row>
     <row r="81" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A81" s="26" t="s">
-        <v>172</v>
+        <v>161</v>
       </c>
       <c r="B81" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A81,Requerimientos!$A:$A,0)),"")</f>
-        <v>Reporte de ingresos por servicios adicionales ordenado de menor a mayor</v>
+        <v>Responder los chats de clientes con reserva activa</v>
       </c>
       <c r="C81" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$C:$C,MATCH($A81,Requerimientos!$A:$A,0)),"")</f>
@@ -9466,11 +9469,11 @@
       </c>
       <c r="D81" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A81,Requerimientos!$A:$A,0)),"")</f>
-        <v>M9 Reportes y logs</v>
+        <v>M7 Chat</v>
       </c>
       <c r="E81" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A81,Requerimientos!$A:$A,0)),"")</f>
-        <v>Media</v>
+        <v>Alta</v>
       </c>
       <c r="F81" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$H:$H,MATCH($A81,Requerimientos!$A:$A,0)),"")</f>
@@ -9487,11 +9490,11 @@
     </row>
     <row r="82" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A82" s="26" t="s">
-        <v>177</v>
+        <v>164</v>
       </c>
       <c r="B82" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A82,Requerimientos!$A:$A,0)),"")</f>
-        <v>Registrar la ubicación del hotel y los lugares históricos cercanos</v>
+        <v>Establecer el monto mínimo de reserva que da derecho al taxi gratuito al aeropuerto</v>
       </c>
       <c r="C82" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$C:$C,MATCH($A82,Requerimientos!$A:$A,0)),"")</f>
@@ -9499,7 +9502,7 @@
       </c>
       <c r="D82" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A82,Requerimientos!$A:$A,0)),"")</f>
-        <v>M3 Catálogo</v>
+        <v>M8 Taxi</v>
       </c>
       <c r="E82" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A82,Requerimientos!$A:$A,0)),"")</f>
@@ -9507,11 +9510,11 @@
       </c>
       <c r="F82" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$H:$H,MATCH($A82,Requerimientos!$A:$A,0)),"")</f>
-        <v>L3  ·  L6  ·  L7</v>
+        <v>L3  ·  L6</v>
       </c>
       <c r="G82" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$I:$I,MATCH($A82,Requerimientos!$A:$A,0)),"")</f>
-        <v>Lab 7</v>
+        <v>Lab 6</v>
       </c>
       <c r="H82" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$J:$J,MATCH($A82,Requerimientos!$A:$A,0)),"")</f>
@@ -9520,11 +9523,11 @@
     </row>
     <row r="83" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A83" s="26" t="s">
-        <v>182</v>
+        <v>169</v>
       </c>
       <c r="B83" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A83,Requerimientos!$A:$A,0)),"")</f>
-        <v>Ver el estado del taxista asignado en camino a recoger y llegó al destino</v>
+        <v>Añadir cobros adicionales por daños con monto motivo y observación</v>
       </c>
       <c r="C83" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$C:$C,MATCH($A83,Requerimientos!$A:$A,0)),"")</f>
@@ -9532,7 +9535,7 @@
       </c>
       <c r="D83" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A83,Requerimientos!$A:$A,0)),"")</f>
-        <v>M8 Taxi</v>
+        <v>M5 Pagos y cobros</v>
       </c>
       <c r="E83" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A83,Requerimientos!$A:$A,0)),"")</f>
@@ -9540,11 +9543,11 @@
       </c>
       <c r="F83" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$H:$H,MATCH($A83,Requerimientos!$A:$A,0)),"")</f>
-        <v>L3  ·  L6  ·  L7</v>
+        <v>L3  ·  L4  ·  L6</v>
       </c>
       <c r="G83" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$I:$I,MATCH($A83,Requerimientos!$A:$A,0)),"")</f>
-        <v>Lab 7</v>
+        <v>Lab 6</v>
       </c>
       <c r="H83" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$J:$J,MATCH($A83,Requerimientos!$A:$A,0)),"")</f>
@@ -9553,27 +9556,27 @@
     </row>
     <row r="84" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A84" s="26" t="s">
-        <v>185</v>
+        <v>172</v>
       </c>
       <c r="B84" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A84,Requerimientos!$A:$A,0)),"")</f>
-        <v>Acceder a la app móvil una vez habilitado</v>
+        <v>Reporte de ingresos por servicios adicionales ordenado de menor a mayor</v>
       </c>
       <c r="C84" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$C:$C,MATCH($A84,Requerimientos!$A:$A,0)),"")</f>
-        <v>Taxista</v>
+        <v>Administrador de hotel</v>
       </c>
       <c r="D84" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A84,Requerimientos!$A:$A,0)),"")</f>
-        <v>M1 Autenticación</v>
+        <v>M9 Reportes y logs</v>
       </c>
       <c r="E84" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A84,Requerimientos!$A:$A,0)),"")</f>
-        <v>Alta</v>
+        <v>Media</v>
       </c>
       <c r="F84" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$H:$H,MATCH($A84,Requerimientos!$A:$A,0)),"")</f>
-        <v>L3  ·  L5  ·  L6</v>
+        <v>L3  ·  L4  ·  L6</v>
       </c>
       <c r="G84" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$I:$I,MATCH($A84,Requerimientos!$A:$A,0)),"")</f>
@@ -9586,19 +9589,19 @@
     </row>
     <row r="85" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A85" s="26" t="s">
-        <v>188</v>
+        <v>177</v>
       </c>
       <c r="B85" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A85,Requerimientos!$A:$A,0)),"")</f>
-        <v>Ver hoteles y pedidos disponibles</v>
+        <v>Registrar la ubicación del hotel y los lugares históricos cercanos</v>
       </c>
       <c r="C85" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$C:$C,MATCH($A85,Requerimientos!$A:$A,0)),"")</f>
-        <v>Taxista</v>
+        <v>Administrador de hotel</v>
       </c>
       <c r="D85" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A85,Requerimientos!$A:$A,0)),"")</f>
-        <v>M8 Taxi</v>
+        <v>M3 Catálogo</v>
       </c>
       <c r="E85" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A85,Requerimientos!$A:$A,0)),"")</f>
@@ -9606,11 +9609,11 @@
       </c>
       <c r="F85" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$H:$H,MATCH($A85,Requerimientos!$A:$A,0)),"")</f>
-        <v>L3  ·  L4  ·  L5  ·  L6</v>
+        <v>L3  ·  L4  ·  L6  ·  L7</v>
       </c>
       <c r="G85" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$I:$I,MATCH($A85,Requerimientos!$A:$A,0)),"")</f>
-        <v>Lab 6</v>
+        <v>Lab 7</v>
       </c>
       <c r="H85" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$J:$J,MATCH($A85,Requerimientos!$A:$A,0)),"")</f>
@@ -9619,15 +9622,15 @@
     </row>
     <row r="86" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A86" s="26" t="s">
-        <v>191</v>
+        <v>182</v>
       </c>
       <c r="B86" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A86,Requerimientos!$A:$A,0)),"")</f>
-        <v>Aceptar un pedido que deja de estar disponible para los demás</v>
+        <v>Ver el estado del taxista asignado en camino a recoger y llegó al destino</v>
       </c>
       <c r="C86" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$C:$C,MATCH($A86,Requerimientos!$A:$A,0)),"")</f>
-        <v>Taxista</v>
+        <v>Administrador de hotel</v>
       </c>
       <c r="D86" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A86,Requerimientos!$A:$A,0)),"")</f>
@@ -9635,15 +9638,15 @@
       </c>
       <c r="E86" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A86,Requerimientos!$A:$A,0)),"")</f>
-        <v>Alta</v>
+        <v>Media</v>
       </c>
       <c r="F86" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$H:$H,MATCH($A86,Requerimientos!$A:$A,0)),"")</f>
-        <v>L3  ·  L6</v>
+        <v>L3  ·  L6  ·  L7</v>
       </c>
       <c r="G86" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$I:$I,MATCH($A86,Requerimientos!$A:$A,0)),"")</f>
-        <v>Lab 6</v>
+        <v>Lab 7</v>
       </c>
       <c r="H86" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$J:$J,MATCH($A86,Requerimientos!$A:$A,0)),"")</f>
@@ -9652,11 +9655,11 @@
     </row>
     <row r="87" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A87" s="26" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="B87" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A87,Requerimientos!$A:$A,0)),"")</f>
-        <v>Actualizar los estados del servicio</v>
+        <v>Acceder a la app móvil una vez habilitado</v>
       </c>
       <c r="C87" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$C:$C,MATCH($A87,Requerimientos!$A:$A,0)),"")</f>
@@ -9664,7 +9667,7 @@
       </c>
       <c r="D87" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A87,Requerimientos!$A:$A,0)),"")</f>
-        <v>M8 Taxi</v>
+        <v>M1 Autenticación</v>
       </c>
       <c r="E87" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A87,Requerimientos!$A:$A,0)),"")</f>
@@ -9672,7 +9675,7 @@
       </c>
       <c r="F87" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$H:$H,MATCH($A87,Requerimientos!$A:$A,0)),"")</f>
-        <v>L3  ·  L6</v>
+        <v>L3  ·  L5  ·  L6</v>
       </c>
       <c r="G87" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$I:$I,MATCH($A87,Requerimientos!$A:$A,0)),"")</f>
@@ -9685,11 +9688,11 @@
     </row>
     <row r="88" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A88" s="26" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="B88" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A88,Requerimientos!$A:$A,0)),"")</f>
-        <v>Registrar automáticamente su ubicación durante el servicio activo</v>
+        <v>Ver hoteles y pedidos disponibles</v>
       </c>
       <c r="C88" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$C:$C,MATCH($A88,Requerimientos!$A:$A,0)),"")</f>
@@ -9705,11 +9708,11 @@
       </c>
       <c r="F88" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$H:$H,MATCH($A88,Requerimientos!$A:$A,0)),"")</f>
-        <v>L6  ·  L7</v>
+        <v>L3  ·  L4  ·  L5  ·  L6</v>
       </c>
       <c r="G88" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$I:$I,MATCH($A88,Requerimientos!$A:$A,0)),"")</f>
-        <v>Lab 7</v>
+        <v>Lab 6</v>
       </c>
       <c r="H88" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$J:$J,MATCH($A88,Requerimientos!$A:$A,0)),"")</f>
@@ -9718,19 +9721,19 @@
     </row>
     <row r="89" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A89" s="26" t="s">
-        <v>211</v>
+        <v>192</v>
       </c>
       <c r="B89" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A89,Requerimientos!$A:$A,0)),"")</f>
-        <v>Autoregistrarse y quedar habilitado automáticamente</v>
+        <v>Aceptar un pedido que deja de estar disponible para los demás</v>
       </c>
       <c r="C89" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$C:$C,MATCH($A89,Requerimientos!$A:$A,0)),"")</f>
-        <v>Cliente</v>
+        <v>Taxista</v>
       </c>
       <c r="D89" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A89,Requerimientos!$A:$A,0)),"")</f>
-        <v>M1 Autenticación</v>
+        <v>M8 Taxi</v>
       </c>
       <c r="E89" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A89,Requerimientos!$A:$A,0)),"")</f>
@@ -9738,7 +9741,7 @@
       </c>
       <c r="F89" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$H:$H,MATCH($A89,Requerimientos!$A:$A,0)),"")</f>
-        <v>L3  ·  L5  ·  L6</v>
+        <v>L3  ·  L6</v>
       </c>
       <c r="G89" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$I:$I,MATCH($A89,Requerimientos!$A:$A,0)),"")</f>
@@ -9751,19 +9754,19 @@
     </row>
     <row r="90" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A90" s="26" t="s">
-        <v>215</v>
+        <v>196</v>
       </c>
       <c r="B90" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A90,Requerimientos!$A:$A,0)),"")</f>
-        <v>Consultar hoteles habitaciones servicios disponibilidad y valoraciones</v>
+        <v>Actualizar los estados del servicio</v>
       </c>
       <c r="C90" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$C:$C,MATCH($A90,Requerimientos!$A:$A,0)),"")</f>
-        <v>Cliente</v>
+        <v>Taxista</v>
       </c>
       <c r="D90" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A90,Requerimientos!$A:$A,0)),"")</f>
-        <v>M3 Catálogo</v>
+        <v>M8 Taxi</v>
       </c>
       <c r="E90" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A90,Requerimientos!$A:$A,0)),"")</f>
@@ -9771,7 +9774,7 @@
       </c>
       <c r="F90" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$H:$H,MATCH($A90,Requerimientos!$A:$A,0)),"")</f>
-        <v>L3  ·  L4  ·  L6</v>
+        <v>L3  ·  L6</v>
       </c>
       <c r="G90" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$I:$I,MATCH($A90,Requerimientos!$A:$A,0)),"")</f>
@@ -9784,19 +9787,19 @@
     </row>
     <row r="91" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A91" s="26" t="s">
-        <v>218</v>
+        <v>199</v>
       </c>
       <c r="B91" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A91,Requerimientos!$A:$A,0)),"")</f>
-        <v>Reservar con tarjeta de crédito o débito simulada</v>
+        <v>Registrar automáticamente su ubicación durante el servicio activo</v>
       </c>
       <c r="C91" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$C:$C,MATCH($A91,Requerimientos!$A:$A,0)),"")</f>
-        <v>Cliente</v>
+        <v>Taxista</v>
       </c>
       <c r="D91" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A91,Requerimientos!$A:$A,0)),"")</f>
-        <v>M4 Reservas</v>
+        <v>M8 Taxi</v>
       </c>
       <c r="E91" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A91,Requerimientos!$A:$A,0)),"")</f>
@@ -9804,11 +9807,11 @@
       </c>
       <c r="F91" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$H:$H,MATCH($A91,Requerimientos!$A:$A,0)),"")</f>
-        <v>L3  ·  L6</v>
+        <v>L6  ·  L7</v>
       </c>
       <c r="G91" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$I:$I,MATCH($A91,Requerimientos!$A:$A,0)),"")</f>
-        <v>Lab 6</v>
+        <v>Lab 7</v>
       </c>
       <c r="H91" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$J:$J,MATCH($A91,Requerimientos!$A:$A,0)),"")</f>
@@ -9817,11 +9820,11 @@
     </row>
     <row r="92" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A92" s="26" t="s">
-        <v>221</v>
+        <v>212</v>
       </c>
       <c r="B92" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A92,Requerimientos!$A:$A,0)),"")</f>
-        <v>Hacer checkout y registrar valoración y observaciones obligatorias</v>
+        <v>Autoregistrarse y quedar habilitado automáticamente</v>
       </c>
       <c r="C92" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$C:$C,MATCH($A92,Requerimientos!$A:$A,0)),"")</f>
@@ -9829,7 +9832,7 @@
       </c>
       <c r="D92" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A92,Requerimientos!$A:$A,0)),"")</f>
-        <v>M6 Checkout y valoraciones</v>
+        <v>M1 Autenticación</v>
       </c>
       <c r="E92" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A92,Requerimientos!$A:$A,0)),"")</f>
@@ -9837,7 +9840,7 @@
       </c>
       <c r="F92" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$H:$H,MATCH($A92,Requerimientos!$A:$A,0)),"")</f>
-        <v>L3  ·  L6</v>
+        <v>L3  ·  L5  ·  L6</v>
       </c>
       <c r="G92" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$I:$I,MATCH($A92,Requerimientos!$A:$A,0)),"")</f>
@@ -9850,11 +9853,11 @@
     </row>
     <row r="93" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A93" s="26" t="s">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="B93" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A93,Requerimientos!$A:$A,0)),"")</f>
-        <v>Recibir notificación cuando se le hace el cobro</v>
+        <v>Consultar hoteles habitaciones servicios disponibilidad y valoraciones</v>
       </c>
       <c r="C93" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$C:$C,MATCH($A93,Requerimientos!$A:$A,0)),"")</f>
@@ -9862,7 +9865,7 @@
       </c>
       <c r="D93" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A93,Requerimientos!$A:$A,0)),"")</f>
-        <v>M5 Pagos y cobros</v>
+        <v>M3 Catálogo</v>
       </c>
       <c r="E93" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A93,Requerimientos!$A:$A,0)),"")</f>
@@ -9870,7 +9873,7 @@
       </c>
       <c r="F93" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$H:$H,MATCH($A93,Requerimientos!$A:$A,0)),"")</f>
-        <v>L3  ·  L5  ·  L6</v>
+        <v>L3  ·  L4  ·  L6</v>
       </c>
       <c r="G93" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$I:$I,MATCH($A93,Requerimientos!$A:$A,0)),"")</f>
@@ -9883,11 +9886,11 @@
     </row>
     <row r="94" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A94" s="26" t="s">
-        <v>228</v>
+        <v>219</v>
       </c>
       <c r="B94" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A94,Requerimientos!$A:$A,0)),"")</f>
-        <v>Chat privado con el hotel entre la confirmación de la reserva y el fin del checkout</v>
+        <v>Reservar con tarjeta de crédito o débito simulada</v>
       </c>
       <c r="C94" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$C:$C,MATCH($A94,Requerimientos!$A:$A,0)),"")</f>
@@ -9895,7 +9898,7 @@
       </c>
       <c r="D94" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A94,Requerimientos!$A:$A,0)),"")</f>
-        <v>M7 Chat</v>
+        <v>M4 Reservas</v>
       </c>
       <c r="E94" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A94,Requerimientos!$A:$A,0)),"")</f>
@@ -9903,7 +9906,7 @@
       </c>
       <c r="F94" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$H:$H,MATCH($A94,Requerimientos!$A:$A,0)),"")</f>
-        <v>L3  ·  L4  ·  L6</v>
+        <v>L3  ·  L6</v>
       </c>
       <c r="G94" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$I:$I,MATCH($A94,Requerimientos!$A:$A,0)),"")</f>
@@ -9916,11 +9919,11 @@
     </row>
     <row r="95" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A95" s="26" t="s">
-        <v>232</v>
+        <v>222</v>
       </c>
       <c r="B95" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A95,Requerimientos!$A:$A,0)),"")</f>
-        <v>Ver el historial de sus reservas</v>
+        <v>Hacer checkout y registrar valoración y observaciones obligatorias</v>
       </c>
       <c r="C95" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$C:$C,MATCH($A95,Requerimientos!$A:$A,0)),"")</f>
@@ -9928,15 +9931,15 @@
       </c>
       <c r="D95" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A95,Requerimientos!$A:$A,0)),"")</f>
-        <v>M4 Reservas</v>
+        <v>M6 Checkout y valoraciones</v>
       </c>
       <c r="E95" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A95,Requerimientos!$A:$A,0)),"")</f>
-        <v>Media</v>
+        <v>Alta</v>
       </c>
       <c r="F95" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$H:$H,MATCH($A95,Requerimientos!$A:$A,0)),"")</f>
-        <v>L3  ·  L4  ·  L6</v>
+        <v>L3  ·  L6</v>
       </c>
       <c r="G95" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$I:$I,MATCH($A95,Requerimientos!$A:$A,0)),"")</f>
@@ -9949,11 +9952,11 @@
     </row>
     <row r="96" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A96" s="26" t="s">
-        <v>235</v>
+        <v>225</v>
       </c>
       <c r="B96" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A96,Requerimientos!$A:$A,0)),"")</f>
-        <v>Consultar los lugares históricos cercanos al hotel</v>
+        <v>Recibir notificación cuando se le hace el cobro</v>
       </c>
       <c r="C96" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$C:$C,MATCH($A96,Requerimientos!$A:$A,0)),"")</f>
@@ -9961,15 +9964,15 @@
       </c>
       <c r="D96" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A96,Requerimientos!$A:$A,0)),"")</f>
-        <v>M3 Catálogo</v>
+        <v>M5 Pagos y cobros</v>
       </c>
       <c r="E96" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A96,Requerimientos!$A:$A,0)),"")</f>
-        <v>Media</v>
+        <v>Alta</v>
       </c>
       <c r="F96" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$H:$H,MATCH($A96,Requerimientos!$A:$A,0)),"")</f>
-        <v>L3  ·  L4  ·  L6</v>
+        <v>L3  ·  L5  ·  L6</v>
       </c>
       <c r="G96" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$I:$I,MATCH($A96,Requerimientos!$A:$A,0)),"")</f>
@@ -9982,11 +9985,11 @@
     </row>
     <row r="97" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A97" s="26" t="s">
-        <v>239</v>
+        <v>229</v>
       </c>
       <c r="B97" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A97,Requerimientos!$A:$A,0)),"")</f>
-        <v>Solicitar el taxi gratuito al aeropuerto si la reserva alcanza el monto mínimo</v>
+        <v>Chat privado con el hotel entre la confirmación de la reserva y el fin del checkout</v>
       </c>
       <c r="C97" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$C:$C,MATCH($A97,Requerimientos!$A:$A,0)),"")</f>
@@ -9994,7 +9997,7 @@
       </c>
       <c r="D97" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A97,Requerimientos!$A:$A,0)),"")</f>
-        <v>M8 Taxi</v>
+        <v>M7 Chat</v>
       </c>
       <c r="E97" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A97,Requerimientos!$A:$A,0)),"")</f>
@@ -10002,11 +10005,11 @@
       </c>
       <c r="F97" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$H:$H,MATCH($A97,Requerimientos!$A:$A,0)),"")</f>
-        <v>L3  ·  L6  ·  L7</v>
+        <v>L3  ·  L4  ·  L6</v>
       </c>
       <c r="G97" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$I:$I,MATCH($A97,Requerimientos!$A:$A,0)),"")</f>
-        <v>Lab 7</v>
+        <v>Lab 6</v>
       </c>
       <c r="H97" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$J:$J,MATCH($A97,Requerimientos!$A:$A,0)),"")</f>
@@ -10015,11 +10018,11 @@
     </row>
     <row r="98" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A98" s="26" t="s">
-        <v>249</v>
+        <v>233</v>
       </c>
       <c r="B98" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A98,Requerimientos!$A:$A,0)),"")</f>
-        <v>Calificar al taxista al finalizar el servicio</v>
+        <v>Ver el historial de sus reservas</v>
       </c>
       <c r="C98" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$C:$C,MATCH($A98,Requerimientos!$A:$A,0)),"")</f>
@@ -10027,7 +10030,7 @@
       </c>
       <c r="D98" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A98,Requerimientos!$A:$A,0)),"")</f>
-        <v>M8 Taxi</v>
+        <v>M4 Reservas</v>
       </c>
       <c r="E98" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A98,Requerimientos!$A:$A,0)),"")</f>
@@ -10035,11 +10038,11 @@
       </c>
       <c r="F98" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$H:$H,MATCH($A98,Requerimientos!$A:$A,0)),"")</f>
-        <v>L3  ·  L6  ·  L7</v>
+        <v>L3  ·  L4  ·  L6</v>
       </c>
       <c r="G98" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$I:$I,MATCH($A98,Requerimientos!$A:$A,0)),"")</f>
-        <v>Lab 7</v>
+        <v>Lab 6</v>
       </c>
       <c r="H98" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$J:$J,MATCH($A98,Requerimientos!$A:$A,0)),"")</f>
@@ -10048,27 +10051,27 @@
     </row>
     <row r="99" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A99" s="26" t="s">
-        <v>258</v>
+        <v>236</v>
       </c>
       <c r="B99" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A99,Requerimientos!$A:$A,0)),"")</f>
-        <v>Una habitación no puede tener reservas de distintos clientes con períodos superpuestos</v>
+        <v>Consultar los lugares históricos cercanos al hotel</v>
       </c>
       <c r="C99" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$C:$C,MATCH($A99,Requerimientos!$A:$A,0)),"")</f>
-        <v>Transversal</v>
+        <v>Cliente</v>
       </c>
       <c r="D99" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A99,Requerimientos!$A:$A,0)),"")</f>
-        <v>M4 Reservas</v>
+        <v>M3 Catálogo</v>
       </c>
       <c r="E99" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A99,Requerimientos!$A:$A,0)),"")</f>
-        <v>Alta</v>
+        <v>Media</v>
       </c>
       <c r="F99" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$H:$H,MATCH($A99,Requerimientos!$A:$A,0)),"")</f>
-        <v>L3  ·  L6</v>
+        <v>L3  ·  L4  ·  L6</v>
       </c>
       <c r="G99" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$I:$I,MATCH($A99,Requerimientos!$A:$A,0)),"")</f>
@@ -10081,19 +10084,19 @@
     </row>
     <row r="100" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A100" s="26" t="s">
-        <v>262</v>
+        <v>240</v>
       </c>
       <c r="B100" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A100,Requerimientos!$A:$A,0)),"")</f>
-        <v>Un mismo cliente no puede tener reservas con fechas de alojamiento superpuestas</v>
+        <v>Solicitar el taxi gratuito al aeropuerto si la reserva alcanza el monto mínimo</v>
       </c>
       <c r="C100" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$C:$C,MATCH($A100,Requerimientos!$A:$A,0)),"")</f>
-        <v>Transversal</v>
+        <v>Cliente</v>
       </c>
       <c r="D100" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A100,Requerimientos!$A:$A,0)),"")</f>
-        <v>M4 Reservas</v>
+        <v>M8 Taxi</v>
       </c>
       <c r="E100" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A100,Requerimientos!$A:$A,0)),"")</f>
@@ -10101,11 +10104,11 @@
       </c>
       <c r="F100" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$H:$H,MATCH($A100,Requerimientos!$A:$A,0)),"")</f>
-        <v>L3  ·  L6</v>
+        <v>L3  ·  L6  ·  L7</v>
       </c>
       <c r="G100" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$I:$I,MATCH($A100,Requerimientos!$A:$A,0)),"")</f>
-        <v>Lab 6</v>
+        <v>Lab 7</v>
       </c>
       <c r="H100" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$J:$J,MATCH($A100,Requerimientos!$A:$A,0)),"")</f>
@@ -10114,31 +10117,31 @@
     </row>
     <row r="101" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A101" s="26" t="s">
-        <v>265</v>
+        <v>250</v>
       </c>
       <c r="B101" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A101,Requerimientos!$A:$A,0)),"")</f>
-        <v>Login único: tras autenticar se resuelve el rol y se navega al flujo correspondiente</v>
+        <v>Calificar al taxista al finalizar el servicio</v>
       </c>
       <c r="C101" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$C:$C,MATCH($A101,Requerimientos!$A:$A,0)),"")</f>
-        <v>Transversal</v>
+        <v>Cliente</v>
       </c>
       <c r="D101" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A101,Requerimientos!$A:$A,0)),"")</f>
-        <v>M1 Autenticación</v>
+        <v>M8 Taxi</v>
       </c>
       <c r="E101" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A101,Requerimientos!$A:$A,0)),"")</f>
-        <v>Alta</v>
+        <v>Media</v>
       </c>
       <c r="F101" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$H:$H,MATCH($A101,Requerimientos!$A:$A,0)),"")</f>
-        <v>L3  ·  L6</v>
+        <v>L3  ·  L6  ·  L7</v>
       </c>
       <c r="G101" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$I:$I,MATCH($A101,Requerimientos!$A:$A,0)),"")</f>
-        <v>Lab 6</v>
+        <v>Lab 7</v>
       </c>
       <c r="H101" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$J:$J,MATCH($A101,Requerimientos!$A:$A,0)),"")</f>
@@ -10147,11 +10150,11 @@
     </row>
     <row r="102" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A102" s="26" t="s">
-        <v>268</v>
+        <v>259</v>
       </c>
       <c r="B102" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A102,Requerimientos!$A:$A,0)),"")</f>
-        <v>Los mensajes de chat persisten con fecha y hora</v>
+        <v>Una habitación no puede tener reservas de distintos clientes con períodos superpuestos</v>
       </c>
       <c r="C102" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$C:$C,MATCH($A102,Requerimientos!$A:$A,0)),"")</f>
@@ -10159,7 +10162,7 @@
       </c>
       <c r="D102" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A102,Requerimientos!$A:$A,0)),"")</f>
-        <v>M7 Chat</v>
+        <v>M4 Reservas</v>
       </c>
       <c r="E102" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A102,Requerimientos!$A:$A,0)),"")</f>
@@ -10167,7 +10170,7 @@
       </c>
       <c r="F102" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$H:$H,MATCH($A102,Requerimientos!$A:$A,0)),"")</f>
-        <v>L3  ·  L4  ·  L6</v>
+        <v>L3  ·  L6</v>
       </c>
       <c r="G102" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$I:$I,MATCH($A102,Requerimientos!$A:$A,0)),"")</f>
@@ -10180,11 +10183,11 @@
     </row>
     <row r="103" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A103" s="26" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="B103" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A103,Requerimientos!$A:$A,0)),"")</f>
-        <v>Las contraseñas nunca se almacenan en texto plano</v>
+        <v>Un mismo cliente no puede tener reservas con fechas de alojamiento superpuestas</v>
       </c>
       <c r="C103" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$C:$C,MATCH($A103,Requerimientos!$A:$A,0)),"")</f>
@@ -10192,7 +10195,7 @@
       </c>
       <c r="D103" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A103,Requerimientos!$A:$A,0)),"")</f>
-        <v>M10 Calidad</v>
+        <v>M4 Reservas</v>
       </c>
       <c r="E103" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A103,Requerimientos!$A:$A,0)),"")</f>
@@ -10200,7 +10203,7 @@
       </c>
       <c r="F103" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$H:$H,MATCH($A103,Requerimientos!$A:$A,0)),"")</f>
-        <v>L6</v>
+        <v>L3  ·  L6</v>
       </c>
       <c r="G103" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$I:$I,MATCH($A103,Requerimientos!$A:$A,0)),"")</f>
@@ -10213,11 +10216,11 @@
     </row>
     <row r="104" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A104" s="26" t="s">
-        <v>275</v>
+        <v>266</v>
       </c>
       <c r="B104" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A104,Requerimientos!$A:$A,0)),"")</f>
-        <v>Las operaciones están restringidas según el rol autenticado</v>
+        <v>Login único: tras autenticar se resuelve el rol y se navega al flujo correspondiente</v>
       </c>
       <c r="C104" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$C:$C,MATCH($A104,Requerimientos!$A:$A,0)),"")</f>
@@ -10225,7 +10228,7 @@
       </c>
       <c r="D104" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A104,Requerimientos!$A:$A,0)),"")</f>
-        <v>M10 Calidad</v>
+        <v>M1 Autenticación</v>
       </c>
       <c r="E104" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A104,Requerimientos!$A:$A,0)),"")</f>
@@ -10233,7 +10236,7 @@
       </c>
       <c r="F104" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$H:$H,MATCH($A104,Requerimientos!$A:$A,0)),"")</f>
-        <v>L6</v>
+        <v>L3  ·  L5  ·  L6</v>
       </c>
       <c r="G104" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$I:$I,MATCH($A104,Requerimientos!$A:$A,0)),"")</f>
@@ -10246,11 +10249,11 @@
     </row>
     <row r="105" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A105" s="26" t="s">
-        <v>278</v>
+        <v>269</v>
       </c>
       <c r="B105" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A105,Requerimientos!$A:$A,0)),"")</f>
-        <v>Un cliente solo accede a sus propios datos</v>
+        <v>Los mensajes de chat persisten con fecha y hora</v>
       </c>
       <c r="C105" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$C:$C,MATCH($A105,Requerimientos!$A:$A,0)),"")</f>
@@ -10258,7 +10261,7 @@
       </c>
       <c r="D105" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A105,Requerimientos!$A:$A,0)),"")</f>
-        <v>M10 Calidad</v>
+        <v>M7 Chat</v>
       </c>
       <c r="E105" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A105,Requerimientos!$A:$A,0)),"")</f>
@@ -10266,7 +10269,7 @@
       </c>
       <c r="F105" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$H:$H,MATCH($A105,Requerimientos!$A:$A,0)),"")</f>
-        <v>L6</v>
+        <v>L3  ·  L4  ·  L6</v>
       </c>
       <c r="G105" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$I:$I,MATCH($A105,Requerimientos!$A:$A,0)),"")</f>
@@ -10279,11 +10282,11 @@
     </row>
     <row r="106" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A106" s="26" t="s">
-        <v>281</v>
+        <v>272</v>
       </c>
       <c r="B106" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A106,Requerimientos!$A:$A,0)),"")</f>
-        <v>La persistencia de la app principal es una base de datos NoSQL</v>
+        <v>Las contraseñas nunca se almacenan en texto plano</v>
       </c>
       <c r="C106" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$C:$C,MATCH($A106,Requerimientos!$A:$A,0)),"")</f>
@@ -10312,11 +10315,11 @@
     </row>
     <row r="107" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A107" s="26" t="s">
-        <v>284</v>
+        <v>276</v>
       </c>
       <c r="B107" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A107,Requerimientos!$A:$A,0)),"")</f>
-        <v>El sistema registra los eventos relevantes en logs consultables por el Superadmin</v>
+        <v>Las operaciones están restringidas según el rol autenticado</v>
       </c>
       <c r="C107" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$C:$C,MATCH($A107,Requerimientos!$A:$A,0)),"")</f>
@@ -10328,7 +10331,7 @@
       </c>
       <c r="E107" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A107,Requerimientos!$A:$A,0)),"")</f>
-        <v>Media</v>
+        <v>Alta</v>
       </c>
       <c r="F107" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$H:$H,MATCH($A107,Requerimientos!$A:$A,0)),"")</f>
@@ -10343,132 +10346,132 @@
         <v>Pendiente</v>
       </c>
     </row>
-    <row r="109" spans="1:8" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A109" s="29" t="s">
-        <v>314</v>
-      </c>
-      <c r="B109" s="30"/>
-      <c r="C109" s="30"/>
-      <c r="D109" s="30"/>
-      <c r="E109" s="30"/>
-      <c r="F109" s="30"/>
-      <c r="G109" s="30"/>
-      <c r="H109" s="30"/>
+    <row r="108" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A108" s="26" t="s">
+        <v>279</v>
+      </c>
+      <c r="B108" s="3" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A108,Requerimientos!$A:$A,0)),"")</f>
+        <v>Un cliente solo accede a sus propios datos</v>
+      </c>
+      <c r="C108" s="24" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$C:$C,MATCH($A108,Requerimientos!$A:$A,0)),"")</f>
+        <v>Transversal</v>
+      </c>
+      <c r="D108" s="24" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A108,Requerimientos!$A:$A,0)),"")</f>
+        <v>M10 Calidad</v>
+      </c>
+      <c r="E108" s="24" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A108,Requerimientos!$A:$A,0)),"")</f>
+        <v>Alta</v>
+      </c>
+      <c r="F108" s="24" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$H:$H,MATCH($A108,Requerimientos!$A:$A,0)),"")</f>
+        <v>L6</v>
+      </c>
+      <c r="G108" s="24" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$I:$I,MATCH($A108,Requerimientos!$A:$A,0)),"")</f>
+        <v>Lab 6</v>
+      </c>
+      <c r="H108" s="24" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$J:$J,MATCH($A108,Requerimientos!$A:$A,0)),"")</f>
+        <v>Pendiente</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A109" s="26" t="s">
+        <v>282</v>
+      </c>
+      <c r="B109" s="3" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A109,Requerimientos!$A:$A,0)),"")</f>
+        <v>La persistencia de la app principal es una base de datos NoSQL</v>
+      </c>
+      <c r="C109" s="24" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$C:$C,MATCH($A109,Requerimientos!$A:$A,0)),"")</f>
+        <v>Transversal</v>
+      </c>
+      <c r="D109" s="24" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A109,Requerimientos!$A:$A,0)),"")</f>
+        <v>M10 Calidad</v>
+      </c>
+      <c r="E109" s="24" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A109,Requerimientos!$A:$A,0)),"")</f>
+        <v>Alta</v>
+      </c>
+      <c r="F109" s="24" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$H:$H,MATCH($A109,Requerimientos!$A:$A,0)),"")</f>
+        <v>L6</v>
+      </c>
+      <c r="G109" s="24" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$I:$I,MATCH($A109,Requerimientos!$A:$A,0)),"")</f>
+        <v>Lab 6</v>
+      </c>
+      <c r="H109" s="24" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$J:$J,MATCH($A109,Requerimientos!$A:$A,0)),"")</f>
+        <v>Pendiente</v>
+      </c>
     </row>
     <row r="110" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A110" s="26" t="s">
-        <v>177</v>
+        <v>285</v>
       </c>
       <c r="B110" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A110,Requerimientos!$A:$A,0)),"")</f>
-        <v>Registrar la ubicación del hotel y los lugares históricos cercanos</v>
+        <v>El sistema registra los eventos relevantes en logs consultables por el Superadmin</v>
       </c>
       <c r="C110" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$C:$C,MATCH($A110,Requerimientos!$A:$A,0)),"")</f>
-        <v>Administrador de hotel</v>
+        <v>Transversal</v>
       </c>
       <c r="D110" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A110,Requerimientos!$A:$A,0)),"")</f>
-        <v>M3 Catálogo</v>
+        <v>M10 Calidad</v>
       </c>
       <c r="E110" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A110,Requerimientos!$A:$A,0)),"")</f>
-        <v>Alta</v>
+        <v>Media</v>
       </c>
       <c r="F110" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$H:$H,MATCH($A110,Requerimientos!$A:$A,0)),"")</f>
-        <v>L3  ·  L6  ·  L7</v>
+        <v>L6</v>
       </c>
       <c r="G110" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$I:$I,MATCH($A110,Requerimientos!$A:$A,0)),"")</f>
-        <v>Lab 7</v>
+        <v>Lab 6</v>
       </c>
       <c r="H110" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$J:$J,MATCH($A110,Requerimientos!$A:$A,0)),"")</f>
         <v>Pendiente</v>
       </c>
     </row>
-    <row r="111" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A111" s="26" t="s">
-        <v>182</v>
-      </c>
-      <c r="B111" s="3" t="str">
-        <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A111,Requerimientos!$A:$A,0)),"")</f>
-        <v>Ver el estado del taxista asignado en camino a recoger y llegó al destino</v>
-      </c>
-      <c r="C111" s="24" t="str">
-        <f>IFERROR(INDEX(Requerimientos!$C:$C,MATCH($A111,Requerimientos!$A:$A,0)),"")</f>
-        <v>Administrador de hotel</v>
-      </c>
-      <c r="D111" s="24" t="str">
-        <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A111,Requerimientos!$A:$A,0)),"")</f>
-        <v>M8 Taxi</v>
-      </c>
-      <c r="E111" s="24" t="str">
-        <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A111,Requerimientos!$A:$A,0)),"")</f>
-        <v>Media</v>
-      </c>
-      <c r="F111" s="24" t="str">
-        <f>IFERROR(INDEX(Requerimientos!$H:$H,MATCH($A111,Requerimientos!$A:$A,0)),"")</f>
-        <v>L3  ·  L6  ·  L7</v>
-      </c>
-      <c r="G111" s="24" t="str">
-        <f>IFERROR(INDEX(Requerimientos!$I:$I,MATCH($A111,Requerimientos!$A:$A,0)),"")</f>
-        <v>Lab 7</v>
-      </c>
-      <c r="H111" s="24" t="str">
-        <f>IFERROR(INDEX(Requerimientos!$J:$J,MATCH($A111,Requerimientos!$A:$A,0)),"")</f>
-        <v>Pendiente</v>
-      </c>
-    </row>
-    <row r="112" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A112" s="26" t="s">
-        <v>198</v>
-      </c>
-      <c r="B112" s="3" t="str">
-        <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A112,Requerimientos!$A:$A,0)),"")</f>
-        <v>Registrar automáticamente su ubicación durante el servicio activo</v>
-      </c>
-      <c r="C112" s="24" t="str">
-        <f>IFERROR(INDEX(Requerimientos!$C:$C,MATCH($A112,Requerimientos!$A:$A,0)),"")</f>
-        <v>Taxista</v>
-      </c>
-      <c r="D112" s="24" t="str">
-        <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A112,Requerimientos!$A:$A,0)),"")</f>
-        <v>M8 Taxi</v>
-      </c>
-      <c r="E112" s="24" t="str">
-        <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A112,Requerimientos!$A:$A,0)),"")</f>
-        <v>Alta</v>
-      </c>
-      <c r="F112" s="24" t="str">
-        <f>IFERROR(INDEX(Requerimientos!$H:$H,MATCH($A112,Requerimientos!$A:$A,0)),"")</f>
-        <v>L6  ·  L7</v>
-      </c>
-      <c r="G112" s="24" t="str">
-        <f>IFERROR(INDEX(Requerimientos!$I:$I,MATCH($A112,Requerimientos!$A:$A,0)),"")</f>
-        <v>Lab 7</v>
-      </c>
-      <c r="H112" s="24" t="str">
-        <f>IFERROR(INDEX(Requerimientos!$J:$J,MATCH($A112,Requerimientos!$A:$A,0)),"")</f>
-        <v>Pendiente</v>
-      </c>
+    <row r="112" spans="1:8" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A112" s="29" t="s">
+        <v>315</v>
+      </c>
+      <c r="B112" s="30"/>
+      <c r="C112" s="30"/>
+      <c r="D112" s="30"/>
+      <c r="E112" s="30"/>
+      <c r="F112" s="30"/>
+      <c r="G112" s="30"/>
+      <c r="H112" s="30"/>
     </row>
     <row r="113" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A113" s="26" t="s">
-        <v>203</v>
+        <v>177</v>
       </c>
       <c r="B113" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A113,Requerimientos!$A:$A,0)),"")</f>
-        <v>Registrar FINALIZADO únicamente escaneando el QR del cliente</v>
+        <v>Registrar la ubicación del hotel y los lugares históricos cercanos</v>
       </c>
       <c r="C113" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$C:$C,MATCH($A113,Requerimientos!$A:$A,0)),"")</f>
-        <v>Taxista</v>
+        <v>Administrador de hotel</v>
       </c>
       <c r="D113" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A113,Requerimientos!$A:$A,0)),"")</f>
-        <v>M8 Taxi</v>
+        <v>M3 Catálogo</v>
       </c>
       <c r="E113" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A113,Requerimientos!$A:$A,0)),"")</f>
@@ -10476,7 +10479,7 @@
       </c>
       <c r="F113" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$H:$H,MATCH($A113,Requerimientos!$A:$A,0)),"")</f>
-        <v>L3  ·  L7</v>
+        <v>L3  ·  L4  ·  L6  ·  L7</v>
       </c>
       <c r="G113" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$I:$I,MATCH($A113,Requerimientos!$A:$A,0)),"")</f>
@@ -10489,15 +10492,15 @@
     </row>
     <row r="114" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A114" s="26" t="s">
-        <v>239</v>
+        <v>182</v>
       </c>
       <c r="B114" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A114,Requerimientos!$A:$A,0)),"")</f>
-        <v>Solicitar el taxi gratuito al aeropuerto si la reserva alcanza el monto mínimo</v>
+        <v>Ver el estado del taxista asignado en camino a recoger y llegó al destino</v>
       </c>
       <c r="C114" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$C:$C,MATCH($A114,Requerimientos!$A:$A,0)),"")</f>
-        <v>Cliente</v>
+        <v>Administrador de hotel</v>
       </c>
       <c r="D114" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A114,Requerimientos!$A:$A,0)),"")</f>
@@ -10505,7 +10508,7 @@
       </c>
       <c r="E114" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A114,Requerimientos!$A:$A,0)),"")</f>
-        <v>Alta</v>
+        <v>Media</v>
       </c>
       <c r="F114" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$H:$H,MATCH($A114,Requerimientos!$A:$A,0)),"")</f>
@@ -10522,15 +10525,15 @@
     </row>
     <row r="115" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A115" s="26" t="s">
-        <v>242</v>
+        <v>199</v>
       </c>
       <c r="B115" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A115,Requerimientos!$A:$A,0)),"")</f>
-        <v>Ver datos vehículo valoración y ubicación del taxista en un mapa</v>
+        <v>Registrar automáticamente su ubicación durante el servicio activo</v>
       </c>
       <c r="C115" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$C:$C,MATCH($A115,Requerimientos!$A:$A,0)),"")</f>
-        <v>Cliente</v>
+        <v>Taxista</v>
       </c>
       <c r="D115" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A115,Requerimientos!$A:$A,0)),"")</f>
@@ -10542,7 +10545,7 @@
       </c>
       <c r="F115" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$H:$H,MATCH($A115,Requerimientos!$A:$A,0)),"")</f>
-        <v>L3  ·  L7</v>
+        <v>L6  ·  L7</v>
       </c>
       <c r="G115" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$I:$I,MATCH($A115,Requerimientos!$A:$A,0)),"")</f>
@@ -10555,15 +10558,15 @@
     </row>
     <row r="116" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A116" s="26" t="s">
-        <v>246</v>
+        <v>204</v>
       </c>
       <c r="B116" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A116,Requerimientos!$A:$A,0)),"")</f>
-        <v>Recibir el QR del hotel y mostrarlo al llegar</v>
+        <v>Registrar FINALIZADO únicamente escaneando el QR del cliente</v>
       </c>
       <c r="C116" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$C:$C,MATCH($A116,Requerimientos!$A:$A,0)),"")</f>
-        <v>Cliente</v>
+        <v>Taxista</v>
       </c>
       <c r="D116" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A116,Requerimientos!$A:$A,0)),"")</f>
@@ -10588,11 +10591,11 @@
     </row>
     <row r="117" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A117" s="26" t="s">
-        <v>249</v>
+        <v>240</v>
       </c>
       <c r="B117" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A117,Requerimientos!$A:$A,0)),"")</f>
-        <v>Calificar al taxista al finalizar el servicio</v>
+        <v>Solicitar el taxi gratuito al aeropuerto si la reserva alcanza el monto mínimo</v>
       </c>
       <c r="C117" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$C:$C,MATCH($A117,Requerimientos!$A:$A,0)),"")</f>
@@ -10604,7 +10607,7 @@
       </c>
       <c r="E117" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A117,Requerimientos!$A:$A,0)),"")</f>
-        <v>Media</v>
+        <v>Alta</v>
       </c>
       <c r="F117" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$H:$H,MATCH($A117,Requerimientos!$A:$A,0)),"")</f>
@@ -10621,19 +10624,19 @@
     </row>
     <row r="118" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A118" s="26" t="s">
-        <v>287</v>
+        <v>243</v>
       </c>
       <c r="B118" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A118,Requerimientos!$A:$A,0)),"")</f>
-        <v>La ubicación del taxista se actualiza periódicamente durante un servicio activo</v>
+        <v>Ver datos vehículo valoración y ubicación del taxista en un mapa</v>
       </c>
       <c r="C118" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$C:$C,MATCH($A118,Requerimientos!$A:$A,0)),"")</f>
-        <v>Transversal</v>
+        <v>Cliente</v>
       </c>
       <c r="D118" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A118,Requerimientos!$A:$A,0)),"")</f>
-        <v>M10 Calidad</v>
+        <v>M8 Taxi</v>
       </c>
       <c r="E118" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A118,Requerimientos!$A:$A,0)),"")</f>
@@ -10641,7 +10644,7 @@
       </c>
       <c r="F118" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$H:$H,MATCH($A118,Requerimientos!$A:$A,0)),"")</f>
-        <v>L7</v>
+        <v>L3  ·  L7</v>
       </c>
       <c r="G118" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$I:$I,MATCH($A118,Requerimientos!$A:$A,0)),"")</f>
@@ -10654,19 +10657,19 @@
     </row>
     <row r="119" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A119" s="26" t="s">
-        <v>291</v>
+        <v>247</v>
       </c>
       <c r="B119" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A119,Requerimientos!$A:$A,0)),"")</f>
-        <v>Si la API de taxistas está caída la app lo informa sin afectar el resto del sistema</v>
+        <v>Recibir el QR del hotel y mostrarlo al llegar</v>
       </c>
       <c r="C119" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$C:$C,MATCH($A119,Requerimientos!$A:$A,0)),"")</f>
-        <v>Transversal</v>
+        <v>Cliente</v>
       </c>
       <c r="D119" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A119,Requerimientos!$A:$A,0)),"")</f>
-        <v>M10 Calidad</v>
+        <v>M8 Taxi</v>
       </c>
       <c r="E119" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A119,Requerimientos!$A:$A,0)),"")</f>
@@ -10674,7 +10677,7 @@
       </c>
       <c r="F119" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$H:$H,MATCH($A119,Requerimientos!$A:$A,0)),"")</f>
-        <v>L7</v>
+        <v>L3  ·  L7</v>
       </c>
       <c r="G119" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$I:$I,MATCH($A119,Requerimientos!$A:$A,0)),"")</f>
@@ -10687,64 +10690,118 @@
     </row>
     <row r="120" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A120" s="26" t="s">
-        <v>295</v>
+        <v>250</v>
       </c>
       <c r="B120" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A120,Requerimientos!$A:$A,0)),"")</f>
-        <v>La app móvil no accede directamente a la base de datos del sistema de taxistas</v>
+        <v>Calificar al taxista al finalizar el servicio</v>
       </c>
       <c r="C120" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$C:$C,MATCH($A120,Requerimientos!$A:$A,0)),"")</f>
-        <v>Transversal</v>
+        <v>Cliente</v>
       </c>
       <c r="D120" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A120,Requerimientos!$A:$A,0)),"")</f>
-        <v>M10 Calidad</v>
+        <v>M8 Taxi</v>
       </c>
       <c r="E120" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A120,Requerimientos!$A:$A,0)),"")</f>
-        <v>Alta</v>
+        <v>Media</v>
       </c>
       <c r="F120" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$H:$H,MATCH($A120,Requerimientos!$A:$A,0)),"")</f>
-        <v>L7  ·  Web</v>
+        <v>L3  ·  L6  ·  L7</v>
       </c>
       <c r="G120" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$I:$I,MATCH($A120,Requerimientos!$A:$A,0)),"")</f>
-        <v>App web</v>
+        <v>Lab 7</v>
       </c>
       <c r="H120" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$J:$J,MATCH($A120,Requerimientos!$A:$A,0)),"")</f>
         <v>Pendiente</v>
       </c>
     </row>
-    <row r="122" spans="1:8" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A122" s="29" t="s">
-        <v>315</v>
-      </c>
-      <c r="B122" s="30"/>
-      <c r="C122" s="30"/>
-      <c r="D122" s="30"/>
-      <c r="E122" s="30"/>
-      <c r="F122" s="30"/>
-      <c r="G122" s="30"/>
-      <c r="H122" s="30"/>
+    <row r="121" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A121" s="26" t="s">
+        <v>288</v>
+      </c>
+      <c r="B121" s="3" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A121,Requerimientos!$A:$A,0)),"")</f>
+        <v>La ubicación del taxista se actualiza periódicamente durante un servicio activo</v>
+      </c>
+      <c r="C121" s="24" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$C:$C,MATCH($A121,Requerimientos!$A:$A,0)),"")</f>
+        <v>Transversal</v>
+      </c>
+      <c r="D121" s="24" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A121,Requerimientos!$A:$A,0)),"")</f>
+        <v>M10 Calidad</v>
+      </c>
+      <c r="E121" s="24" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A121,Requerimientos!$A:$A,0)),"")</f>
+        <v>Alta</v>
+      </c>
+      <c r="F121" s="24" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$H:$H,MATCH($A121,Requerimientos!$A:$A,0)),"")</f>
+        <v>L7</v>
+      </c>
+      <c r="G121" s="24" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$I:$I,MATCH($A121,Requerimientos!$A:$A,0)),"")</f>
+        <v>Lab 7</v>
+      </c>
+      <c r="H121" s="24" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$J:$J,MATCH($A121,Requerimientos!$A:$A,0)),"")</f>
+        <v>Pendiente</v>
+      </c>
+    </row>
+    <row r="122" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A122" s="26" t="s">
+        <v>292</v>
+      </c>
+      <c r="B122" s="3" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A122,Requerimientos!$A:$A,0)),"")</f>
+        <v>Si la API de taxistas está caída la app lo informa sin afectar el resto del sistema</v>
+      </c>
+      <c r="C122" s="24" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$C:$C,MATCH($A122,Requerimientos!$A:$A,0)),"")</f>
+        <v>Transversal</v>
+      </c>
+      <c r="D122" s="24" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A122,Requerimientos!$A:$A,0)),"")</f>
+        <v>M10 Calidad</v>
+      </c>
+      <c r="E122" s="24" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A122,Requerimientos!$A:$A,0)),"")</f>
+        <v>Alta</v>
+      </c>
+      <c r="F122" s="24" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$H:$H,MATCH($A122,Requerimientos!$A:$A,0)),"")</f>
+        <v>L7</v>
+      </c>
+      <c r="G122" s="24" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$I:$I,MATCH($A122,Requerimientos!$A:$A,0)),"")</f>
+        <v>Lab 7</v>
+      </c>
+      <c r="H122" s="24" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$J:$J,MATCH($A122,Requerimientos!$A:$A,0)),"")</f>
+        <v>Pendiente</v>
+      </c>
     </row>
     <row r="123" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A123" s="26" t="s">
-        <v>141</v>
+        <v>296</v>
       </c>
       <c r="B123" s="3" t="str">
         <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A123,Requerimientos!$A:$A,0)),"")</f>
-        <v>Aprobar o habilitar taxistas desde la app web</v>
+        <v>La app móvil no accede directamente a la base de datos del sistema de taxistas</v>
       </c>
       <c r="C123" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$C:$C,MATCH($A123,Requerimientos!$A:$A,0)),"")</f>
-        <v>Superadmin</v>
+        <v>Transversal</v>
       </c>
       <c r="D123" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A123,Requerimientos!$A:$A,0)),"")</f>
-        <v>M2 Gestión de usuarios</v>
+        <v>M10 Calidad</v>
       </c>
       <c r="E123" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A123,Requerimientos!$A:$A,0)),"")</f>
@@ -10752,7 +10809,7 @@
       </c>
       <c r="F123" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$H:$H,MATCH($A123,Requerimientos!$A:$A,0)),"")</f>
-        <v>Web</v>
+        <v>L7  ·  Web</v>
       </c>
       <c r="G123" s="24" t="str">
         <f>IFERROR(INDEX(Requerimientos!$I:$I,MATCH($A123,Requerimientos!$A:$A,0)),"")</f>
@@ -10763,85 +10820,130 @@
         <v>Pendiente</v>
       </c>
     </row>
-    <row r="124" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A124" s="26" t="s">
-        <v>208</v>
-      </c>
-      <c r="B124" s="3" t="str">
-        <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A124,Requerimientos!$A:$A,0)),"")</f>
+    <row r="125" spans="1:8" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A125" s="29" t="s">
+        <v>316</v>
+      </c>
+      <c r="B125" s="30"/>
+      <c r="C125" s="30"/>
+      <c r="D125" s="30"/>
+      <c r="E125" s="30"/>
+      <c r="F125" s="30"/>
+      <c r="G125" s="30"/>
+      <c r="H125" s="30"/>
+    </row>
+    <row r="126" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A126" s="26" t="s">
+        <v>141</v>
+      </c>
+      <c r="B126" s="3" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A126,Requerimientos!$A:$A,0)),"")</f>
+        <v>Aprobar o habilitar taxistas desde la app web</v>
+      </c>
+      <c r="C126" s="24" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$C:$C,MATCH($A126,Requerimientos!$A:$A,0)),"")</f>
+        <v>Superadmin</v>
+      </c>
+      <c r="D126" s="24" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A126,Requerimientos!$A:$A,0)),"")</f>
+        <v>M2 Gestión de usuarios</v>
+      </c>
+      <c r="E126" s="24" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A126,Requerimientos!$A:$A,0)),"")</f>
+        <v>Alta</v>
+      </c>
+      <c r="F126" s="24" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$H:$H,MATCH($A126,Requerimientos!$A:$A,0)),"")</f>
+        <v>Web</v>
+      </c>
+      <c r="G126" s="24" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$I:$I,MATCH($A126,Requerimientos!$A:$A,0)),"")</f>
+        <v>App web</v>
+      </c>
+      <c r="H126" s="24" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$J:$J,MATCH($A126,Requerimientos!$A:$A,0)),"")</f>
+        <v>Pendiente</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A127" s="26" t="s">
+        <v>209</v>
+      </c>
+      <c r="B127" s="3" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A127,Requerimientos!$A:$A,0)),"")</f>
         <v>Autoregistrarse en la app web con todos sus datos y fotos</v>
       </c>
-      <c r="C124" s="24" t="str">
-        <f>IFERROR(INDEX(Requerimientos!$C:$C,MATCH($A124,Requerimientos!$A:$A,0)),"")</f>
+      <c r="C127" s="24" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$C:$C,MATCH($A127,Requerimientos!$A:$A,0)),"")</f>
         <v>Taxista</v>
       </c>
-      <c r="D124" s="24" t="str">
-        <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A124,Requerimientos!$A:$A,0)),"")</f>
+      <c r="D127" s="24" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A127,Requerimientos!$A:$A,0)),"")</f>
         <v>M1 Autenticación</v>
       </c>
-      <c r="E124" s="24" t="str">
-        <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A124,Requerimientos!$A:$A,0)),"")</f>
-        <v>Alta</v>
-      </c>
-      <c r="F124" s="24" t="str">
-        <f>IFERROR(INDEX(Requerimientos!$H:$H,MATCH($A124,Requerimientos!$A:$A,0)),"")</f>
+      <c r="E127" s="24" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A127,Requerimientos!$A:$A,0)),"")</f>
+        <v>Alta</v>
+      </c>
+      <c r="F127" s="24" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$H:$H,MATCH($A127,Requerimientos!$A:$A,0)),"")</f>
         <v>Web</v>
       </c>
-      <c r="G124" s="24" t="str">
-        <f>IFERROR(INDEX(Requerimientos!$I:$I,MATCH($A124,Requerimientos!$A:$A,0)),"")</f>
+      <c r="G127" s="24" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$I:$I,MATCH($A127,Requerimientos!$A:$A,0)),"")</f>
         <v>App web</v>
       </c>
-      <c r="H124" s="24" t="str">
-        <f>IFERROR(INDEX(Requerimientos!$J:$J,MATCH($A124,Requerimientos!$A:$A,0)),"")</f>
-        <v>Pendiente</v>
-      </c>
-    </row>
-    <row r="125" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A125" s="26" t="s">
-        <v>295</v>
-      </c>
-      <c r="B125" s="3" t="str">
-        <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A125,Requerimientos!$A:$A,0)),"")</f>
+      <c r="H127" s="24" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$J:$J,MATCH($A127,Requerimientos!$A:$A,0)),"")</f>
+        <v>Pendiente</v>
+      </c>
+    </row>
+    <row r="128" spans="1:8" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A128" s="26" t="s">
+        <v>296</v>
+      </c>
+      <c r="B128" s="3" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$E:$E,MATCH($A128,Requerimientos!$A:$A,0)),"")</f>
         <v>La app móvil no accede directamente a la base de datos del sistema de taxistas</v>
       </c>
-      <c r="C125" s="24" t="str">
-        <f>IFERROR(INDEX(Requerimientos!$C:$C,MATCH($A125,Requerimientos!$A:$A,0)),"")</f>
+      <c r="C128" s="24" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$C:$C,MATCH($A128,Requerimientos!$A:$A,0)),"")</f>
         <v>Transversal</v>
       </c>
-      <c r="D125" s="24" t="str">
-        <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A125,Requerimientos!$A:$A,0)),"")</f>
+      <c r="D128" s="24" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$B:$B,MATCH($A128,Requerimientos!$A:$A,0)),"")</f>
         <v>M10 Calidad</v>
       </c>
-      <c r="E125" s="24" t="str">
-        <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A125,Requerimientos!$A:$A,0)),"")</f>
-        <v>Alta</v>
-      </c>
-      <c r="F125" s="24" t="str">
-        <f>IFERROR(INDEX(Requerimientos!$H:$H,MATCH($A125,Requerimientos!$A:$A,0)),"")</f>
+      <c r="E128" s="24" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$G:$G,MATCH($A128,Requerimientos!$A:$A,0)),"")</f>
+        <v>Alta</v>
+      </c>
+      <c r="F128" s="24" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$H:$H,MATCH($A128,Requerimientos!$A:$A,0)),"")</f>
         <v>L7  ·  Web</v>
       </c>
-      <c r="G125" s="24" t="str">
-        <f>IFERROR(INDEX(Requerimientos!$I:$I,MATCH($A125,Requerimientos!$A:$A,0)),"")</f>
+      <c r="G128" s="24" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$I:$I,MATCH($A128,Requerimientos!$A:$A,0)),"")</f>
         <v>App web</v>
       </c>
-      <c r="H125" s="24" t="str">
-        <f>IFERROR(INDEX(Requerimientos!$J:$J,MATCH($A125,Requerimientos!$A:$A,0)),"")</f>
+      <c r="H128" s="24" t="str">
+        <f>IFERROR(INDEX(Requerimientos!$J:$J,MATCH($A128,Requerimientos!$A:$A,0)),"")</f>
         <v>Pendiente</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="9">
     <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A61:H61"/>
     <mergeCell ref="A6:H6"/>
     <mergeCell ref="A3:H3"/>
-    <mergeCell ref="A122:H122"/>
-    <mergeCell ref="A69:H69"/>
-    <mergeCell ref="A109:H109"/>
+    <mergeCell ref="A125:H125"/>
     <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A63:H63"/>
+    <mergeCell ref="A72:H72"/>
+    <mergeCell ref="A112:H112"/>
     <mergeCell ref="A44:H44"/>
   </mergeCells>
-  <conditionalFormatting sqref="H6:H125">
+  <conditionalFormatting sqref="H6:H128">
     <cfRule type="cellIs" dxfId="5" priority="1" operator="equal">
       <formula>"Hecho"</formula>
     </cfRule>
@@ -10855,7 +10957,7 @@
       <formula>"Pendiente"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E6:E125">
+  <conditionalFormatting sqref="E6:E128">
     <cfRule type="cellIs" dxfId="1" priority="5" operator="equal">
       <formula>"Alta"</formula>
     </cfRule>

--- a/docs/requerimientos.xlsx
+++ b/docs/requerimientos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USUARIO\Desktop\roomtrip\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49937ABE-C5FD-4683-A2F0-2E13C30F46A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECEFEE0A-C158-45C1-AC22-D3AA32BA142D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="390" yWindow="195" windowWidth="21600" windowHeight="15405" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -546,7 +546,7 @@
     <t>L3  ·  L6</t>
   </si>
   <si>
-    <t>Sin este monto no se puede evaluar la regla del taxi gratuito.</t>
+    <t>Derivado del enunciado: sin este monto no se puede evaluar la regla del taxi gratuito. No se incluye en el archivo de entrega al profesor.</t>
   </si>
   <si>
     <t>RF-AH-07</t>
@@ -684,7 +684,7 @@
     <t>Autoregistrarse y quedar habilitado automáticamente</t>
   </si>
   <si>
-    <t>Al completar el formulario con nombres apellidos tipo y número de documento fecha de nacimiento correo teléfono domicilio y foto la cuenta queda activa sin aprobación</t>
+    <t>Al completar el formulario con nombres, apellidos, tipo de documento (DNI, Pasaporte o Carnet de extranjería), número de documento, fecha de nacimiento, correo, teléfono, domicilio y foto, la cuenta queda activa sin necesidad de aprobación</t>
   </si>
   <si>
     <t>Faltan en el mockup el tipo de documento y la fecha de nacimiento.</t>
@@ -759,7 +759,7 @@
     <t>El cliente ve la lista de lugares históricos cercanos registrados por el administrador del hotel</t>
   </si>
   <si>
-    <t>Falta la pantalla en Figma; el hotel ya los registra en RF-AH-01.</t>
+    <t>Derivado del enunciado: el hotel ya los registra en RF-AH-01. No se incluye en el archivo de entrega al profesor.</t>
   </si>
   <si>
     <t>RF-CL-08</t>
@@ -1632,7 +1632,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-75F8-4C25-962A-C8A1C179A207}"/>
+              <c16:uniqueId val="{00000000-B5E1-47D3-A555-0A63EC2BEBC3}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
